--- a/Issues.xlsx
+++ b/Issues.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -830,6 +830,3322 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>4053</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Nonpolar solvation energy in OpenMM Implicit Solvent models</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4053</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses implicit solvent models, nonpolar solvation energy, the ACE approximation, and references mathematical equations from a scientific paper, all of which involve domain-specific scientific knowledge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>4301</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Encode long-range Coulomb interaction with distance-dependent dielectric into openmm</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4301</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>The issue contains a mathematical equation for a distance-dependent dielectric Coulomb potential and discusses domain-specific concepts like PME, cutoff, and dielectric constants, qualifying as Type 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>2567</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>PME interpolation order</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/2567</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>documentation
+low effort
+low priority</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/4294</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>4294</v>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Issue discusses the interpolation order parameter for the PME (Particle Mesh Ewald) algorithm, a domain-specific numerical method used in molecular dynamics simulations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>4342</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Where/How does OpenMM calculate energy?</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4342</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>The issue asks about the mathematical and algorithmic details of how OpenMM computes van der Waals and electrostatic energies, which involves domain-specific scientific knowledge of force field calculations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>4253</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Efficient dipole-dipole interactions with OpenMM</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4253</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves mathematical formulations (equations in LaTeX), discusses domain-specific concepts like dipole-dipole interactions, cutoff methods, and scaling laws in molecular dynamics, making it a Type 1 scientific issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>4808</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Improvements in latest OpenMM</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4808</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses domain-specific scientific concepts such as accelerated molecular dynamics (aMD), boost potentials, collective variables, and GPU performance for statistical sampling, which involve chemistry/molecular dynamics knowledge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>3821</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Circular variance term for nonbonded interactions</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3821</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses implementing a circular variance term involving mathematical equations (norm of sum of unit vectors, number of neighbors) from scientific papers, which is domain-specific scientific knowledge in molecular dynamics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>4166</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Building virtual site based on an arbitrary amount of atoms?</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4166</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses building virtual sites based on CA atoms for non-bonded interactions in a protein domain, which involves molecular geometry and computational chemistry concepts, qualifying as domain-specific scientific knowledge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>4135</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Wrong formula for Langevin Integrator (at least in the documentation)</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4135</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/assets/6825443/8f3d28c2-5a6d-47d5-b02e-b4c144ba3d03</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/4138</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>4138</v>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses discrepancies between documented and referenced mathematical formulas for the Langevin integrator, including variance and timestep errors (Type 1), and includes an embedded image of a paper's equations (Type 2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>3676</v>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Modifying the PME calculations for smeared charges</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3676</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses modifying particle mesh Ewald (PME) calculations for smeared charge distributions in molecular simulations, referencing a specific paper and mathematical forms of the Coulomb potential, which involves domain-specific scientific knowledge in computational chemistry and physics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>1936</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>ValueError: Energy is NaN</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/1936</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses numerical precision limits in GPU molecular dynamics simulation leading to NaN energy, which involves domain-specific knowledge about force representation and fixed-point arithmetic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>3364</v>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Hybrid solvent model for protein simulation with openmm?</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3364</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="n"/>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses hybrid solvent models for protein simulation, references specific force fields and molecular dynamics methods, and involves domain-specific scientific knowledge about explicit and implicit solvent representations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>3281</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>How to reproduce standard nonbonded force as a custom nonbonded force?</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3281</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses reproducing a standard NonbondedForce using CustomNonbondedForce, involving mathematical formulas for Lennard-Jones and Coulomb interactions, reaction field, and dispersion corrections, which are domain-specific scientific knowledge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>3348</v>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>weird openmm warnings in miniconda3/lib/python3.8/site-packages/openmm/app/charmmparameterset.py</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3348</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr"/>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses conflicting dihedral parameter definitions in CHARMM force fields and the VRORV integrator's temperature accuracy, both involving domain-specific scientific knowledge about molecular simulation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>933</v>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Custom Ewald force</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/933</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr"/>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses Particle Mesh Ewald (PME) implementation for custom forces, involving mathematical derivations, potential functions, convergence conditions, and recurrence relations, which are domain-specific scientific knowledge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>2593</v>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Around 2 % overestimation for density under NPT simulation by OpenMM compared with other softwares</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/2593</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>https://user-images.githubusercontent.com/379616/76448902-66a7b800-63cb-11ea-856d-b9fde323cd48.png</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr"/>
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses scientific behavior (density overestimation in MD simulations comparing barostat algorithms) and includes an embedded scientific plot of density vs time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>2496</v>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Discrepancy in results between OpenMM versions</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/2496</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>https://user-images.githubusercontent.com/28569164/70261519-9ad26380-1760-11ea-9127-2787652e6f33.png
+https://user-images.githubusercontent.com/28569164/70261543-a887e900-1760-11ea-87d7-2cf6758b9f26.png</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr"/>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses discrepancies in molecular simulation results between OpenMM versions, involving force field parameters, constraints, and timestep settings, which are domain-specific scientific concepts, and includes scientific plots of RMSD data for protein folding analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>1766</v>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Drude particles have zero mass</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/1766</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr"/>
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves domain-specific scientific knowledge about Drude particles in force fields, masses, simulation stability, and integrator behavior, which are all concepts in computational chemistry and molecular dynamics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>1796</v>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Features to support metadynamics</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/1796</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/1837</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>1837</v>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses implementing metadynamics in OpenMM, involving collective variables, biasing potentials, and tabulated function derivatives, which are domain-specific concepts in molecular dynamics and computational chemistry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>1574</v>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>my new method to compute nonbonded force</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/1574</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr"/>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses implementing a new method for computing nonbonded forces using a quantum mechanics database, which involves domain-specific scientific concepts like pair molecular configuration potential and spatial configuration, but does not include any scientific images.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>2297</v>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Question regarding CMMotionRemover()</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/2297</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses the behavior of CMMotionRemover in molecular dynamics simulations, referencing theory documentation and internal implementation details, which involves domain-specific scientific knowledge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>1168</v>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Extending ffxml to separate charge and Lennard-Jones parameter assignment</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/1168</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr"/>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses modifications to force field XML format for molecular simulation, referencing AMBER force fields, Lennard-Jones parameters, and atom typing, which are domain-specific scientific concepts in computational chemistry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>1696</v>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Implement pair-wise nonbonded interaction using CustomNonbondedForce</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/1696</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves domain-specific scientific knowledge about molecular dynamics force fields, nonbonded interaction parameterization, and combining rules, including mathematical formulas for sigma and epsilon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>4042</v>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Cost of CustomHbondForce</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4042</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>https://user-images.githubusercontent.com/24451788/233815448-3091d1f8-a5ee-4d92-9e6a-8b368fe2286f.png</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses the performance of CustomHbondForce with a mathematical formula involving cutoff functions, hydrogen bond geometry, and physical parameters, which is domain-specific scientific knowledge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>761</v>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>We should report PME grid dimensions for AmoebaMultipoleForce</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/761</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr"/>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses PME grid dimensions, Ewald parameters, and algorithmic details for electrostatic calculations in molecular dynamics, which are domain-specific scientific concepts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>1108</v>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Energy discrepancies between platforms on large systems</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/1108</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr"/>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="n"/>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses energy discrepancies in molecular dynamics simulations using PME, involving Ewald error tolerance, grid sizes, and FFT platform differences, which are domain-specific numerical methods in computational chemistry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Interface extension proposal: Addition of System.getNumVsites() and System.getNumDegreesOfFreedom()</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/350</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves a formula for computing degrees of freedom in molecular dynamics systems, referencing virtual sites, constraints, and zero-mass particles, which are domain-specific scientific concepts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>3983</v>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Particles in same position</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3983</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses custom non-bonded potentials with LaTeX equations, force calculations, and molecular dynamics simulation behavior, which are domain-specific scientific knowledge in computational chemistry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>5270</v>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Can vectors be used in CustomManyParticleForce</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/5270</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr"/>
+      <c r="I38" s="2" t="n"/>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves domain-specific scientific knowledge about implementing molecular force field terms using vector math (cross product, dot product, angle calculations) and mathematical expressions for CH-pi interactions, which is firmly in the realm of computational chemistry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>1437</v>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Space group symmetry</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/1437</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n"/>
+      <c r="J39" s="2" t="n"/>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses implementing space group symmetry for molecular simulations, involving crystallographic concepts, mathematical transformations (rotation matrices, translation vectors), and references domain-specific knowledge about space groups and virtual sites.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>4929</v>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Time Synchronization of Forces &amp; Velocities from VerletIntegrator</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4929</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr"/>
+      <c r="I40" s="2" t="n"/>
+      <c r="J40" s="2" t="n"/>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses the leapfrog algorithm, velocity correction using force and mass terms, and constraints, which are domain-specific scientific numerical methods in molecular dynamics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>5035</v>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>SymmetrySite use case</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/5035</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr"/>
+      <c r="I41" s="2" t="n"/>
+      <c r="J41" s="2" t="n"/>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses biasing protein orientation relative to a surface using SymmetrySite and angle forces, involving domain-specific concepts from molecular simulation and metadynamics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>5025</v>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Gromacs topology reader has two issues for systems with NBFIX</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/5025</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr"/>
+      <c r="I42" s="2" t="n"/>
+      <c r="J42" s="2" t="n"/>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>The issue describes incorrect mathematical formulas for Lennard-Jones interactions and parameter handling in Gromacs topology reader, involving domain-specific scientific knowledge about force fields and combinatorial rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>4592</v>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Alchemical free energy calculation: How to remove the original NonbondedForce after add CustomNonbondedForce between two sets?</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4592</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/user-attachments/assets/2d87635f-ce21-4c99-acc3-fc6e29a7d674
+https://github.com/user-attachments/assets/bd0e7746-4603-408d-8a87-7b827bc09833</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr"/>
+      <c r="I43" s="2" t="n"/>
+      <c r="J43" s="2" t="n"/>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses alchemical free energy calculations, nonbonded force handling, and PME methods, which are domain-specific scientific topics, and it includes images of free energy difference plots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>5274</v>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Feature request: Add atom-wise box rescaling option to MonteCarloAnisotropicBarostat and select epsilon value for finite difference equation</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/5274</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/5278</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>5278</v>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses domain-specific scientific knowledge about barostat algorithms, finite difference virial calculations, and polymer network simulations, referencing numerical methods and physical constants.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>3740</v>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Time evolution of pressure</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3740</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>question
+faq</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/4881</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>4881</v>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves domain-specific scientific knowledge about computing pressure in molecular dynamics simulations, including discussion of the virial, finite-difference energy derivatives, and references to a physics paper.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>4868</v>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Question on the nonbonded cutoff implementation for implicit solvent models</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4868</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr"/>
+      <c r="I46" s="2" t="n"/>
+      <c r="J46" s="2" t="n"/>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses the mathematical implementation of nonbonded cutoffs in generalized Born implicit solvent models, including equations and physical constants, which is domain-specific scientific knowledge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>4896</v>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Questions Regarding LiGaMD2 Implementation: PME Electrostatics and Multiple CustomNonbondedForce Objects</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4896</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr"/>
+      <c r="I47" s="2" t="n"/>
+      <c r="J47" s="2" t="n"/>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses domain-specific scientific concepts such as LiGaMD2, PME electrostatics, CustomNonbondedForce, and 12-6-4 Lennard-Jones potentials, requiring specialized chemistry and physics knowledge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>1435</v>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Dissipative Particle Dynamics</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/1435</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/4799</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>4799</v>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses implementing Dissipative Particle Dynamics (DPD), a specific scientific simulation method, referencing a paper and involving domain concepts like hydrodynamics and coarse-grained simulations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>4635</v>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Is there a way to output the pressure tensor to calculate the viscosity using the Green-Kubo(equilibrium state method) on Openmm? </t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4635</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr"/>
+      <c r="I49" s="2" t="n"/>
+      <c r="J49" s="2" t="n"/>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses equilibrium molecular dynamics methods for computing viscosity via the Green-Kubo relation and pressure tensor, which involves domain-specific scientific knowledge in statistical mechanics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>4848</v>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Unexpectedly High Temperature in Brownian Integrator</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4848</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr"/>
+      <c r="I50" s="2" t="n"/>
+      <c r="J50" s="2" t="n"/>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves domain-specific knowledge about molecular dynamics integrators and temperature computation in Brownian dynamics, which is a scientific concept.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>3856</v>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Cannot use openMM to run em on a solavted system from Gromacs topology with HBond constrain</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3856</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr"/>
+      <c r="I51" s="2" t="n"/>
+      <c r="J51" s="2" t="n"/>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses molecular dynamics constraints, CCMA and LINCS algorithms, and over-constrained molecular systems, which are domain-specific scientific concepts in computational chemistry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>4471</v>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Free energy calculation for Protein-protein binding with Openmm</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4471</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n"/>
+      <c r="J52" s="2" t="n"/>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses protein-protein binding free energy calculations, referencing alchemical methods and convergence challenges, which are domain-specific scientific concepts in computational chemistry and thermodynamics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>5038</v>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Equations in API documentation</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/5038</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>enhancement
+documentation</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n"/>
+      <c r="J53" s="2" t="n"/>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses adding equations and mathematical notation for force field energy terms to the API documentation, which involves domain-specific scientific knowledge and symbolic formulas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>4643</v>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Interaction energy with energy minimization</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4643</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr"/>
+      <c r="I54" s="2" t="n"/>
+      <c r="J54" s="2" t="n"/>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves domain-specific scientific knowledge about molecular dynamics force fields, energy minimization, and interaction energy computation in protein-ligand complexes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>4674</v>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Accessing Interatomic Distance in CustomExternalForce</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4674</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr"/>
+      <c r="I55" s="2" t="n"/>
+      <c r="J55" s="2" t="n"/>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves implementing a DLVO potential using mathematical equations for interatomic distances, which is a domain-specific scientific concept.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>4809</v>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Modifying forces on-the-fly</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4809</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr"/>
+      <c r="I56" s="2" t="n"/>
+      <c r="J56" s="2" t="n"/>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses modifying forces in molecular dynamics simulations, referencing physical constants (Boltzmann constant, gas constant), integrators, and ML/MM force evaluation, which involves domain-specific scientific knowledge of molecular simulation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>4581</v>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Applying flat-bottom potential restraints</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4581</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/assets/103068766/0a2a80a8-cd2e-496c-a940-d77a973297c8
+https://github.com/user-attachments/assets/d912fce6-6761-405c-8bd7-0898abdfde75
+https://github.com/user-attachments/as Can you explain what I should be seeing in the animation, and in what way it doesn't work?  Does the width of the black rectangle represent the restrained area (4.8 nm
+https://github.com/user-attachments/assets/73ba3bfc-9740-4b7e-a835-731b22ae05d9
+https://github.com/user-attachments/assets/e5f57947-c843-4b7a-b327-c2b1df652222</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr"/>
+      <c r="I57" s="2" t="n"/>
+      <c r="J57" s="2" t="n"/>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves applying flat-bottom potential restraints with mathematical equations and physical constants, and includes scientific images showing the resulting ion behavior.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>4359</v>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Trajectory reporters not writing the box dimensions</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4359</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="inlineStr"/>
+      <c r="I58" s="2" t="n"/>
+      <c r="J58" s="2" t="n"/>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses periodic boundary conditions, topology properties, and system settings in molecular dynamics simulations, which are domain-specific scientific concepts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>4387</v>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Usage of NonBondedForce.setIncludeDirectSpace(False)</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4387</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr"/>
+      <c r="I59" s="2" t="n"/>
+      <c r="J59" s="2" t="n"/>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves domain-specific scientific knowledge about PME electrostatics, direct/reciprocal space contributions, and exception handling in molecular dynamics force calculations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>4296</v>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Custom virtual sites</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4296</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr"/>
+      <c r="H60" s="3" t="inlineStr"/>
+      <c r="I60" s="2" t="n"/>
+      <c r="J60" s="2" t="n"/>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses custom virtual site equations involving bond vectors and deviation from equilibrium bond lengths, which are domain-specific mathematical formulations related to molecular dynamics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>4303</v>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>DrudeForce issues/questions</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4303</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr"/>
+      <c r="H61" s="3" t="inlineStr"/>
+      <c r="I61" s="2" t="n"/>
+      <c r="J61" s="2" t="n"/>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses scientific domain concepts (Drude polarizable force field, Thole damping, polarization energy comparison between OpenMM and GROMACS) and numerical precision in molecular simulations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>3066</v>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>external electric field</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3066</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>https://user-images.githubusercontent.com/28215638/111356721-99ae1700-86c3-11eb-8c0d-658ec6bb9d75.png</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n"/>
+      <c r="J62" s="2" t="n"/>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses simulating an external electric field on a protein, involving force field charges and domain-specific chemical knowledge, and includes an image of a table of amino acid charges.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>4414</v>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Adding free ions in topology</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4414</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr"/>
+      <c r="H63" s="3" t="inlineStr"/>
+      <c r="I63" s="2" t="n"/>
+      <c r="J63" s="2" t="n"/>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves scientific domain knowledge such as molecular dynamics, RNA folding, divalent ions, potential functions, tabulated functions, and unit conversions (nm vs angstrom), with explicit references to equations and domain-specific scientific concepts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>4262</v>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Units of virtual site weights</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4262</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr"/>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>documentation</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n"/>
+      <c r="J64" s="2" t="n"/>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses mathematical equations and physical units (distance squared, inverse distance) for virtual site weights in molecular dynamics, which is domain-specific scientific knowledge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>4228</v>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Plugin for xtb</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4228</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr"/>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n"/>
+      <c r="J65" s="2" t="n"/>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses integrating a plugin for the xtb semiempirical quantum chemistry package, referencing domain-specific concepts like GFN-FF force fields, GFN2-xTB methods, and QM/MM embedding, which qualifies as Type 1 scientific domain knowledge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>4132</v>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Equations for calculating non-bonded energies</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4132</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr"/>
+      <c r="H66" s="3" t="inlineStr"/>
+      <c r="I66" s="2" t="n"/>
+      <c r="J66" s="2" t="n"/>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves mathematical equations for non-bonded energy calculations (Coulomb and Lennard-Jones) and combining rules, which are domain-specific scientific knowledge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>4222</v>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>How is surface tension defined for MonteCarloMembraneBarostat?</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4222</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr"/>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n"/>
+      <c r="J67" s="2" t="n"/>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves a discussion of the mathematical definition of surface tension in membrane simulations, including a LaTeX equation and domain-specific thermodynamic concepts, and reports an error related to that definition, making it a Type 1 scientific issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>4100</v>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Nose Hoover Friction Coefficient/Debugging the Step Function</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4100</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr"/>
+      <c r="H68" s="3" t="inlineStr"/>
+      <c r="I68" s="2" t="n"/>
+      <c r="J68" s="2" t="n"/>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves mathematical formulations from Hoover's paper, discusses the friction coefficient and its derivative in the Nose-Hoover integrator, and references domain-specific scientific knowledge about thermostat algorithms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>4016</v>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Calculation of the non-polar part of the GBSA implicit solvents</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4016</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr"/>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n"/>
+      <c r="J69" s="2" t="n"/>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses the mathematical formula for the non-polar part of GBSA solvation free energy, compares it to a published equation, and asks about correctness of the implementation, which involves domain-specific scientific knowledge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>4244</v>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>how to implement gromacs virtual site type 4fdn using LocalCoordinatesSite?</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4244</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr"/>
+      <c r="H70" s="3" t="inlineStr"/>
+      <c r="I70" s="2" t="n"/>
+      <c r="J70" s="2" t="n"/>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>Issue discusses implementing a Gromacs virtual site type using OpenMM's LocalCoordinatesSite, referencing mathematical definitions and molecular geometry concepts (lone pairs, Trimethylamine), which involves domain-specific scientific knowledge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>3858</v>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Calculation of reweighting factor in metadynamics (Tiwary, Parrinello, J. Phys. Chem. B 2015, 119, 3, 736–742)</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3858</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr"/>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n"/>
+      <c r="J71" s="2" t="n"/>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses implementing a time-dependent reweighting factor in metadynamics, referencing a specific scientific paper and involving domain-specific concepts such as bias potential, free energy surface, and reweighting algorithm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>3889</v>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>FP64 emulation for Metal plugin</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3889</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr"/>
+      <c r="H72" s="3" t="inlineStr"/>
+      <c r="I72" s="2" t="n"/>
+      <c r="J72" s="2" t="n"/>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses numerical precision improvements through Kahan summation and FP64 emulation in a scientific molecular dynamics library, involving domain-specific numerical methods and floating-point accuracy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>3777</v>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Efficiency of nonbonded custom force</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3777</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr"/>
+      <c r="H73" s="3" t="inlineStr"/>
+      <c r="I73" s="2" t="n"/>
+      <c r="J73" s="2" t="n"/>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses implementing a nonbonded custom force with Lennard-Jones-type energy expressions, combining rules, and tabulated functions, which involves domain-specific scientific knowledge in molecular simulation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>3744</v>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Substituting energy value from external calculation into openmm for coordinates generation</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3744</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr"/>
+      <c r="H74" s="3" t="inlineStr"/>
+      <c r="I74" s="2" t="n"/>
+      <c r="J74" s="2" t="n"/>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses substituting single point energies from external QM software into OpenMM for force computation and dynamics, involving domain concepts like energy derivatives, ab initio molecular dynamics, and force fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>3611</v>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Handling mixed periodic/non-periodic CVs in Metadynamics</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3611</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr"/>
+      <c r="H75" s="3" t="inlineStr"/>
+      <c r="I75" s="2" t="n"/>
+      <c r="J75" s="2" t="n"/>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses handling periodic and non-periodic collective variables (CVs) in metadynamics, which involves domain-specific knowledge of molecular dynamics, dihedral angles, and bias functional forms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Reporting the pressure</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/147</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr"/>
+      <c r="H76" s="3" t="inlineStr"/>
+      <c r="I76" s="2" t="n"/>
+      <c r="J76" s="2" t="n"/>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses computing pressure via the virial equation in molecular dynamics simulations, involving domain-specific concepts like barostats, PBCs, and AMOEBA force fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>3437</v>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>customGBforce issues</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3437</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr"/>
+      <c r="H77" s="3" t="inlineStr"/>
+      <c r="I77" s="2" t="n"/>
+      <c r="J77" s="2" t="n"/>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves mathematical formulas for implicit membrane models (Imem, Imol, B), domain-specific concepts like Generalized Born (GB) forces, and discussion of physical behavior of charged particles in a membrane, which are all scientific and mathematical in nature.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>2898</v>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Potential enhancement: Add option to MonteCarloBarostat to not wrap coordinates into box</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/2898</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr"/>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/3260</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>3260</v>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses molecular simulation algorithms, Monte Carlo barostat behavior, and molecular re-imaging techniques, all domain-specific scientific knowledge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>3782</v>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>How to warm up a system followed by NVT/NPT equilibration while slowly removing backbone constraints</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3782</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>https://user-images.githubusercontent.com/79198385/191270450-0dc3f3e9-3592-4eca-af7a-644f066bcfbb.png</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr"/>
+      <c r="I79" s="2" t="n"/>
+      <c r="J79" s="2" t="n"/>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses molecular dynamics simulation protocols (NVT/NPT equilibration, backbone restraints) which are domain-specific scientific knowledge, and includes a screenshot of a protein-solvent system as a scientific image.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>3426</v>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>NonbondedForce cutoff</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3426</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr"/>
+      <c r="H80" s="3" t="inlineStr"/>
+      <c r="I80" s="2" t="n"/>
+      <c r="J80" s="2" t="n"/>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses domain-specific scientific knowledge about nonbonded interactions, cutoff distances, PME electrostatics, and reaction field approximation in a molecular simulation context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>3292</v>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>[Question] How to create a 2D potential in OpenMM and sample it with Langevin integrator</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3292</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>https://user-images.githubusercontent.com/37775482/137891909-c8774402-ea9c-4404-b150-3219e049c123.png</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr"/>
+      <c r="I81" s="2" t="n"/>
+      <c r="J81" s="2" t="n"/>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves a mathematical potential energy function (domain-specific scientific knowledge) and includes an image of the equation, qualifying it as both type 1 and type 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>3282</v>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>the theory and mathematical equation behind getPotentialEnergy()</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3282</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr"/>
+      <c r="H82" s="3" t="inlineStr"/>
+      <c r="I82" s="2" t="n"/>
+      <c r="J82" s="2" t="n"/>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>The issue asks for the theory and mathematical equation behind getPotentialEnergy(), which involves molecular force field energy calculations, a domain-specific scientific concept.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>3031</v>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Is it Possible to Calculate just Nonbonded energy for saving time?</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3031</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr"/>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n"/>
+      <c r="J83" s="2" t="n"/>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses calculating only nonbonded energy in molecular dynamics simulations, which involves domain-specific knowledge about force fields, energy groups, and interaction algorithms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>3137</v>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Question about the SHAKE implementation</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3137</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>https://user-images.githubusercontent.com/72212636/120674974-a3dde700-c462-11eb-8993-6c068bcee183.png</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n"/>
+      <c r="J84" s="2" t="n"/>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses mathematical equations and numerical methods (SHAKE algorithm, first-order vs quadratic solving) and includes an image of the relevant equation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>3090</v>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>Spherical computational domain</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3090</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr"/>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n"/>
+      <c r="J85" s="2" t="n"/>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses implementing spherical boundary conditions with complex cumulative distribution functions for reinjecting particles, referencing specific equations from a scientific paper, which involves domain-specific scientific knowledge in computational physics and molecular dynamics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>3008</v>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Update charges in every step</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3008</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr"/>
+      <c r="H86" s="3" t="inlineStr"/>
+      <c r="I86" s="2" t="n"/>
+      <c r="J86" s="2" t="n"/>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses implementing a polarizable model (CTPOL) with a mathematical formula for charge transfer depending on atomic distances, involving domain-specific scientific knowledge about force fields and electrostatics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>2033</v>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>AMOEBA plugin documentation improvements</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/2033</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr"/>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>documentation</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n"/>
+      <c r="J87" s="2" t="n"/>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses domain-specific scientific concepts like polarizable forcefields, units for polarizability, Thole damping, and polarization groups, and references equations in cited literature, which qualifies as Type 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="n">
+        <v>3026</v>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>Specific custom external force</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3026</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr"/>
+      <c r="H88" s="3" t="inlineStr"/>
+      <c r="I88" s="2" t="n"/>
+      <c r="J88" s="2" t="n"/>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves domain-specific scientific knowledge about solving coupled Newton's and Poisson's equations for charged particles, including numerical methods and electrostatic potential calculations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="n">
+        <v>2931</v>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>What is the best way to calculate time-averaged distances in a custom force?</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/2931</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr"/>
+      <c r="H89" s="3" t="inlineStr"/>
+      <c r="I89" s="2" t="n"/>
+      <c r="J89" s="2" t="n"/>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses a mathematical recurrence relation for time-averaged distances, references a scientific paper, and involves custom force implementation with energy expressions, which are domain-specific scientific concepts.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -841,7 +4157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -873,22 +4189,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>89.8%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>10.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
-        <v>8</v>
+      <c r="B4" s="1" t="n">
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/Issues.xlsx
+++ b/Issues.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K89"/>
+  <dimension ref="A1:K116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -504,16 +504,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>4567</v>
+        <v>4827</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Discrepancy in Reaction Field (RF) Implementation between OpenMM and GROMACS</t>
+          <t>Why no flexibleConstraints option in Amber createSystem?</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/4567</t>
+          <t>https://github.com/openmm/openmm/issues/4827</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -528,11 +528,17 @@
       </c>
       <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/4832</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>4832</v>
+      </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses discrepancies in mathematical formulas for Reaction Field (RF) implementation, involving scientific constants like epsilon_r and energy calculations, which is domain-specific scientific knowledge.</t>
+          <t>The issue discusses molecular dynamics force field parameters, constraints, and minimization involving domain-specific scientific concepts about Amber and CHARMM systems.</t>
         </is>
       </c>
     </row>
@@ -543,16 +549,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>4827</v>
+        <v>3647</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Why no flexibleConstraints option in Amber createSystem?</t>
+          <t>Calculate the pressure tensor</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/4827</t>
+          <t>https://github.com/openmm/openmm/issues/3647</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -566,18 +572,23 @@
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>question
+cookbook</t>
+        </is>
+      </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/pull/4832</t>
+          <t>https://github.com/openmm/openmm/pull/4881</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>4832</v>
+        <v>4881</v>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses molecular dynamics force field parameters, constraints, and minimization involving domain-specific scientific concepts about Amber and CHARMM systems.</t>
+          <t>The issue involves mathematical formulas and domain-specific scientific knowledge about calculating the pressure tensor and virial stress in molecular dynamics simulations, referencing LAMMPS documentation and a paper.</t>
         </is>
       </c>
     </row>
@@ -588,16 +599,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4350</v>
+        <v>2567</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>custom function in the expression of energy function</t>
+          <t>PME interpolation order</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/4350</t>
+          <t>https://github.com/openmm/openmm/issues/2567</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -611,351 +622,421 @@
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="2" t="n"/>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>The issue requests a feature to compute the angle between two planes defined by atoms in a molecular force field, which involves domain-specific geometric and chemical concepts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>openmm/openmm</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>5295</v>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>PSWF-based Ewald summation</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/openmm/openmm/issues/5295</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>enhancement</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="n"/>
-      <c r="J5" s="2" t="n"/>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>The issue proposes a new mathematical method (PSWF-based Ewald summation) for electrostatics in MD simulations, discussing algorithms, grid size, and computational physics concepts, without any scientific images.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>openmm/openmm</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>4860</v>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Obtaining polarization data from MDs with Drude polarizable force field</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/openmm/openmm/issues/4860</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="2" t="n"/>
-      <c r="J6" s="2" t="n"/>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>The issue involves computing polarization, induced dipole moments, and electric field from molecular dynamics simulations using a Drude polarizable force field, which are domain-specific scientific concepts in computational chemistry and biophysics.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>openmm/openmm</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>3972</v>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Pressure tensor calculation every 50 timesteps</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/openmm/openmm/issues/3972</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="2" t="n"/>
-      <c r="J7" s="2" t="n"/>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>The issue involves domain-specific scientific knowledge about pressure tensor calculation, surface tension, virial, and finite-difference methods for molecular dynamics simulations of ionic liquids.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>openmm/openmm</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>3647</v>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Calculate the pressure tensor</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/openmm/openmm/issues/3647</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>question
-cookbook</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/openmm/openmm/pull/4881</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>4881</v>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>The issue involves mathematical formulas and domain-specific scientific knowledge about calculating the pressure tensor and virial stress in molecular dynamics simulations, referencing LAMMPS documentation and a paper.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>openmm/openmm</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>4880</v>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Question regarding PME Implementation</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/openmm/openmm/issues/4880</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="2" t="n"/>
-      <c r="J9" s="2" t="n"/>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>The issue discusses the implementation of PME electrostatic calculations, including mathematical formulas (erfc, alpha, cutoff dependence) and domain-specific physical chemistry concepts, making it Type 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>openmm/openmm</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>4053</v>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Nonpolar solvation energy in OpenMM Implicit Solvent models</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/openmm/openmm/issues/4053</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="2" t="n"/>
-      <c r="J10" s="2" t="n"/>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>The issue discusses implicit solvent models, nonpolar solvation energy, the ACE approximation, and references mathematical equations from a scientific paper, all of which involve domain-specific scientific knowledge.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>openmm/openmm</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>4301</v>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Encode long-range Coulomb interaction with distance-dependent dielectric into openmm</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/openmm/openmm/issues/4301</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="2" t="n"/>
-      <c r="J11" s="2" t="n"/>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>The issue contains a mathematical equation for a distance-dependent dielectric Coulomb potential and discusses domain-specific concepts like PME, cutoff, and dielectric constants, qualifying as Type 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>openmm/openmm</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>2567</v>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>PME interpolation order</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/openmm/openmm/issues/2567</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>documentation
 low effort
 low priority</t>
         </is>
       </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/4294</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>4294</v>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Issue discusses the interpolation order parameter for the PME (Particle Mesh Ewald) algorithm, a domain-specific numerical method used in molecular dynamics simulations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>4135</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Wrong formula for Langevin Integrator (at least in the documentation)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4135</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/assets/6825443/8f3d28c2-5a6d-47d5-b02e-b4c144ba3d03</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/4138</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>4138</v>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses discrepancies between documented and referenced mathematical formulas for the Langevin integrator, including variance and timestep errors (Type 1), and includes an embedded image of a paper's equations (Type 2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>1796</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Features to support metadynamics</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/1796</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/1837</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>1837</v>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses implementing metadynamics in OpenMM, involving collective variables, biasing potentials, and tabulated function derivatives, which are domain-specific concepts in molecular dynamics and computational chemistry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>5274</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Feature request: Add atom-wise box rescaling option to MonteCarloAnisotropicBarostat and select epsilon value for finite difference equation</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/5274</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/5278</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>5278</v>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses domain-specific scientific knowledge about barostat algorithms, finite difference virial calculations, and polymer network simulations, referencing numerical methods and physical constants.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>3740</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Time evolution of pressure</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3740</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>question
+faq</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/4881</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>4881</v>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves domain-specific scientific knowledge about computing pressure in molecular dynamics simulations, including discussion of the virial, finite-difference energy derivatives, and references to a physics paper.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>1435</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Dissipative Particle Dynamics</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/1435</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/4799</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>4799</v>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses implementing Dissipative Particle Dynamics (DPD), a specific scientific simulation method, referencing a paper and involving domain concepts like hydrodynamics and coarse-grained simulations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>2898</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Potential enhancement: Add option to MonteCarloBarostat to not wrap coordinates into box</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/2898</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/3260</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>3260</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses molecular simulation algorithms, Monte Carlo barostat behavior, and molecular re-imaging techniques, all domain-specific scientific knowledge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>4023</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Problem adding membrane to system</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4023</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/4025</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>4025</v>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves molecular dynamics force fields (CHARMM36, amber) and membrane modeling, which are domain-specific scientific concepts in computational chemistry, and the error arises from how a specific force field interacts with the membrane addition function.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>1702</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Proposed API for CHARMM-like BLOCK nonbonded facility</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/1702</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/pull/4294</t>
+          <t>https://github.com/openmm/openmm/pull/2105</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>4294</v>
+        <v>2105</v>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Issue discusses the interpolation order parameter for the PME (Particle Mesh Ewald) algorithm, a domain-specific numerical method used in molecular dynamics simulations.</t>
+          <t>The issue contains mathematical equations (linear combinations of parameters), references to domain-specific concepts (PME, lambda dynamics, CHARMM BLOCK), and discusses energy derivatives, all of which are scientific/mathematical in nature.</t>
         </is>
       </c>
     </row>
@@ -966,16 +1047,16 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>4342</v>
+        <v>1567</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Where/How does OpenMM calculate energy?</t>
+          <t>Potential GPU Performance Bottleneck?</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/4342</t>
+          <t>https://github.com/openmm/openmm/issues/1567</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -990,11 +1071,17 @@
       </c>
       <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="2" t="n"/>
-      <c r="J13" s="2" t="n"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/1640</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>1640</v>
+      </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>The issue asks about the mathematical and algorithmic details of how OpenMM computes van der Waals and electrostatic energies, which involves domain-specific scientific knowledge of force field calculations.</t>
+          <t>The issue discusses a performance bottleneck in the DIIS algorithm for iterating induced dipoles, involving matrix inversion and numerical precision, which are domain-specific scientific computing concepts.</t>
         </is>
       </c>
     </row>
@@ -1005,16 +1092,16 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>4253</v>
+        <v>2250</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Efficient dipole-dipole interactions with OpenMM</t>
+          <t>OpenCL platform falling back to CPU for minimization</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/4253</t>
+          <t>https://github.com/openmm/openmm/issues/2250</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1029,11 +1116,17 @@
       </c>
       <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="2" t="n"/>
-      <c r="J14" s="2" t="n"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/2255</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>2255</v>
+      </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>The issue involves mathematical formulations (equations in LaTeX), discusses domain-specific concepts like dipole-dipole interactions, cutoff methods, and scaling laws in molecular dynamics, making it a Type 1 scientific issue.</t>
+          <t>The issue involves a mathematical energy equation for a CustomCompoundBondForce, references domain-specific concepts like MDFF, force fields, and minimization algorithms, and discusses numerical precision and platform behavior in scientific software.</t>
         </is>
       </c>
     </row>
@@ -1044,16 +1137,16 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>4808</v>
+        <v>4077</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Improvements in latest OpenMM</t>
+          <t>RPMDIntegrator does not integrate at double precision at mixed prec mode</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/4808</t>
+          <t>https://github.com/openmm/openmm/issues/4077</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1067,12 +1160,22 @@
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="2" t="n"/>
-      <c r="J15" s="2" t="n"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/4079</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>4079</v>
+      </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses domain-specific scientific concepts such as accelerated molecular dynamics (aMD), boost potentials, collective variables, and GPU performance for statistical sampling, which involve chemistry/molecular dynamics knowledge.</t>
+          <t>The issue discusses numerical precision and energy conservation in a molecular dynamics integrator, which involves domain-specific scientific knowledge about numerical methods and physics.</t>
         </is>
       </c>
     </row>
@@ -1083,16 +1186,16 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>3821</v>
+        <v>1491</v>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Circular variance term for nonbonded interactions</t>
+          <t>problem in energy/force calculation</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/3821</t>
+          <t>https://github.com/openmm/openmm/issues/1491</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1106,12 +1209,22 @@
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr"/>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/1540</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>1540</v>
+      </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses implementing a circular variance term involving mathematical equations (norm of sum of unit vectors, number of neighbors) from scientific papers, which is domain-specific scientific knowledge in molecular dynamics.</t>
+          <t>The issue involves domain-specific scientific knowledge about GB implicit solvent models (GBn, GBn2) and numerical precision in energy/force calculations leading to NaN energies.</t>
         </is>
       </c>
     </row>
@@ -1122,39 +1235,47 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>4166</v>
+        <v>4548</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Building virtual site based on an arbitrary amount of atoms?</t>
+          <t>Incorrect Potential Energy with MonteCarloFlexibleBarostat</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/4166</t>
+          <t>https://github.com/openmm/openmm/issues/4548</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>question</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/assets/33414534/514e5615-32bc-44da-94a3-453cf1a4c1aa
+https://github.com/openmm/openmm/assets/33414534/0fdadfbd-1a7e-4c1a-a212-99442edac8d8
+https://github.com/openmm/openmm/assets/33414534/267c83f2-d969-4775-82c6-9669cae41d2b</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/4618</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>4618</v>
+      </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses building virtual sites based on CA atoms for non-bonded interactions in a protein domain, which involves molecular geometry and computational chemistry concepts, qualifying as domain-specific scientific knowledge.</t>
+          <t>The issue describes incorrect potential energy and density values in molecular dynamics simulations with a flexible barostat, involving domain-specific concepts like potential energy, box vectors, and numerical precision, and includes scientific plots showing energy traces.</t>
         </is>
       </c>
     </row>
@@ -1165,16 +1286,16 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>4135</v>
+        <v>4905</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Wrong formula for Langevin Integrator (at least in the documentation)</t>
+          <t>Long-range electrostatics methods should include net charge correction</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/4135</t>
+          <t>https://github.com/openmm/openmm/issues/4905</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1184,30 +1305,26 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/openmm/openmm/assets/6825443/8f3d28c2-5a6d-47d5-b02e-b4c144ba3d03</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>enhancement</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/pull/4138</t>
+          <t>https://github.com/openmm/openmm/pull/4907</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>4138</v>
+        <v>4907</v>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses discrepancies between documented and referenced mathematical formulas for the Langevin integrator, including variance and timestep errors (Type 1), and includes an embedded image of a paper's equations (Type 2).</t>
+          <t>The issue involves mathematical correction terms for electrostatic interactions (Type 1) and includes scientific plots showing energy dependence on the Ewald parameter (Type 2).</t>
         </is>
       </c>
     </row>
@@ -1218,16 +1335,16 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>3676</v>
+        <v>5067</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Modifying the PME calculations for smeared charges</t>
+          <t>Energy discrepancy in particle parameter offsets using CUDA in 8.3.x</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/3676</t>
+          <t>https://github.com/openmm/openmm/issues/5067</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1242,11 +1359,17 @@
       </c>
       <c r="G19" s="3" t="inlineStr"/>
       <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/5069</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>5069</v>
+      </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses modifying particle mesh Ewald (PME) calculations for smeared charge distributions in molecular simulations, referencing a specific paper and mathematical forms of the Coulomb potential, which involves domain-specific scientific knowledge in computational chemistry and physics.</t>
+          <t>The issue reports an energy discrepancy in molecular dynamics simulations due to a numerical precision problem related to the plasma self energy correction, which is a domain-specific scientific behavior involving force field calculations and nonbonded interactions.</t>
         </is>
       </c>
     </row>
@@ -1257,16 +1380,16 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1936</v>
+        <v>3921</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>ValueError: Energy is NaN</t>
+          <t>AmoebaVdwForce.get/setParticleParameters() not working as intended</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/1936</t>
+          <t>https://github.com/openmm/openmm/issues/3921</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1281,11 +1404,17 @@
       </c>
       <c r="G20" s="3" t="inlineStr"/>
       <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="2" t="n"/>
-      <c r="J20" s="2" t="n"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/3923</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>3923</v>
+      </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses numerical precision limits in GPU molecular dynamics simulation leading to NaN energy, which involves domain-specific knowledge about force representation and fixed-point arithmetic.</t>
+          <t>The issue reports incorrect behavior in setting/getting AMOEBA vdW force field parameters, involving domain-specific scientific knowledge of force field combining rules and parameter handling.</t>
         </is>
       </c>
     </row>
@@ -1296,16 +1425,16 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>3364</v>
+        <v>3325</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Hybrid solvent model for protein simulation with openmm?</t>
+          <t>Exception raised when creating exception with zero sigma and epsilon</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/3364</t>
+          <t>https://github.com/openmm/openmm/issues/3325</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1321,14 +1450,20 @@
       <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>question</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="n"/>
-      <c r="J21" s="2" t="n"/>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/3326</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>3326</v>
+      </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses hybrid solvent models for protein simulation, references specific force fields and molecular dynamics methods, and involves domain-specific scientific knowledge about explicit and implicit solvent representations.</t>
+          <t>The issue discusses the physical validity of sigma and epsilon parameters in molecular dynamics force fields, referencing water models and potential numerical instabilities, which involves domain-specific scientific knowledge.</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1474,16 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>3281</v>
+        <v>2509</v>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>How to reproduce standard nonbonded force as a custom nonbonded force?</t>
+          <t>OpenMM ForceField handling for SMIRNOFF impropers</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/3281</t>
+          <t>https://github.com/openmm/openmm/issues/2509</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1364,14 +1499,20 @@
       <c r="G22" s="3" t="inlineStr"/>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>question</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="n"/>
-      <c r="J22" s="2" t="n"/>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/2511</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>2511</v>
+      </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses reproducing a standard NonbondedForce using CustomNonbondedForce, involving mathematical formulas for Lennard-Jones and Coulomb interactions, reaction field, and dispersion corrections, which are domain-specific scientific knowledge.</t>
+          <t>The issue discusses SMIRNOFF improper torsions and molecular geometry, which are domain-specific concepts in computational chemistry and molecular mechanics.</t>
         </is>
       </c>
     </row>
@@ -1382,16 +1523,16 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>3348</v>
+        <v>2532</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>weird openmm warnings in miniconda3/lib/python3.8/site-packages/openmm/app/charmmparameterset.py</t>
+          <t>Discretizations of Langevin integrator</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/3348</t>
+          <t>https://github.com/openmm/openmm/issues/2532</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1406,11 +1547,17 @@
       </c>
       <c r="G23" s="3" t="inlineStr"/>
       <c r="H23" s="3" t="inlineStr"/>
-      <c r="I23" s="2" t="n"/>
-      <c r="J23" s="2" t="n"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/2561</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>2561</v>
+      </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses conflicting dihedral parameter definitions in CHARMM force fields and the VRORV integrator's temperature accuracy, both involving domain-specific scientific knowledge about molecular simulation.</t>
+          <t>The issue discusses numerical discretizations of Langevin integrators, symplectic methods, and thermodynamic quantities (temperature, kinetic energy) in molecular dynamics simulations, which are domain-specific scientific concepts.</t>
         </is>
       </c>
     </row>
@@ -1421,16 +1568,16 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>933</v>
+        <v>2722</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Custom Ewald force</t>
+          <t>GCC 8.5 produces large force differences (at least in ppc64le)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/933</t>
+          <t>https://github.com/openmm/openmm/issues/2722</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1445,11 +1592,17 @@
       </c>
       <c r="G24" s="3" t="inlineStr"/>
       <c r="H24" s="3" t="inlineStr"/>
-      <c r="I24" s="2" t="n"/>
-      <c r="J24" s="2" t="n"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/2781</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>2781</v>
+      </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses Particle Mesh Ewald (PME) implementation for custom forces, involving mathematical derivations, potential functions, convergence conditions, and recurrence relations, which are domain-specific scientific knowledge.</t>
+          <t>The issue concerns large force differences in molecular dynamics simulations due to compiler-specific behavior, involving numerical precision and platform-specific vector intrinsics, which are domain-specific scientific computing concepts.</t>
         </is>
       </c>
     </row>
@@ -1460,39 +1613,41 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>2593</v>
+        <v>2310</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Around 2 % overestimation for density under NPT simulation by OpenMM compared with other softwares</t>
+          <t>NonbondedForce Exceptions Change Energy and Force with Nonbonded Cutoff</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/2593</t>
+          <t>https://github.com/openmm/openmm/issues/2310</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>https://user-images.githubusercontent.com/379616/76448902-66a7b800-63cb-11ea-856d-b9fde323cd48.png</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
       <c r="H25" s="3" t="inlineStr"/>
-      <c r="I25" s="2" t="n"/>
-      <c r="J25" s="2" t="n"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/2318</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>2318</v>
+      </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses scientific behavior (density overestimation in MD simulations comparing barostat algorithms) and includes an embedded scientific plot of density vs time.</t>
+          <t>The issue discusses incorrect energy and force changes when adding nonbonded exceptions in a molecular dynamics simulation, involving domain-specific concepts like PME, cutoff methods, and force field parameters, which is a scientific numerical accuracy problem.</t>
         </is>
       </c>
     </row>
@@ -1503,40 +1658,41 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>2496</v>
+        <v>1931</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Discrepancy in results between OpenMM versions</t>
+          <t>Bug or operator error in adding atoms/virtual sites to topology/system "out of order"</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/2496</t>
+          <t>https://github.com/openmm/openmm/issues/1931</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>https://user-images.githubusercontent.com/28569164/70261519-9ad26380-1760-11ea-9127-2787652e6f33.png
-https://user-images.githubusercontent.com/28569164/70261543-a887e900-1760-11ea-87d7-2cf6758b9f26.png</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
       <c r="H26" s="3" t="inlineStr"/>
-      <c r="I26" s="2" t="n"/>
-      <c r="J26" s="2" t="n"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/1932</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>1932</v>
+      </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses discrepancies in molecular simulation results between OpenMM versions, involving force field parameters, constraints, and timestep settings, which are domain-specific scientific concepts, and includes scientific plots of RMSD data for protein folding analysis.</t>
+          <t>The issue deals with domain-specific molecular simulation concepts such as topology, residues, virtual sites, and atom ordering in the context of a scientific software library (OpenMM), reflecting scientific correctness concerns.</t>
         </is>
       </c>
     </row>
@@ -1547,16 +1703,16 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>1766</v>
+        <v>1677</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Drude particles have zero mass</t>
+          <t>Precision in CustomIntegrator kernels</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/1766</t>
+          <t>https://github.com/openmm/openmm/issues/1677</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1571,11 +1727,17 @@
       </c>
       <c r="G27" s="3" t="inlineStr"/>
       <c r="H27" s="3" t="inlineStr"/>
-      <c r="I27" s="2" t="n"/>
-      <c r="J27" s="2" t="n"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/1679</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>1679</v>
+      </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>The issue involves domain-specific scientific knowledge about Drude particles in force fields, masses, simulation stability, and integrator behavior, which are all concepts in computational chemistry and molecular dynamics.</t>
+          <t>The issue discusses numerical precision in molecular dynamics integrators (GHMC/velocity Verlet), which involves domain-specific scientific knowledge about algorithm implementation and numerical conditioning.</t>
         </is>
       </c>
     </row>
@@ -1586,16 +1748,16 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>1796</v>
+        <v>1476</v>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Features to support metadynamics</t>
+          <t>CPU and CUDA produce different energy values</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/1796</t>
+          <t>https://github.com/openmm/openmm/issues/1476</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1609,22 +1771,18 @@
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr"/>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>enhancement</t>
-        </is>
-      </c>
+      <c r="H28" s="3" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/pull/1837</t>
+          <t>https://github.com/openmm/openmm/pull/1495</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1837</v>
+        <v>1495</v>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses implementing metadynamics in OpenMM, involving collective variables, biasing potentials, and tabulated function derivatives, which are domain-specific concepts in molecular dynamics and computational chemistry.</t>
+          <t>The issue reports platform-dependent energy values in a molecular simulation library, involving domain-specific concepts like force field energy components, NaN from numerical operations, and numerical precision in scientific computing.</t>
         </is>
       </c>
     </row>
@@ -1635,16 +1793,16 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>1574</v>
+        <v>907</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>my new method to compute nonbonded force</t>
+          <t>Significant potential energy discrepancy on CPU platform for solvated system</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/1574</t>
+          <t>https://github.com/openmm/openmm/issues/907</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1659,11 +1817,17 @@
       </c>
       <c r="G29" s="3" t="inlineStr"/>
       <c r="H29" s="3" t="inlineStr"/>
-      <c r="I29" s="2" t="n"/>
-      <c r="J29" s="2" t="n"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/920</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>920</v>
+      </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses implementing a new method for computing nonbonded forces using a quantum mechanics database, which involves domain-specific scientific concepts like pair molecular configuration potential and spatial configuration, but does not include any scientific images.</t>
+          <t>The issue discusses potential energy discrepancies in molecular dynamics simulations involving PME and FFT implementations, which are domain-specific scientific concepts related to computational chemistry and numerical methods.</t>
         </is>
       </c>
     </row>
@@ -1674,16 +1838,16 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>2297</v>
+        <v>1486</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Question regarding CMMotionRemover()</t>
+          <t>Unstable simulation with GPU</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/2297</t>
+          <t>https://github.com/openmm/openmm/issues/1486</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1698,11 +1862,17 @@
       </c>
       <c r="G30" s="3" t="inlineStr"/>
       <c r="H30" s="3" t="inlineStr"/>
-      <c r="I30" s="2" t="n"/>
-      <c r="J30" s="2" t="n"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/1487</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>1487</v>
+      </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses the behavior of CMMotionRemover in molecular dynamics simulations, referencing theory documentation and internal implementation details, which involves domain-specific scientific knowledge.</t>
+          <t>The issue involves incorrect scientific behavior in molecular dynamics simulations (temperature instability due to a bug in PME handling with triclinic boxes), referencing domain-specific concepts like PME, cutoff, and periodic boundary conditions.</t>
         </is>
       </c>
     </row>
@@ -1713,16 +1883,16 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>1168</v>
+        <v>5241</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Extending ffxml to separate charge and Lennard-Jones parameter assignment</t>
+          <t>LocalEnergyMinimizer can fail to converge on large systems with constraints in single precision</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/1168</t>
+          <t>https://github.com/openmm/openmm/issues/5241</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1737,11 +1907,17 @@
       </c>
       <c r="G31" s="3" t="inlineStr"/>
       <c r="H31" s="3" t="inlineStr"/>
-      <c r="I31" s="2" t="n"/>
-      <c r="J31" s="2" t="n"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/5242</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>5242</v>
+      </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses modifications to force field XML format for molecular simulation, referencing AMBER force fields, Lennard-Jones parameters, and atom typing, which are domain-specific scientific concepts in computational chemistry.</t>
+          <t>The issue involves numerical precision, convergence checks, gradient magnitudes, and domain-specific scientific computation in molecular dynamics minimizers.</t>
         </is>
       </c>
     </row>
@@ -1752,16 +1928,16 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>1696</v>
+        <v>1237</v>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Implement pair-wise nonbonded interaction using CustomNonbondedForce</t>
+          <t>GPU LBFGS Minimizer</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/1696</t>
+          <t>https://github.com/openmm/openmm/issues/1237</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1775,12 +1951,22 @@
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr"/>
-      <c r="H32" s="3" t="inlineStr"/>
-      <c r="I32" s="2" t="n"/>
-      <c r="J32" s="2" t="n"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/5198</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>5198</v>
+      </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>The issue involves domain-specific scientific knowledge about molecular dynamics force fields, nonbonded interaction parameterization, and combining rules, including mathematical formulas for sigma and epsilon.</t>
+          <t>The issue discusses domain-specific scientific concepts such as GPU LBFGS minimization, constraint solvers, gradient projection for constrained optimization, and references GROMACS, all within the context of molecular dynamics simulation software.</t>
         </is>
       </c>
     </row>
@@ -1791,16 +1977,16 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>4042</v>
+        <v>3277</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Cost of CustomHbondForce</t>
+          <t xml:space="preserve">CustomNonbondedForce force long range correction does not converge </t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/4042</t>
+          <t>https://github.com/openmm/openmm/issues/3277</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1810,24 +1996,22 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>https://user-images.githubusercontent.com/24451788/233815448-3091d1f8-a5ee-4d92-9e6a-8b368fe2286f.png</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>question</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="n"/>
-      <c r="J33" s="2" t="n"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/3280</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>3280</v>
+      </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses the performance of CustomHbondForce with a mathematical formula involving cutoff functions, hydrogen bond geometry, and physical parameters, which is domain-specific scientific knowledge.</t>
+          <t>The issue discusses convergence of a long-range correction for a double exponential potential involving very small parameters, which is a domain-specific numerical issue in scientific computing.</t>
         </is>
       </c>
     </row>
@@ -1838,16 +2022,16 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>761</v>
+        <v>5116</v>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>We should report PME grid dimensions for AmoebaMultipoleForce</t>
+          <t>CustomBondForce with zero bonds gives a near but non-zero energy value with newer OpenMM &amp; CUDA versions</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/761</t>
+          <t>https://github.com/openmm/openmm/issues/5116</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1862,11 +2046,17 @@
       </c>
       <c r="G34" s="3" t="inlineStr"/>
       <c r="H34" s="3" t="inlineStr"/>
-      <c r="I34" s="2" t="n"/>
-      <c r="J34" s="2" t="n"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/5117</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>5117</v>
+      </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses PME grid dimensions, Ewald parameters, and algorithmic details for electrostatic calculations in molecular dynamics, which are domain-specific scientific concepts.</t>
+          <t>The issue involves numerical precision of potential energy calculations for a CustomBondForce in molecular dynamics, referencing physical concepts like force groups and neutralizing plasma self energy.</t>
         </is>
       </c>
     </row>
@@ -1877,16 +2067,16 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>1108</v>
+        <v>5134</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Energy discrepancies between platforms on large systems</t>
+          <t>Incorrect FFT results on version 2025.3 of Intel OpenCL for CPUs</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/1108</t>
+          <t>https://github.com/openmm/openmm/issues/5134</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1901,11 +2091,17 @@
       </c>
       <c r="G35" s="3" t="inlineStr"/>
       <c r="H35" s="3" t="inlineStr"/>
-      <c r="I35" s="2" t="n"/>
-      <c r="J35" s="2" t="n"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/5137</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>5137</v>
+      </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses energy discrepancies in molecular dynamics simulations using PME, involving Ewald error tolerance, grid sizes, and FFT platform differences, which are domain-specific numerical methods in computational chemistry.</t>
+          <t>The issue discusses incorrect FFT results in the PME algorithm, a numerical method for molecular dynamics electrostatics, involving mathematical concepts like prime factors and trig function accuracy, which is domain-specific scientific knowledge.</t>
         </is>
       </c>
     </row>
@@ -1916,21 +2112,21 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>350</v>
+        <v>5206</v>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Interface extension proposal: Addition of System.getNumVsites() and System.getNumDegreesOfFreedom()</t>
+          <t>Center of mass drift in small crystal simulation</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/350</t>
+          <t>https://github.com/openmm/openmm/issues/5206</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -1939,16 +2135,18 @@
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr"/>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>enhancement</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="n"/>
-      <c r="J36" s="2" t="n"/>
+      <c r="H36" s="3" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/5219</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>5219</v>
+      </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>The issue involves a formula for computing degrees of freedom in molecular dynamics systems, referencing virtual sites, constraints, and zero-mass particles, which are domain-specific scientific concepts.</t>
+          <t>The issue discusses center-of-mass drift in a molecular dynamics simulation with Lennard-Jones particles, referencing specific simulation methods (NVT ensemble, CMMotionRemover, LangevinIntegrator) and includes embedded plots of COM velocity and kinetic energy, combining domain-specific scientific knowledge with scientific images.</t>
         </is>
       </c>
     </row>
@@ -1959,16 +2157,16 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>3983</v>
+        <v>4793</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Particles in same position</t>
+          <t>"xtc_read(): precision mismatch" when creating a new reporter appending to an existing file</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/3983</t>
+          <t>https://github.com/openmm/openmm/issues/4793</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1982,16 +2180,18 @@
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr"/>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>question</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="n"/>
-      <c r="J37" s="2" t="n"/>
+      <c r="H37" s="3" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/4794</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>4794</v>
+      </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses custom non-bonded potentials with LaTeX equations, force calculations, and molecular dynamics simulation behavior, which are domain-specific scientific knowledge in computational chemistry.</t>
+          <t>The issue involves a precision mismatch in XTC file compression for molecular dynamics trajectories, which is a domain-specific scientific data handling issue related to coordinate compression algorithms.</t>
         </is>
       </c>
     </row>
@@ -2002,16 +2202,16 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>5270</v>
+        <v>4739</v>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Can vectors be used in CustomManyParticleForce</t>
+          <t>Loss of Zn2+ Ion Representation After Energy Minimization in PDB File</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/5270</t>
+          <t>https://github.com/openmm/openmm/issues/4739</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2026,11 +2226,17 @@
       </c>
       <c r="G38" s="3" t="inlineStr"/>
       <c r="H38" s="3" t="inlineStr"/>
-      <c r="I38" s="2" t="n"/>
-      <c r="J38" s="2" t="n"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/4748</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>4748</v>
+      </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>The issue involves domain-specific scientific knowledge about implementing molecular force field terms using vector math (cross product, dot product, angle calculations) and mathematical expressions for CH-pi interactions, which is firmly in the realm of computational chemistry.</t>
+          <t>The issue reports incorrect scientific behavior (loss of Zn2+ ion representation during energy minimization in molecular dynamics), referencing domain-specific concepts like PDB files, formal charges, and Modeller.</t>
         </is>
       </c>
     </row>
@@ -2041,16 +2247,16 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>1437</v>
+        <v>4080</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Space group symmetry</t>
+          <t>RPMDIntegrator is sometimes unreliable</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/1437</t>
+          <t>https://github.com/openmm/openmm/issues/4080</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2064,16 +2270,18 @@
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr"/>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>enhancement</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="n"/>
-      <c r="J39" s="2" t="n"/>
+      <c r="H39" s="3" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/4090</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>4090</v>
+      </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses implementing space group symmetry for molecular simulations, involving crystallographic concepts, mathematical transformations (rotation matrices, translation vectors), and references domain-specific knowledge about space groups and virtual sites.</t>
+          <t>The issue describes incorrect scientific behavior (energy non-conservation and position drift) due to a race condition in RPMDIntegrator, which falls under domain-specific numerical precision and physical correctness.</t>
         </is>
       </c>
     </row>
@@ -2084,16 +2292,16 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>4929</v>
+        <v>3620</v>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Time Synchronization of Forces &amp; Velocities from VerletIntegrator</t>
+          <t>A large potential energy difference between GROMACS-2021.4 and OpenMM-7.6.0</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/4929</t>
+          <t>https://github.com/openmm/openmm/issues/3620</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2107,12 +2315,23 @@
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="3" t="inlineStr"/>
-      <c r="I40" s="2" t="n"/>
-      <c r="J40" s="2" t="n"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>bug
+enhancement</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/3630</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>3630</v>
+      </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses the leapfrog algorithm, velocity correction using force and mass terms, and constraints, which are domain-specific scientific numerical methods in molecular dynamics.</t>
+          <t>The issue reports a discrepancy in potential energy between molecular dynamics engines, involving force field parameters, virtual sites, constraints, and water model details, which are domain-specific scientific concepts.</t>
         </is>
       </c>
     </row>
@@ -2123,16 +2342,16 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>5035</v>
+        <v>3447</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>SymmetrySite use case</t>
+          <t>Changing nonbonded parameters causing system to explode in openmm 7.5.0+</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/5035</t>
+          <t>https://github.com/openmm/openmm/issues/3447</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2147,11 +2366,17 @@
       </c>
       <c r="G41" s="3" t="inlineStr"/>
       <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="2" t="n"/>
-      <c r="J41" s="2" t="n"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/3460</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>3460</v>
+      </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses biasing protein orientation relative to a surface using SymmetrySite and angle forces, involving domain-specific concepts from molecular simulation and metadynamics.</t>
+          <t>The issue involves molecular dynamics simulation parameters, nonbonded force calculations, and system instability due to changes in physical parameters, which are domain-specific scientific concepts in computational chemistry.</t>
         </is>
       </c>
     </row>
@@ -2162,16 +2387,16 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>5025</v>
+        <v>3257</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Gromacs topology reader has two issues for systems with NBFIX</t>
+          <t>Incorrect non-bonded energy with CHARMM FF</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/5025</t>
+          <t>https://github.com/openmm/openmm/issues/3257</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2185,12 +2410,22 @@
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr"/>
-      <c r="H42" s="3" t="inlineStr"/>
-      <c r="I42" s="2" t="n"/>
-      <c r="J42" s="2" t="n"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/3324</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>3324</v>
+      </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>The issue describes incorrect mathematical formulas for Lennard-Jones interactions and parameter handling in Gromacs topology reader, involving domain-specific scientific knowledge about force fields and combinatorial rules.</t>
+          <t>The issue discusses incorrect non-bonded energy calculations due to missing NBFIX parameter implementation for 1-4 pairs and differences in electrostatic cutoff methods, which are domain-specific scientific concepts in molecular mechanics force fields.</t>
         </is>
       </c>
     </row>
@@ -2201,21 +2436,21 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>4592</v>
+        <v>3414</v>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Alchemical free energy calculation: How to remove the original NonbondedForce after add CustomNonbondedForce between two sets?</t>
+          <t>CUDA_ERROR_ILLEGAL_ADDRESS (700) when running gentle equilibration on a large system with many contexts</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/4592</t>
+          <t>https://github.com/openmm/openmm/issues/3414</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2225,16 +2460,25 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/user-attachments/assets/2d87635f-ce21-4c99-acc3-fc6e29a7d674
-https://github.com/user-attachments/assets/bd0e7746-4603-408d-8a87-7b827bc09833</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr"/>
-      <c r="I43" s="2" t="n"/>
-      <c r="J43" s="2" t="n"/>
+          <t>https://user-images.githubusercontent.com/35546250/149588135-8c044513-cccb-45a4-8f4c-ef9485256081.png</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/3428</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>3428</v>
+      </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses alchemical free energy calculations, nonbonded force handling, and PME methods, which are domain-specific scientific topics, and it includes images of free energy difference plots.</t>
+          <t>The issue includes a scientific image (screenshot of a gentle equilibration protocol) and is classified as a software bug rather than a mathematical or scientific correctness problem.</t>
         </is>
       </c>
     </row>
@@ -2245,16 +2489,16 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>5274</v>
+        <v>1920</v>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Feature request: Add atom-wise box rescaling option to MonteCarloAnisotropicBarostat and select epsilon value for finite difference equation</t>
+          <t>Context seems to be left in an inconsistent state after NaN</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/5274</t>
+          <t>https://github.com/openmm/openmm/issues/1920</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2268,22 +2512,18 @@
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr"/>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>enhancement</t>
-        </is>
-      </c>
+      <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/pull/5278</t>
+          <t>https://github.com/openmm/openmm/pull/1924</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>5278</v>
+        <v>1924</v>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses domain-specific scientific knowledge about barostat algorithms, finite difference virial calculations, and polymer network simulations, referencing numerical methods and physical constants.</t>
+          <t>The issue discusses recovering from NaN errors in molecular dynamics simulations, involving domain-specific concepts like LangevinIntegrator, Context reinitialization, and simulation state management.</t>
         </is>
       </c>
     </row>
@@ -2294,16 +2534,16 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>3740</v>
+        <v>2805</v>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Time evolution of pressure</t>
+          <t>CUDA platform breaks at 1.5M atoms</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/3740</t>
+          <t>https://github.com/openmm/openmm/issues/2805</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2319,21 +2559,20 @@
       <c r="G45" s="3" t="inlineStr"/>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>question
-faq</t>
+          <t>bug</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/pull/4881</t>
+          <t>https://github.com/openmm/openmm/pull/2806</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>4881</v>
+        <v>2806</v>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>The issue involves domain-specific scientific knowledge about computing pressure in molecular dynamics simulations, including discussion of the virial, finite-difference energy derivatives, and references to a physics paper.</t>
+          <t>The issue describes incorrect force calculations for large atom counts in a molecular dynamics library, involving domain-specific concepts like nonbonded forces, periodic boundary conditions, and numerical precision, making it a scientific software bug.</t>
         </is>
       </c>
     </row>
@@ -2344,16 +2583,16 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>4868</v>
+        <v>2817</v>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Question on the nonbonded cutoff implementation for implicit solvent models</t>
+          <t>OpenCL platform breaks on AMD GPUs</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/4868</t>
+          <t>https://github.com/openmm/openmm/issues/2817</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2368,11 +2607,17 @@
       </c>
       <c r="G46" s="3" t="inlineStr"/>
       <c r="H46" s="3" t="inlineStr"/>
-      <c r="I46" s="2" t="n"/>
-      <c r="J46" s="2" t="n"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/2829</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>2829</v>
+      </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses the mathematical implementation of nonbonded cutoffs in generalized Born implicit solvent models, including equations and physical constants, which is domain-specific scientific knowledge.</t>
+          <t>The issue involves numerical precision errors in force calculations for a molecular dynamics system, which is domain-specific scientific knowledge about physical simulation algorithms.</t>
         </is>
       </c>
     </row>
@@ -2383,16 +2628,16 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>4896</v>
+        <v>2145</v>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Questions Regarding LiGaMD2 Implementation: PME Electrostatics and Multiple CustomNonbondedForce Objects</t>
+          <t>Inconsistent AmoebaMultipoleForce energy between CPU vs CUDA platform (nan energy in CUDA)</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/4896</t>
+          <t>https://github.com/openmm/openmm/issues/2145</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2407,11 +2652,17 @@
       </c>
       <c r="G47" s="3" t="inlineStr"/>
       <c r="H47" s="3" t="inlineStr"/>
-      <c r="I47" s="2" t="n"/>
-      <c r="J47" s="2" t="n"/>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/2152</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>2152</v>
+      </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses domain-specific scientific concepts such as LiGaMD2, PME electrostatics, CustomNonbondedForce, and 12-6-4 Lennard-Jones potentials, requiring specialized chemistry and physics knowledge.</t>
+          <t>The issue discusses numerical precision problems in energy calculations due to zero polarizabilities, involving domain-specific scientific concepts like PME, force fields, and single vs double precision arithmetic.</t>
         </is>
       </c>
     </row>
@@ -2422,16 +2673,16 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>1435</v>
+        <v>2291</v>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Dissipative Particle Dynamics</t>
+          <t>Possible bug when computing distances in CustomCentroidBondForce</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/1435</t>
+          <t>https://github.com/openmm/openmm/issues/2291</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2445,22 +2696,18 @@
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr"/>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>enhancement</t>
-        </is>
-      </c>
+      <c r="H48" s="3" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/pull/4799</t>
+          <t>https://github.com/openmm/openmm/pull/2322</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>4799</v>
+        <v>2322</v>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses implementing Dissipative Particle Dynamics (DPD), a specific scientific simulation method, referencing a paper and involving domain concepts like hydrodynamics and coarse-grained simulations.</t>
+          <t>The issue reports a bug in the distance function of CustomCentroidBondForce yielding incorrect values for periodic systems, involving domain-specific knowledge of molecular simulation, periodic boundary conditions, and platform-specific numerical behavior.</t>
         </is>
       </c>
     </row>
@@ -2471,16 +2718,16 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>4635</v>
+        <v>1799</v>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Is there a way to output the pressure tensor to calculate the viscosity using the Green-Kubo(equilibrium state method) on Openmm? </t>
+          <t>Is there a way to make PME energies on the CPU deterministic?</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/4635</t>
+          <t>https://github.com/openmm/openmm/issues/1799</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2494,12 +2741,22 @@
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr"/>
-      <c r="H49" s="3" t="inlineStr"/>
-      <c r="I49" s="2" t="n"/>
-      <c r="J49" s="2" t="n"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/1802</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>1802</v>
+      </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses equilibrium molecular dynamics methods for computing viscosity via the Green-Kubo relation and pressure tensor, which involves domain-specific scientific knowledge in statistical mechanics.</t>
+          <t>The issue discusses deterministic PME energy calculations on CPU, involving floating point accumulation order and single precision grid computations, which are domain-specific numerical methods in computational chemistry.</t>
         </is>
       </c>
     </row>
@@ -2510,35 +2767,46 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>4848</v>
+        <v>2254</v>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Unexpectedly High Temperature in Brownian Integrator</t>
+          <t xml:space="preserve">Precision bug in openmm 7.3.0? </t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/4848</t>
+          <t>https://github.com/openmm/openmm/issues/2254</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G50" s="3" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>https://user-images.githubusercontent.com/3977731/52308068-5de3e780-296a-11e9-9503-16d09b683f28.png
+https://user-images.githubusercontent.com/3656088/52311687-d2705380-2975-11e9-84ce-0f51e42ba3fc.png</t>
+        </is>
+      </c>
       <c r="H50" s="3" t="inlineStr"/>
-      <c r="I50" s="2" t="n"/>
-      <c r="J50" s="2" t="n"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/2257</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>2257</v>
+      </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>The issue involves domain-specific knowledge about molecular dynamics integrators and temperature computation in Brownian dynamics, which is a scientific concept.</t>
+          <t>The issue discusses numerical precision errors in molecular dynamics simulations involving charge perturbations and NCMC protocols, and includes scientific plots of cumulative work versus step, qualifying it for both Type 1 (scientific/math content) and Type 2 (scientific images).</t>
         </is>
       </c>
     </row>
@@ -2549,35 +2817,45 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>3856</v>
+        <v>1666</v>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Cannot use openMM to run em on a solavted system from Gromacs topology with HBond constrain</t>
+          <t>NaN issue</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/3856</t>
+          <t>https://github.com/openmm/openmm/issues/1666</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>https://cloud.githubusercontent.com/assets/19587267/20185625/140ef63a-a76d-11e6-9864-316234a4a2e4.png</t>
+        </is>
+      </c>
       <c r="H51" s="3" t="inlineStr"/>
-      <c r="I51" s="2" t="n"/>
-      <c r="J51" s="2" t="n"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/1682</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>1682</v>
+      </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses molecular dynamics constraints, CCMA and LINCS algorithms, and over-constrained molecular systems, which are domain-specific scientific concepts in computational chemistry.</t>
+          <t>Issue involves domain-specific knowledge of molecular dynamics (MD) simulations, forcefields, integrators, and NaN errors in particle coordinates, and includes an image (table) showing simulation results.</t>
         </is>
       </c>
     </row>
@@ -2588,16 +2866,16 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>4471</v>
+        <v>4435</v>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Free energy calculation for Protein-protein binding with Openmm</t>
+          <t>Use LF-Middle for LangevinIntegrator</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/4471</t>
+          <t>https://github.com/openmm/openmm/issues/4435</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2613,14 +2891,20 @@
       <c r="G52" s="3" t="inlineStr"/>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>question</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="n"/>
-      <c r="J52" s="2" t="n"/>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/4440</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>4440</v>
+      </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses protein-protein binding free energy calculations, referencing alchemical methods and convergence challenges, which are domain-specific scientific concepts in computational chemistry and thermodynamics.</t>
+          <t>The issue proposes switching the Langevin integrator algorithm to a more accurate discretization (LF-Middle), which involves domain-specific knowledge about numerical integration methods in molecular dynamics.</t>
         </is>
       </c>
     </row>
@@ -2631,16 +2915,16 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>5038</v>
+        <v>2039</v>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Equations in API documentation</t>
+          <t>Disulfide bonds are broken in CHARMM36</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/5038</t>
+          <t>https://github.com/openmm/openmm/issues/2039</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2654,872 +2938,1022 @@
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr"/>
-      <c r="H53" s="3" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/2040</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>2040</v>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses a critical force field error involving disulfide bond handling in CHARMM36, referencing patches and residue topology, which is domain-specific scientific knowledge about molecular dynamics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>2814</v>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>A small number of constraints have extreme impact of CustomIntegrator performance</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/2814</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/2818</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>2818</v>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses performance of CustomIntegrator with CCMA constraints in free energy calculations, referencing specific algorithms (CCMA, SHAKE, RATTLE, SETTLE) and domain concepts like alchemical calculations and constraint geometry, which qualifies as domain-specific scientific knowledge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Is it possible to distinguish between vector components in CustomIntegrator?</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/2050</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/2057</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>2057</v>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses implementing Lorentz forces via cross products in a physics simulation, involving domain-specific physics concepts and mathematical operations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>1527</v>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Stuck at creating system after the fastmatching update</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/1527</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>https://cloud.githubusercontent.com/assets/3656088/16462292/8feb26bc-3dfe-11e6-857a-09c69638604d.png</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/1528</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>1528</v>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves domain-specific graph matching algorithm for force field assignment in molecular simulations (type 1) and includes a chemical diagram of graphite (type 2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>1194</v>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Automatic neutralisation of system</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/1194</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/1235</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>1235</v>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses neutralization of molecular systems, counter ions, PME convergence, and reaction field approximation, which are domain-specific scientific concepts in computational chemistry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>4863</v>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Constant potential simulations</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4863</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/4870</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>4870</v>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses implementing constant potential simulations with mathematical formulations (Thomas-Fermi model, equations) and domain-specific scientific concepts (electrochemistry, conductive electrodes, charge constraints).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>1099</v>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Problem with constraint triangles that are not water</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/1099</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/1100</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>1100</v>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses molecular dynamics constraint algorithms (SETTLE vs CCMA) and their applicability to specific molecular geometries, involving domain-specific scientific knowledge about force fields and numerical methods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>3507</v>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>truncated octahedron from LEaP</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3507</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>https://user-images.githubusercontent.com/8700070/157335351-a7b9252b-680f-4d3c-8330-3326e26bd471.png</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/3521</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>3521</v>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses domain-specific scientific knowledge about truncated octahedron solvent boxes, triclinic box vectors, and periodic boundary conditions in molecular dynamics simulations, and includes a scientific image showing the molecular system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>1699</v>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Context.setVelocitiesToTemperature() produces  large or`nan` velocities</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/1699</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr"/>
+      <c r="H61" s="3" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/1711</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>1711</v>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>Issue describes incorrect physical behavior (large/NaN velocities) from velocity initialization in molecular dynamics, involving constraints and temperature, which is domain-specific scientific knowledge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Degree-to-radian conversion in AMOEBA with constraints.</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/148</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr"/>
+      <c r="H62" s="3" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/826</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>826</v>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses a unit conversion (degrees vs radians) for angle parameters in molecular dynamics force fields, which involves domain-specific scientific knowledge about physical constants and simulation correctness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>1790</v>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Strange problems with CustomCompoundBondForce / Continuous3DFunction</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/1790</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr"/>
+      <c r="H63" s="3" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/1806</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>1806</v>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses custom force fields for molecular simulation with electron density maps, involving domain-specific scientific concepts and is accompanied by an image showing force-related atom visualization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>4247</v>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Energy parameter derivatives calculated incorrectly on CUDA under certain conditions</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4247</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr"/>
+      <c r="H64" s="3" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/4249</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>4249</v>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>The issue describes incorrect computation of energy parameter derivatives in a molecular dynamics context, involving custom nonbonded forces and interaction groups, which is a domain-specific scientific calculation bug.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>1649</v>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Bug in getPotentialEnergy() on CUDA platform?</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/1649</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr"/>
+      <c r="H65" s="3" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/1652</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>1652</v>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>The issue reports incorrect scientific behavior (NaN potential energy) on the CUDA platform due to a pathological case in AMOEBA polarizable force field covalent maps, involving domain-specific molecular mechanics knowledge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>3833</v>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>large differences in force evaluation on `CPU` vs `CUDA` in omm7.7.0 with `CustomNonbondedForce` and `CustomBondForce``</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3833</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr"/>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/3834</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>3834</v>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves incorrect force evaluation due to a mathematical problem (0^0 = nan) in derivative calculations of softcore potentials, which is a domain-specific numerical issue in molecular simulation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>3111</v>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Particle at the origin causes large force in a spherical-container potential</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3111</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr"/>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/3240</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>3240</v>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>The issue describes a numerical singularity in a molecular dynamics potential due to the derivative of the max function at the origin, involving domain-specific force field mathematics and the analytical derivative implementation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>3113</v>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Adding fixed number of solvent molecules leads to NaNs for certain systems</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3113</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr"/>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>bug
+medium priority
+low effort</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/3151</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>3151</v>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves numerical artifacts (NaNs) arising from solvation parameters in molecular dynamics simulations, which requires domain-specific knowledge of force fields, energy minimization, and solvent placement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>5300</v>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Incorrect `AmoebaMultipoleForce::ForceInfo` can break `reorderAtoms()` and produce wrong CUDA results</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/5300</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr"/>
+      <c r="H69" s="3" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/5302</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>5302</v>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves domain-specific scientific concepts from molecular dynamics (covalent bonds, molecular groups, exclusion tiles, force fields) and describes incorrect simulation results due to incomplete connectivity information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>2521</v>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Potential energy inconsistency in CPU platform</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/2521</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr"/>
+      <c r="H70" s="3" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/2544</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>2544</v>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves domain-specific scientific knowledge about molecular dynamics, force fields, and energy calculations, specifically a potential energy inconsistency in a CustomNonbondedForce due to mismatched nonbonded methods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>5150</v>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Gromacs Topology File does not yet support `virtual_site3` with `funct=3`</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/5150</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr"/>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/5155</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>5155</v>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses adding support for a Gromacs virtual_site3 function type in OpenMM, which involves molecular dynamics domain knowledge, and includes a screenshot of a molecular structure from VMD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>4771</v>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Zero boxes in CHARMM simulations</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4771</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr"/>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/4777</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>4777</v>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses incorrect handling of periodic box vectors in CHARMM simulations, which is a domain-specific scientific problem in molecular dynamics simulation software.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>4184</v>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>unusual water behaviour with gromacs files</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4184</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/assets/60986121/bb0a62ec-c282-4338-aa43-48dbcf7ccf61</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/4188</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>4188</v>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves domain-specific scientific knowledge about water model bond definitions in molecular simulation, and includes an image showing broken water molecules from the simulation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>4521</v>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic boundary conditions with DrudeForce </t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4521</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/assets/55751764/15364d77-a88d-4c9f-b622-efd6efc418b2</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
         <is>
           <t>enhancement
 documentation</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n"/>
-      <c r="J53" s="2" t="n"/>
-      <c r="K53" s="3" t="inlineStr">
-        <is>
-          <t>The issue discusses adding equations and mathematical notation for force field energy terms to the API documentation, which involves domain-specific scientific knowledge and symbolic formulas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>openmm/openmm</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="n">
-        <v>4643</v>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>Interaction energy with energy minimization</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/openmm/openmm/issues/4643</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="inlineStr"/>
-      <c r="H54" s="3" t="inlineStr"/>
-      <c r="I54" s="2" t="n"/>
-      <c r="J54" s="2" t="n"/>
-      <c r="K54" s="3" t="inlineStr">
-        <is>
-          <t>The issue involves domain-specific scientific knowledge about molecular dynamics force fields, energy minimization, and interaction energy computation in protein-ligand complexes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>openmm/openmm</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="n">
-        <v>4674</v>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>Accessing Interatomic Distance in CustomExternalForce</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/openmm/openmm/issues/4674</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr"/>
-      <c r="H55" s="3" t="inlineStr"/>
-      <c r="I55" s="2" t="n"/>
-      <c r="J55" s="2" t="n"/>
-      <c r="K55" s="3" t="inlineStr">
-        <is>
-          <t>The issue involves implementing a DLVO potential using mathematical equations for interatomic distances, which is a domain-specific scientific concept.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>openmm/openmm</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="n">
-        <v>4809</v>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>Modifying forces on-the-fly</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/openmm/openmm/issues/4809</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G56" s="3" t="inlineStr"/>
-      <c r="H56" s="3" t="inlineStr"/>
-      <c r="I56" s="2" t="n"/>
-      <c r="J56" s="2" t="n"/>
-      <c r="K56" s="3" t="inlineStr">
-        <is>
-          <t>The issue discusses modifying forces in molecular dynamics simulations, referencing physical constants (Boltzmann constant, gas constant), integrators, and ML/MM force evaluation, which involves domain-specific scientific knowledge of molecular simulation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>openmm/openmm</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="n">
-        <v>4581</v>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>Applying flat-bottom potential restraints</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/openmm/openmm/issues/4581</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>1,2</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/openmm/openmm/assets/103068766/0a2a80a8-cd2e-496c-a940-d77a973297c8
-https://github.com/user-attachments/assets/d912fce6-6761-405c-8bd7-0898abdfde75
-https://github.com/user-attachments/as Can you explain what I should be seeing in the animation, and in what way it doesn't work?  Does the width of the black rectangle represent the restrained area (4.8 nm
-https://github.com/user-attachments/assets/73ba3bfc-9740-4b7e-a835-731b22ae05d9
-https://github.com/user-attachments/assets/e5f57947-c843-4b7a-b327-c2b1df652222</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr"/>
-      <c r="I57" s="2" t="n"/>
-      <c r="J57" s="2" t="n"/>
-      <c r="K57" s="3" t="inlineStr">
-        <is>
-          <t>The issue involves applying flat-bottom potential restraints with mathematical equations and physical constants, and includes scientific images showing the resulting ion behavior.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>openmm/openmm</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="n">
-        <v>4359</v>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>Trajectory reporters not writing the box dimensions</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/openmm/openmm/issues/4359</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="inlineStr"/>
-      <c r="H58" s="3" t="inlineStr"/>
-      <c r="I58" s="2" t="n"/>
-      <c r="J58" s="2" t="n"/>
-      <c r="K58" s="3" t="inlineStr">
-        <is>
-          <t>The issue discusses periodic boundary conditions, topology properties, and system settings in molecular dynamics simulations, which are domain-specific scientific concepts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>openmm/openmm</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="n">
-        <v>4387</v>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>Usage of NonBondedForce.setIncludeDirectSpace(False)</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/openmm/openmm/issues/4387</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="inlineStr"/>
-      <c r="H59" s="3" t="inlineStr"/>
-      <c r="I59" s="2" t="n"/>
-      <c r="J59" s="2" t="n"/>
-      <c r="K59" s="3" t="inlineStr">
-        <is>
-          <t>The issue involves domain-specific scientific knowledge about PME electrostatics, direct/reciprocal space contributions, and exception handling in molecular dynamics force calculations.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>openmm/openmm</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="n">
-        <v>4296</v>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>Custom virtual sites</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/openmm/openmm/issues/4296</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="inlineStr"/>
-      <c r="H60" s="3" t="inlineStr"/>
-      <c r="I60" s="2" t="n"/>
-      <c r="J60" s="2" t="n"/>
-      <c r="K60" s="3" t="inlineStr">
-        <is>
-          <t>The issue discusses custom virtual site equations involving bond vectors and deviation from equilibrium bond lengths, which are domain-specific mathematical formulations related to molecular dynamics.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>openmm/openmm</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="n">
-        <v>4303</v>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>DrudeForce issues/questions</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/openmm/openmm/issues/4303</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr"/>
-      <c r="H61" s="3" t="inlineStr"/>
-      <c r="I61" s="2" t="n"/>
-      <c r="J61" s="2" t="n"/>
-      <c r="K61" s="3" t="inlineStr">
-        <is>
-          <t>The issue discusses scientific domain concepts (Drude polarizable force field, Thole damping, polarization energy comparison between OpenMM and GROMACS) and numerical precision in molecular simulations.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>openmm/openmm</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="n">
-        <v>3066</v>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>external electric field</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/openmm/openmm/issues/3066</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>1,2</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="inlineStr">
-        <is>
-          <t>https://user-images.githubusercontent.com/28215638/111356721-99ae1700-86c3-11eb-8c0d-658ec6bb9d75.png</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>question</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="n"/>
-      <c r="J62" s="2" t="n"/>
-      <c r="K62" s="3" t="inlineStr">
-        <is>
-          <t>The issue discusses simulating an external electric field on a protein, involving force field charges and domain-specific chemical knowledge, and includes an image of a table of amino acid charges.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>openmm/openmm</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="n">
-        <v>4414</v>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>Adding free ions in topology</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/openmm/openmm/issues/4414</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr"/>
-      <c r="H63" s="3" t="inlineStr"/>
-      <c r="I63" s="2" t="n"/>
-      <c r="J63" s="2" t="n"/>
-      <c r="K63" s="3" t="inlineStr">
-        <is>
-          <t>The issue involves scientific domain knowledge such as molecular dynamics, RNA folding, divalent ions, potential functions, tabulated functions, and unit conversions (nm vs angstrom), with explicit references to equations and domain-specific scientific concepts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>openmm/openmm</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="n">
-        <v>4262</v>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>Units of virtual site weights</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/openmm/openmm/issues/4262</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="inlineStr"/>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>documentation</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="n"/>
-      <c r="J64" s="2" t="n"/>
-      <c r="K64" s="3" t="inlineStr">
-        <is>
-          <t>The issue discusses mathematical equations and physical units (distance squared, inverse distance) for virtual site weights in molecular dynamics, which is domain-specific scientific knowledge.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>openmm/openmm</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="n">
-        <v>4228</v>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>Plugin for xtb</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/openmm/openmm/issues/4228</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G65" s="3" t="inlineStr"/>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>enhancement</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="n"/>
-      <c r="J65" s="2" t="n"/>
-      <c r="K65" s="3" t="inlineStr">
-        <is>
-          <t>The issue discusses integrating a plugin for the xtb semiempirical quantum chemistry package, referencing domain-specific concepts like GFN-FF force fields, GFN2-xTB methods, and QM/MM embedding, which qualifies as Type 1 scientific domain knowledge.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>openmm/openmm</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="n">
-        <v>4132</v>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>Equations for calculating non-bonded energies</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/openmm/openmm/issues/4132</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr"/>
-      <c r="H66" s="3" t="inlineStr"/>
-      <c r="I66" s="2" t="n"/>
-      <c r="J66" s="2" t="n"/>
-      <c r="K66" s="3" t="inlineStr">
-        <is>
-          <t>The issue involves mathematical equations for non-bonded energy calculations (Coulomb and Lennard-Jones) and combining rules, which are domain-specific scientific knowledge.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>openmm/openmm</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="n">
-        <v>4222</v>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>How is surface tension defined for MonteCarloMembraneBarostat?</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/openmm/openmm/issues/4222</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr"/>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="n"/>
-      <c r="J67" s="2" t="n"/>
-      <c r="K67" s="3" t="inlineStr">
-        <is>
-          <t>The issue involves a discussion of the mathematical definition of surface tension in membrane simulations, including a LaTeX equation and domain-specific thermodynamic concepts, and reports an error related to that definition, making it a Type 1 scientific issue.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>openmm/openmm</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="n">
-        <v>4100</v>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>Nose Hoover Friction Coefficient/Debugging the Step Function</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/openmm/openmm/issues/4100</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G68" s="3" t="inlineStr"/>
-      <c r="H68" s="3" t="inlineStr"/>
-      <c r="I68" s="2" t="n"/>
-      <c r="J68" s="2" t="n"/>
-      <c r="K68" s="3" t="inlineStr">
-        <is>
-          <t>The issue involves mathematical formulations from Hoover's paper, discusses the friction coefficient and its derivative in the Nose-Hoover integrator, and references domain-specific scientific knowledge about thermostat algorithms.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>openmm/openmm</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="n">
-        <v>4016</v>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>Calculation of the non-polar part of the GBSA implicit solvents</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/openmm/openmm/issues/4016</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="inlineStr"/>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>question</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="n"/>
-      <c r="J69" s="2" t="n"/>
-      <c r="K69" s="3" t="inlineStr">
-        <is>
-          <t>The issue discusses the mathematical formula for the non-polar part of GBSA solvation free energy, compares it to a published equation, and asks about correctness of the implementation, which involves domain-specific scientific knowledge.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>openmm/openmm</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="n">
-        <v>4244</v>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>how to implement gromacs virtual site type 4fdn using LocalCoordinatesSite?</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/openmm/openmm/issues/4244</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G70" s="3" t="inlineStr"/>
-      <c r="H70" s="3" t="inlineStr"/>
-      <c r="I70" s="2" t="n"/>
-      <c r="J70" s="2" t="n"/>
-      <c r="K70" s="3" t="inlineStr">
-        <is>
-          <t>Issue discusses implementing a Gromacs virtual site type using OpenMM's LocalCoordinatesSite, referencing mathematical definitions and molecular geometry concepts (lone pairs, Trimethylamine), which involves domain-specific scientific knowledge.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>openmm/openmm</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="n">
-        <v>3858</v>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>Calculation of reweighting factor in metadynamics (Tiwary, Parrinello, J. Phys. Chem. B 2015, 119, 3, 736–742)</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/openmm/openmm/issues/3858</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="inlineStr"/>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>question</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="n"/>
-      <c r="J71" s="2" t="n"/>
-      <c r="K71" s="3" t="inlineStr">
-        <is>
-          <t>The issue discusses implementing a time-dependent reweighting factor in metadynamics, referencing a specific scientific paper and involving domain-specific concepts such as bias potential, free energy surface, and reweighting algorithm.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>openmm/openmm</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="n">
-        <v>3889</v>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>FP64 emulation for Metal plugin</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/openmm/openmm/issues/3889</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G72" s="3" t="inlineStr"/>
-      <c r="H72" s="3" t="inlineStr"/>
-      <c r="I72" s="2" t="n"/>
-      <c r="J72" s="2" t="n"/>
-      <c r="K72" s="3" t="inlineStr">
-        <is>
-          <t>The issue discusses numerical precision improvements through Kahan summation and FP64 emulation in a scientific molecular dynamics library, involving domain-specific numerical methods and floating-point accuracy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>openmm/openmm</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="n">
-        <v>3777</v>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>Efficiency of nonbonded custom force</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/openmm/openmm/issues/3777</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G73" s="3" t="inlineStr"/>
-      <c r="H73" s="3" t="inlineStr"/>
-      <c r="I73" s="2" t="n"/>
-      <c r="J73" s="2" t="n"/>
-      <c r="K73" s="3" t="inlineStr">
-        <is>
-          <t>The issue discusses implementing a nonbonded custom force with Lennard-Jones-type energy expressions, combining rules, and tabulated functions, which involves domain-specific scientific knowledge in molecular simulation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>openmm/openmm</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="n">
-        <v>3744</v>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>Substituting energy value from external calculation into openmm for coordinates generation</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/openmm/openmm/issues/3744</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G74" s="3" t="inlineStr"/>
-      <c r="H74" s="3" t="inlineStr"/>
-      <c r="I74" s="2" t="n"/>
-      <c r="J74" s="2" t="n"/>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/4523</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>4523</v>
+      </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses substituting single point energies from external QM software into OpenMM for force computation and dynamics, involving domain concepts like energy derivatives, ab initio molecular dynamics, and force fields.</t>
+          <t>The issue contains a scientific image (diagram of Drude particles with periodic boundary conditions) which is domain-specific visual content, qualifying it as Type 2.</t>
         </is>
       </c>
     </row>
@@ -3530,21 +3964,21 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>3611</v>
+        <v>4117</v>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Handling mixed periodic/non-periodic CVs in Metadynamics</t>
+          <t>Problem with jumping molecules</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/3611</t>
+          <t>https://github.com/openmm/openmm/issues/4117</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -3554,11 +3988,17 @@
       </c>
       <c r="G75" s="3" t="inlineStr"/>
       <c r="H75" s="3" t="inlineStr"/>
-      <c r="I75" s="2" t="n"/>
-      <c r="J75" s="2" t="n"/>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/4119</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>4119</v>
+      </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses handling periodic and non-periodic collective variables (CVs) in metadynamics, which involves domain-specific knowledge of molecular dynamics, dihedral angles, and bias functional forms.</t>
+          <t>Issue describes incorrect molecular dynamics simulation behavior (jumping molecules) in a water system with barostat, which involves domain-specific physics and chemistry, and includes movies showing molecular trajectories as scientific visualizations.</t>
         </is>
       </c>
     </row>
@@ -3569,16 +4009,16 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>147</v>
+        <v>4085</v>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Reporting the pressure</t>
+          <t>`Modeller.addSolvent`'s `numAdded` option forces the output periodic box to be cubic</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/147</t>
+          <t>https://github.com/openmm/openmm/issues/4085</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -3593,11 +4033,17 @@
       </c>
       <c r="G76" s="3" t="inlineStr"/>
       <c r="H76" s="3" t="inlineStr"/>
-      <c r="I76" s="2" t="n"/>
-      <c r="J76" s="2" t="n"/>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/4086</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>4086</v>
+      </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses computing pressure via the virial equation in molecular dynamics simulations, involving domain-specific concepts like barostats, PBCs, and AMOEBA force fields.</t>
+          <t>The issue involves domain-specific scientific knowledge about periodic box shapes (cube, dodecahedron, octahedron) in molecular simulations, and reports incorrect scientific behavior when a predetermined number of solvent molecules is added with a non-cubic box shape.</t>
         </is>
       </c>
     </row>
@@ -3608,16 +4054,16 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>3437</v>
+        <v>3767</v>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>customGBforce issues</t>
+          <t>Incorrect behavior of context.reinitialize(preserveState=True)</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/3437</t>
+          <t>https://github.com/openmm/openmm/issues/3767</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -3632,11 +4078,17 @@
       </c>
       <c r="G77" s="3" t="inlineStr"/>
       <c r="H77" s="3" t="inlineStr"/>
-      <c r="I77" s="2" t="n"/>
-      <c r="J77" s="2" t="n"/>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/3771</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>3771</v>
+      </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>The issue involves mathematical formulas for implicit membrane models (Imem, Imol, B), domain-specific concepts like Generalized Born (GB) forces, and discussion of physical behavior of charged particles in a membrane, which are all scientific and mathematical in nature.</t>
+          <t>The issue involves incorrect potential energy calculations due to atom reordering in OpenMM's CUDA platform, which is a domain-specific scientific software for molecular dynamics, and the bug affects the correctness of forces and energies.</t>
         </is>
       </c>
     </row>
@@ -3647,16 +4099,16 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>2898</v>
+        <v>3499</v>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Potential enhancement: Add option to MonteCarloBarostat to not wrap coordinates into box</t>
+          <t>TIP4P waters not compatible with AllBonds?</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/2898</t>
+          <t>https://github.com/openmm/openmm/issues/3499</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -3670,22 +4122,18 @@
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr"/>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>enhancement</t>
-        </is>
-      </c>
+      <c r="H78" s="3" t="inlineStr"/>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/pull/3260</t>
+          <t>https://github.com/openmm/openmm/pull/3506</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>3260</v>
+        <v>3506</v>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses molecular simulation algorithms, Monte Carlo barostat behavior, and molecular re-imaging techniques, all domain-specific scientific knowledge.</t>
+          <t>The issue discusses the incompatibility of TIP4P water model virtual sites with the AllBonds constraint in OpenMM, involving domain-specific knowledge about force field parameter files, extra particles, and constraint handling in molecular dynamics simulations.</t>
         </is>
       </c>
     </row>
@@ -3696,39 +4144,45 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>3782</v>
+        <v>3487</v>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>How to warm up a system followed by NVT/NPT equilibration while slowly removing backbone constraints</t>
+          <t>Switching the order of forcefield.xml files causes simulation to crash</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/3782</t>
+          <t>https://github.com/openmm/openmm/issues/3487</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G79" s="3" t="inlineStr">
-        <is>
-          <t>https://user-images.githubusercontent.com/79198385/191270450-0dc3f3e9-3592-4eca-af7a-644f066bcfbb.png</t>
-        </is>
-      </c>
-      <c r="H79" s="3" t="inlineStr"/>
-      <c r="I79" s="2" t="n"/>
-      <c r="J79" s="2" t="n"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr"/>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/3493</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>3493</v>
+      </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses molecular dynamics simulation protocols (NVT/NPT equilibration, backbone restraints) which are domain-specific scientific knowledge, and includes a screenshot of a protein-solvent system as a scientific image.</t>
+          <t>The issue involves incorrect assignment of force field parameters (stretch-bend) leading to simulation crashes, which is a domain-specific scientific problem in molecular dynamics.</t>
         </is>
       </c>
     </row>
@@ -3739,16 +4193,16 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>3426</v>
+        <v>3692</v>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>NonbondedForce cutoff</t>
+          <t>Water clashes with protein for octahedral boxes not centred in unit cell</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/3426</t>
+          <t>https://github.com/openmm/openmm/issues/3692</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -3763,11 +4217,17 @@
       </c>
       <c r="G80" s="3" t="inlineStr"/>
       <c r="H80" s="3" t="inlineStr"/>
-      <c r="I80" s="2" t="n"/>
-      <c r="J80" s="2" t="n"/>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/3696</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>3696</v>
+      </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses domain-specific scientific knowledge about nonbonded interactions, cutoff distances, PME electrostatics, and reaction field approximation in a molecular simulation context.</t>
+          <t>The issue discusses incorrect water placement in octahedral solvent boxes due to an algorithmic flaw in clash detection, which involves domain-specific knowledge about molecular geometry, periodic boundary conditions, and van der Waals radii.</t>
         </is>
       </c>
     </row>
@@ -3778,39 +4238,41 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>3292</v>
+        <v>5234</v>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>[Question] How to create a 2D potential in OpenMM and sample it with Langevin integrator</t>
+          <t>Spurious constraint application from residue templates</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/3292</t>
+          <t>https://github.com/openmm/openmm/issues/5234</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G81" s="3" t="inlineStr">
-        <is>
-          <t>https://user-images.githubusercontent.com/37775482/137891909-c8774402-ea9c-4404-b150-3219e049c123.png</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr"/>
       <c r="H81" s="3" t="inlineStr"/>
-      <c r="I81" s="2" t="n"/>
-      <c r="J81" s="2" t="n"/>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/5236</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>5236</v>
+      </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>The issue involves a mathematical potential energy function (domain-specific scientific knowledge) and includes an image of the equation, qualifying it as both type 1 and type 2.</t>
+          <t>The issue reports a bug in constraint application from residue templates in OpenMM, a molecular dynamics library, involving domain-specific knowledge of force fields, molecular topology, and residue templates.</t>
         </is>
       </c>
     </row>
@@ -3821,16 +4283,16 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>3282</v>
+        <v>5169</v>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>the theory and mathematical equation behind getPotentialEnergy()</t>
+          <t>issue with a phosphorylated Serine</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/3282</t>
+          <t>https://github.com/openmm/openmm/issues/5169</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -3844,12 +4306,22 @@
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr"/>
-      <c r="H82" s="3" t="inlineStr"/>
-      <c r="I82" s="2" t="n"/>
-      <c r="J82" s="2" t="n"/>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/5179</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>5179</v>
+      </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>The issue asks for the theory and mathematical equation behind getPotentialEnergy(), which involves molecular force field energy calculations, a domain-specific scientific concept.</t>
+          <t>The issue involves domain-specific scientific knowledge about PDB file handling and molecular bonds for a phosphorylated serine residue, describing incorrect scientific behavior (missing CONECT bond).</t>
         </is>
       </c>
     </row>
@@ -3860,16 +4332,16 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>3031</v>
+        <v>4534</v>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Is it Possible to Calculate just Nonbonded energy for saving time?</t>
+          <t>problem [ virtural_site3 ] from GROMACS files</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/3031</t>
+          <t>https://github.com/openmm/openmm/issues/4534</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -3885,14 +4357,20 @@
       <c r="G83" s="3" t="inlineStr"/>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>question</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="n"/>
-      <c r="J83" s="2" t="n"/>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/4536</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>4536</v>
+      </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses calculating only nonbonded energy in molecular dynamics simulations, which involves domain-specific knowledge about force fields, energy groups, and interaction algorithms.</t>
+          <t>The issue reports incorrect parsing of virtual_sites3 from GROMACS topology files for the Martini forcefield, which involves domain-specific knowledge about molecular simulation and virtual site definitions in computational chemistry.</t>
         </is>
       </c>
     </row>
@@ -3903,43 +4381,41 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>3137</v>
+        <v>4759</v>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Question about the SHAKE implementation</t>
+          <t>Absinth XML file: Missing energies from C-terminal residues</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/3137</t>
+          <t>https://github.com/openmm/openmm/issues/4759</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G84" s="3" t="inlineStr">
-        <is>
-          <t>https://user-images.githubusercontent.com/72212636/120674974-a3dde700-c462-11eb-8993-6c068bcee183.png</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>question</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="n"/>
-      <c r="J84" s="2" t="n"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr"/>
+      <c r="H84" s="3" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/4760</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>4760</v>
+      </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses mathematical equations and numerical methods (SHAKE algorithm, first-order vs quadratic solving) and includes an image of the relevant equation.</t>
+          <t>The issue discusses missing harmonic bond force definitions for specific atom classes in a molecular mechanics force field XML file, which involves domain-specific scientific knowledge about protein structure and force field parameters.</t>
         </is>
       </c>
     </row>
@@ -3950,16 +4426,16 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>3090</v>
+        <v>3901</v>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Spherical computational domain</t>
+          <t>Support another GROMACS bond type</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/3090</t>
+          <t>https://github.com/openmm/openmm/issues/3901</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -3975,14 +4451,20 @@
       <c r="G85" s="3" t="inlineStr"/>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>question</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="n"/>
-      <c r="J85" s="2" t="n"/>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/4028</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>4028</v>
+      </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses implementing spherical boundary conditions with complex cumulative distribution functions for reinjecting particles, referencing specific equations from a scientific paper, which involves domain-specific scientific knowledge in computational physics and molecular dynamics.</t>
+          <t>The issue requests support for new bond and angle function types from GROMACS force fields, which is a domain-specific scientific feature for molecular dynamics simulations.</t>
         </is>
       </c>
     </row>
@@ -3993,16 +4475,16 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>3008</v>
+        <v>4152</v>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Update charges in every step</t>
+          <t>Parametrize protein with uncapped residues</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/3008</t>
+          <t>https://github.com/openmm/openmm/issues/4152</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -4017,11 +4499,17 @@
       </c>
       <c r="G86" s="3" t="inlineStr"/>
       <c r="H86" s="3" t="inlineStr"/>
-      <c r="I86" s="2" t="n"/>
-      <c r="J86" s="2" t="n"/>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/4161</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>4161</v>
+      </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses implementing a polarizable model (CTPOL) with a mathematical formula for charge transfer depending on atomic distances, involving domain-specific scientific knowledge about force fields and electrostatics.</t>
+          <t>The issue involves domain-specific scientific knowledge about molecular force fields, protein parametrization, and chemical patches for uncapped residues, with no images present.</t>
         </is>
       </c>
     </row>
@@ -4032,16 +4520,16 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>2033</v>
+        <v>3304</v>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>AMOEBA plugin documentation improvements</t>
+          <t>Source build produces HarmonicBondForce error for AMOEBA</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/2033</t>
+          <t>https://github.com/openmm/openmm/issues/3304</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -4055,16 +4543,18 @@
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr"/>
-      <c r="H87" s="3" t="inlineStr">
-        <is>
-          <t>documentation</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="n"/>
-      <c r="J87" s="2" t="n"/>
+      <c r="H87" s="3" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/3311</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>3311</v>
+      </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses domain-specific scientific concepts like polarizable forcefields, units for polarizability, Thole damping, and polarization groups, and references equations in cited literature, which qualifies as Type 1.</t>
+          <t>The issue discusses a negative spring constant in the Urey-Bradley term of the AMOEBA force field, which is a domain-specific concept in molecular mechanics and force field parameterization.</t>
         </is>
       </c>
     </row>
@@ -4075,16 +4565,16 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>3026</v>
+        <v>3815</v>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Specific custom external force</t>
+          <t>CHARMM-Drude 2019 residue patch</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/3026</t>
+          <t>https://github.com/openmm/openmm/issues/3815</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -4098,12 +4588,22 @@
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr"/>
-      <c r="H88" s="3" t="inlineStr"/>
-      <c r="I88" s="2" t="n"/>
-      <c r="J88" s="2" t="n"/>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/3851</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>3851</v>
+      </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>The issue involves domain-specific scientific knowledge about solving coupled Newton's and Poisson's equations for charged particles, including numerical methods and electrostatic potential calculations.</t>
+          <t>The issue discusses missing bond topology in CHARMM-Drude force field XML patches, which is a domain-specific scientific bug affecting molecular simulation correctness.</t>
         </is>
       </c>
     </row>
@@ -4114,16 +4614,16 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>2931</v>
+        <v>3185</v>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>What is the best way to calculate time-averaged distances in a custom force?</t>
+          <t>Raise exceptions if non-physical parameters are defined in forces</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/2931</t>
+          <t>https://github.com/openmm/openmm/issues/3185</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -4137,12 +4637,1310 @@
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr"/>
-      <c r="H89" s="3" t="inlineStr"/>
-      <c r="I89" s="2" t="n"/>
-      <c r="J89" s="2" t="n"/>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/3286</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>3286</v>
+      </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>The issue discusses a mathematical recurrence relation for time-averaged distances, references a scientific paper, and involves custom force implementation with energy expressions, which are domain-specific scientific concepts.</t>
+          <t>The issue proposes adding validation for physical parameters like angles, LJ sigma, epsilon, and GB radii, which involves domain-specific scientific knowledge about molecular force fields and physical constraints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="n">
+        <v>3175</v>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>addHydrogens() fails to add hydrogens to topology with glycam residues</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3175</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>https://user-images.githubusercontent.com/35546250/127049398-b0a85917-367c-4511-8bf1-d9adab2c4c45.png</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/3303</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>3303</v>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses the failure to add hydrogens to glycam residues, involving domain-specific knowledge about molecular modeling, force fields, and hydrogen atom placement, and includes a scientific image of chemical bonds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="n">
+        <v>3094</v>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>bug with NBFIX in python wrapper openmm/app/charmmpsffile.py</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3094</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr"/>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/3210</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>3210</v>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>Issue discusses incorrect handling of NBFIX terms in CHARMM force field parameters, which is a domain-specific scientific feature related to molecular dynamics simulations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Inconsistent PME energy when atoms cross the boundary</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/2500</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr"/>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/2570</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>2570</v>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses inconsistent PME energy calculations under periodic boundary conditions, involving domain-specific concepts like Ewald summation, Coulomb interactions, and bonded forces in molecular simulations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="n">
+        <v>2379</v>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>1-2 / 1-3 nonbonded interactions when creating system using PSF</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/2379</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr"/>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/2381</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>2381</v>
+      </c>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves domain-specific scientific knowledge about nonbonded interaction exclusions in molecular dynamics force fields, specifically for coarse-grained simulations with NBFIX pairs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>4850</v>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Multiple CMAPTorsionForce sections result in incorrect map assignment</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4850</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr"/>
+      <c r="H94" s="3" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/4852</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>4852</v>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>The issue concerns incorrect indexing of CMAP map entries in force field parsing, which directly affects the correctness of molecular mechanics simulations, a domain-specific scientific computation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="n">
+        <v>3006</v>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>Gromacs integration breaks with recent versions (&gt;2018)</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3006</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr"/>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/4246</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>4246</v>
+      </c>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves domain-specific scientific knowledge about molecular dynamics, force fields, implicit solvent, and Gromacs integration, but no scientific images are mentioned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="n">
+        <v>3865</v>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>iAMOEBA (direct polarization) water model no longer working.</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3865</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr"/>
+      <c r="H96" s="3" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/3872</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>3872</v>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves a mathematical problem (division by zero) in the iAMOEBA force field implementation, specifically the sigma parameter in a 14-7 potential causing NaN, which is a domain-specific scientific numerical error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="n">
+        <v>4360</v>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>Unstable Energies with NPT Dynamics in OpenMM 8.1.0</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4360</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/assets/25778144/b3bc5535-fc7d-4bc2-a533-4191107ced92
+https://github.com/openmm/openmm/assets/25778144/eb5b6b13-0784-4fbc-8b4a-94a2cf5b930a</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/4364</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>4364</v>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves molecular dynamics simulations with NPT ensemble, integrators, and barostats (Type 1), and includes embedded scientific plots of potential energy and temperature (Type 2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="n">
+        <v>5248</v>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>Issue for computePressureComponent in MoneCarloFlexibleBarostat</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/5248</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr"/>
+      <c r="H98" s="3" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/5251</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>5251</v>
+      </c>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses mathematical formulation of pressure tensor calculation involving finite difference and volume, referencing specific code and equations, and includes scientific images comparing pressure tensor results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="n">
+        <v>3305</v>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>AMOEBA RNA forcefield cannot match bonding arrangement in PDB</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3305</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>https://user-images.githubusercontent.com/3656088 @peastman: Maybe we want to add the `ambdpdb -conect` suggestion to the [FAQ](https://github.com/openmm/openmm/wiki/Frequently-Asked-Questions#why-am-i-getting-an-error-that-says-no-template-found-for-residue</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/3313</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>3313</v>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses a molecular modeling error involving AMOEBA RNA forcefield, PDB bond matching, and chemical residue templates, which requires domain-specific knowledge of molecular structure and forcefield parameterization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="n">
+        <v>1443</v>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>Add optional bond order to Topology object?</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/1443</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr"/>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/1668</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>1668</v>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses adding bond order information to the Topology object, which is a chemistry-related enhancement involving molecular structure, connectivity, and small molecule parameterization, all domain-specific scientific concepts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="n">
+        <v>3029</v>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>INF Energies in 7.5.0</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3029</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr"/>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/3057</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>3057</v>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>The issue reports incorrect scientific behavior (infinite energy values) in molecular dynamics energy evaluations, involving domain-specific numerical computation and platform-dependent results, which qualifies as a math/science bug.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="n">
+        <v>1193</v>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>Dummy atoms in OpenMM</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/1193</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr"/>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/1302</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>1302</v>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses dummy atoms in OpenMM for molecular dynamics simulations, involving domain-specific concepts like PDB file loading, atom types, charges, and LJ parameters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="n">
+        <v>4716</v>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>`loadCheckpoint()` doesn't reproduce the trajectories for the `LangevinMiddleIntegrator`</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/4716</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr"/>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/4740</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>4740</v>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>The issue describes incorrect scientific behavior in molecular dynamics simulations (trajectory non-reproducibility upon checkpointing) due to differences in random number generator implementations between CPU and other platforms, involving domain-specific knowledge of integrators and stochastic processes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="n">
+        <v>3104</v>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>AMBER14 or CHARMM36 force field with implicit water model?</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/3104</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr"/>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/3214</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>3214</v>
+      </c>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves domain-specific scientific knowledge about molecular dynamics force fields (AMBER14, CHARMM36) and implicit solvent models, including discussion of physical parameters like reaction field dielectric and cutoffs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="n">
+        <v>2585</v>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>Update CHARMM polarizable force field</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/2585</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr"/>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/2738</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>2738</v>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves domain-specific scientific knowledge about updating a CHARMM polarizable force field, including new molecule types and parameter conversion, without any scientific images.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>2502</v>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>CharmmParameterSet Parsing</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/2502</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr"/>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/2596</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>2596</v>
+      </c>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves correct parsing of CHARMM force field parameter files, which is domain-specific scientific knowledge for molecular dynamics simulations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="n">
+        <v>1855</v>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>Additional virtual site types</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/1855</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr"/>
+      <c r="H107" s="3" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/1858</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>1858</v>
+      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses adding new virtual site types for representing lone pairs and sigma holes in force fields, involving domain-specific chemistry concepts and mathematical geometry formulations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>2348</v>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>non-integer residue ID in CHARMM PSF and CRD files</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/2348</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr"/>
+      <c r="H108" s="3" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/2355</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>2355</v>
+      </c>
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves handling non-integer residue IDs with insertion codes in CHARMM PSF and CRD files, which is a domain-specific problem in computational chemistry and molecular dynamics software.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>2392</v>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>OpenMM 7.4.0 crashes when using the Drude-2013 forcefield</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/2392</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr"/>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/2429</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>2429</v>
+      </c>
+      <c r="K109" s="3" t="inlineStr">
+        <is>
+          <t>The issue describes incorrect virtual site placement for lone pairs in a molecular force field, which is a domain-specific scientific behavior affecting simulation correctness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>1612</v>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>Instability in VariableLangevinIntegrator leading to runaway memory leak</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/1612</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr"/>
+      <c r="H110" s="3" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/1628</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>1628</v>
+      </c>
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses numerical instability in a molecular dynamics integrator, involving atomic forces, coordinates, and temperature thresholds, which are domain-specific scientific concepts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="n">
+        <v>1406</v>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>PDBFile should write unrecognized residues as HETATM with CONECT residues</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/1406</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr"/>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/1425</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>This issue involves domain-specific scientific knowledge about PDB file format standards for representing non-standard residues as HETATM records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="n">
+        <v>2239</v>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>Nested cross products don't work in CUDA / OpenCL</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/2239</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr"/>
+      <c r="H112" s="3" t="inlineStr"/>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/2241</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>2241</v>
+      </c>
+      <c r="K112" s="3" t="inlineStr">
+        <is>
+          <t>The issue reports incorrect results from nested cross product computations in a molecular dynamics integrator, which is a domain-specific mathematical operation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="n">
+        <v>2012</v>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>Context.getState randomly returns NaN forces on CPU</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/2012</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr"/>
+      <c r="H113" s="3" t="inlineStr"/>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/2016</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>2016</v>
+      </c>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>The issue reports incorrect force calculations (NaN) due to uninitialized memory in a molecular dynamics force field implementation, which is a domain-specific scientific computation problem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="n">
+        <v>2360</v>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>amber_file_parser produces system with nonzero SA term, even though None is requested</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/2360</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr"/>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/2362</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>2362</v>
+      </c>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves incorrect behavior of an implicit solvent model (GBSA) in a molecular dynamics library, which is a domain-specific scientific concept requiring knowledge of computational chemistry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="n">
+        <v>1742</v>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>OpenMM 7.0 crashes with large system (500k atoms)</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/1742</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr"/>
+      <c r="H115" s="3" t="inlineStr"/>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/1752</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>1752</v>
+      </c>
+      <c r="K115" s="3" t="inlineStr">
+        <is>
+          <t>The issue discusses molecular dynamics simulation details such as solvent placement, initial potential energy values, and minimization failures, which involve domain-specific scientific knowledge in computational chemistry and biophysics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="n">
+        <v>2047</v>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>CHARMM36 termini patches are not recognized/handled</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/2047</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr"/>
+      <c r="H116" s="3" t="inlineStr"/>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/2053</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>2053</v>
+      </c>
+      <c r="K116" s="3" t="inlineStr">
+        <is>
+          <t>The issue involves domain-specific scientific knowledge about CHARMM36 force field residue patches and molecular topology, and describes incorrect scientific behavior where the force field fails to recognize modified termini.</t>
         </is>
       </c>
     </row>
@@ -4157,7 +5955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4189,11 +5987,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>85.2%</t>
         </is>
       </c>
     </row>
@@ -4204,22 +6002,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>13.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
-        <v>88</v>
+      <c r="B5" s="1" t="n">
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/Issues.xlsx
+++ b/Issues.xlsx
@@ -9,11 +9,13 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Issues" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excluded" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evaluation Confound" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excluded" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Issues'!$A$1:$Q$99</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Excluded'!$A$1:$R$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Issues'!$A$1:$Q$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Evaluation Confound'!$A$1:$S$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Excluded'!$A$1:$R$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q99"/>
+  <dimension ref="A1:Q90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3781,45 +3783,49 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>openmm/openmm</t>
+          <t>rdkit/rdkit</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>2689</v>
+        <v>9330</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Langevin dynamics with multiple time steps</t>
+          <t>CDXML reads of atropisomer don't run AssignStereochem</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/2689</t>
+          <t>https://github.com/rdkit/rdkit/issues/9330</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/user-attachments/assets/ffbfd710-c50e-47d4-a680-b51105b3bda9</t>
+        </is>
+      </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>enhancement</t>
+          <t>bug</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/pull/2695</t>
+          <t>https://github.com/rdkit/rdkit/pull/9331</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>2695</v>
+        <v>9331</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
@@ -3828,22 +3834,23 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>wrappers/python/tests/TestIntegrators.py</t>
+          <t>External/ChemDraw/test.cpp
+External/ChemDraw/test_data/atrop-endpoint-cip.cdxml</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>Langevin dynamics with multiple time steps: the oracle requires interpreting the physical or chemical rule encoded by the expected result; deriving the expected scientific value, invariant, units, or tolerance; understanding the domain algorithm and the scientific properties its output must preserve.</t>
+          <t>CDXML reads of atropisomer don't run AssignStereochem: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Molecular Simulation</t>
+          <t>Cheminformatics</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Chemistry or physics semantics; Numerical scientific invariants; Scientific algorithms</t>
+          <t>Scientific format semantics; Molecular representation or stereochemistry</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -3853,56 +3860,52 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>Langevin dynamics with multiple time steps: the oracle requires interpreting the physical or chemical rule encoded by the expected result; deriving the expected scientific value, invariant, units, or tolerance; understanding the domain algorithm and the scientific properties its output must preserve.</t>
+          <t>CDXML reads of atropisomer don't run AssignStereochem: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>openmm/openmm</t>
+          <t>rdkit/rdkit</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>2427</v>
+        <v>6505</v>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Update values for physical constants</t>
+          <t>RegistrationHash.GetMolLayers() with v2 tautomer hash does not filter CX extensions</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/issues/2427</t>
+          <t>https://github.com/rdkit/rdkit/issues/6505</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>https://user-images.githubusercontent.com/3656088/67059150-d4ee9400-f125-11e9-9067-58e81d51f559.png</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="n"/>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>enhancement</t>
+          <t>bug</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/pull/2802</t>
+          <t>https://github.com/rdkit/rdkit/pull/6506</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>2802</v>
+        <v>6506</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
@@ -3911,46 +3914,32 @@
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>plugins/amoeba/platforms/cuda/tests/TestCudaAmoebaAngleForce.cpp
-plugins/amoeba/platforms/cuda/tests/TestCudaAmoebaInPlaneAngleForce.cpp
-plugins/amoeba/platforms/cuda/tests/TestCudaAmoebaOutOfPlaneBendForce.cpp
-plugins/amoeba/platforms/cuda/tests/TestCudaAmoebaPiTorsionForce.cpp
-plugins/amoeba/platforms/cuda/tests/TestCudaAmoebaStretchBendForce.cpp
-plugins/amoeba/platforms/reference/tests/TestReferenceAmoebaAngleForce.cpp
-plugins/amoeba/platforms/reference/tests/TestReferenceAmoebaInPlaneAngleForce.cpp
-plugins/amoeba/platforms/reference/tests/TestReferenceAmoebaOutOfPlaneBendForce.cpp
-plugins/amoeba/platforms/reference/tests/TestReferenceAmoebaPiTorsionForce.cpp
-plugins/amoeba/platforms/reference/tests/TestReferenceAmoebaStretchBendForce.cpp
-plugins/amoeba/serialization/tests/TestSerializeAmoebaMultipoleForce.cpp
-plugins/drude/tests/TestDrudeNoseHoover.h
-plugins/drude/tests/TestDrudeSCFIntegrator.h
-tests/TestEwald.h
-wrappers/python/tests/TestAPIUnits.py</t>
+          <t>Code/GraphMol/MolHash/catch_tests.cpp</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>Update values for physical constants: the oracle requires deriving the expected scientific value, invariant, units, or tolerance.</t>
+          <t>RegistrationHash.GetMolLayers() with v2 tautomer hash does not filter CX extensions: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Molecular Simulation</t>
+          <t>Cheminformatics</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Numerical scientific invariants</t>
+          <t>Scientific format semantics; Scientific algorithms</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>Update values for physical constants: the oracle requires deriving the expected scientific value, invariant, units, or tolerance.</t>
+          <t>RegistrationHash.GetMolLayers() with v2 tautomer hash does not filter CX extensions: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
     </row>
@@ -3961,16 +3950,16 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>9330</v>
+        <v>8965</v>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>CDXML reads of atropisomer don't run AssignStereochem</t>
+          <t>Stereo bond inversion in SMILES Writer canonicalization</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rdkit/rdkit/issues/9330</t>
+          <t>https://github.com/rdkit/rdkit/issues/8965</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -3985,7 +3974,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/user-attachments/assets/ffbfd710-c50e-47d4-a680-b51105b3bda9</t>
+          <t>https://github.com/user-attachments/assets/b8614a3e-5a5f-41d4-acde-2ea585711f8e</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -3995,11 +3984,11 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rdkit/rdkit/pull/9331</t>
+          <t>https://github.com/rdkit/rdkit/pull/8968</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>9331</v>
+        <v>8968</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -4007,249 +3996,6 @@
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t>External/ChemDraw/test.cpp
-External/ChemDraw/test_data/atrop-endpoint-cip.cdxml</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t>CDXML reads of atropisomer don't run AssignStereochem: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>Cheminformatics</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>Scientific format semantics; Molecular representation or stereochemistry</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>CDXML reads of atropisomer don't run AssignStereochem: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>rdkit/rdkit</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="n">
-        <v>6505</v>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>RegistrationHash.GetMolLayers() with v2 tautomer hash does not filter CX extensions</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/issues/6505</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="n"/>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/pull/6506</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="n">
-        <v>6506</v>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr">
-        <is>
-          <t>Code/GraphMol/MolHash/catch_tests.cpp</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t>RegistrationHash.GetMolLayers() with v2 tautomer hash does not filter CX extensions: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; understanding the domain algorithm and the scientific properties its output must preserve.</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>Cheminformatics</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>Scientific format semantics; Scientific algorithms</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>RegistrationHash.GetMolLayers() with v2 tautomer hash does not filter CX extensions: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; understanding the domain algorithm and the scientific properties its output must preserve.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>rdkit/rdkit</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="n">
-        <v>8513</v>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>rdShapeAlign is sensitive to starting conformation</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/issues/8513</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="n"/>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/pull/8999</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t>External/pubchem_shape/Wrap/test_rdshapealign.py
-External/pubchem_shape/test.cpp</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t>rdShapeAlign is sensitive to starting conformation: the oracle requires deriving the expected scientific value, invariant, units, or tolerance; understanding the domain algorithm and the scientific properties its output must preserve.</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Computational Chemistry</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>Numerical scientific invariants; Scientific algorithms</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>rdShapeAlign is sensitive to starting conformation: the oracle requires deriving the expected scientific value, invariant, units, or tolerance; understanding the domain algorithm and the scientific properties its output must preserve.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>rdkit/rdkit</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="n">
-        <v>8965</v>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>Stereo bond inversion in SMILES Writer canonicalization</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/issues/8965</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>1,2</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/user-attachments/assets/b8614a3e-5a5f-41d4-acde-2ea585711f8e</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/pull/8968</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="n">
-        <v>8968</v>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L47" s="3" t="inlineStr">
         <is>
           <t>Code/GraphMol/SmilesParse/catch_tests.cpp
 Code/GraphMol/SmilesParse/smitest1.cpp
@@ -4257,502 +4003,336 @@
 Code/JavaWrappers/gmwrapper/src-test/org/RDKit/SmilesDetailsTests.java</t>
         </is>
       </c>
-      <c r="M47" s="3" t="inlineStr">
+      <c r="M44" s="3" t="inlineStr">
         <is>
           <t>Stereo bond inversion in SMILES Writer canonicalization: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>Cheminformatics</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>Scientific format semantics; Molecular representation or stereochemistry; Scientific algorithms</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>Stereo bond inversion in SMILES Writer canonicalization: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>rdkit/rdkit</t>
         </is>
       </c>
-      <c r="B48" s="2" t="n">
-        <v>8360</v>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>Missing bonds in MCES when singleLargestFrag = True</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/issues/8360</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="B45" s="2" t="n">
+        <v>6945</v>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>FindMolChiralCenters should honor RDK_USE_LEGACY_STEREO_PERCEPTION</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/issues/6945</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/pull/6948</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>6948</v>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Code/GraphMol/Wrap/rough_test.py</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>FindMolChiralCenters should honor RDK_USE_LEGACY_STEREO_PERCEPTION: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Cheminformatics</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Molecular representation or stereochemistry; Scientific algorithms</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>FindMolChiralCenters should honor RDK_USE_LEGACY_STEREO_PERCEPTION: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>rdkit/rdkit</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>6058</v>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Bad drawing of ferrocene</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/issues/6058</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/user-attachments/assets/15042039-734a-444d-813d-f3a96034bea9</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="n"/>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/pull/8376</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="n">
-        <v>8376</v>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L48" s="3" t="inlineStr">
-        <is>
-          <t>Code/GraphMol/RascalMCES/Wrap/testRascalMCES.py</t>
-        </is>
-      </c>
-      <c r="M48" s="3" t="inlineStr">
-        <is>
-          <t>Missing bonds in MCES when singleLargestFrag = True: the oracle requires understanding the domain algorithm and the scientific properties its output must preserve.</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Cheminformatics</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>Scientific algorithms</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>Missing bonds in MCES when singleLargestFrag = True: the oracle requires understanding the domain algorithm and the scientific properties its output must preserve.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>rdkit/rdkit</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="n">
-        <v>6945</v>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>FindMolChiralCenters should honor RDK_USE_LEGACY_STEREO_PERCEPTION</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/issues/6945</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="n"/>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/pull/6948</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="n">
-        <v>6948</v>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L49" s="3" t="inlineStr">
-        <is>
-          <t>Code/GraphMol/Wrap/rough_test.py</t>
-        </is>
-      </c>
-      <c r="M49" s="3" t="inlineStr">
-        <is>
-          <t>FindMolChiralCenters should honor RDK_USE_LEGACY_STEREO_PERCEPTION: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>Cheminformatics</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>Molecular representation or stereochemistry; Scientific algorithms</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>FindMolChiralCenters should honor RDK_USE_LEGACY_STEREO_PERCEPTION: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>rdkit/rdkit</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="n">
-        <v>6058</v>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>Bad drawing of ferrocene</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/issues/6058</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>1,2</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G50" s="3" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
         <is>
           <t>https://user-images.githubusercontent.com/9198870/216962372-db77f0a2-a703-406b-aa94-1c3d4895a1cf.png
 https://user-images.githubusercontent.com/9198870/217028362-48cbd5e2-bd7c-495c-9d0a-355751e7d9d2.png</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t>bug</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/pull/6231</t>
         </is>
       </c>
-      <c r="J50" s="2" t="n">
+      <c r="J46" s="2" t="n">
         <v>6231</v>
       </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L50" s="3" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
         <is>
           <t>Code/GraphMol/Depictor/catch_tests.cpp
 Code/GraphMol/Depictor/testDepictor.cpp
 Code/GraphMol/MolDraw2D/catch_tests.cpp</t>
         </is>
       </c>
-      <c r="M50" s="3" t="inlineStr">
+      <c r="M46" s="3" t="inlineStr">
         <is>
           <t>Bad drawing of ferrocene: the oracle requires interpreting the physical or chemical rule encoded by the expected result; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; distinguishing chemically meaningful depiction from ordinary canvas layout; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>Cheminformatics</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>Chemistry or physics semantics; Molecular representation or stereochemistry; Molecular drawing/visualization meaning; Scientific algorithms</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>Bad drawing of ferrocene: the oracle requires interpreting the physical or chemical rule encoded by the expected result; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; distinguishing chemically meaningful depiction from ordinary canvas layout; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>rdkit/rdkit</t>
         </is>
       </c>
-      <c r="B51" s="2" t="n">
-        <v>6082</v>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>queryMol from FindMCS doesn't match mols used to generate MCS</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/issues/6082</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="B47" s="2" t="n">
+        <v>2042</v>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ability to generate a list of possible smiles representation for a given molecule </t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/issues/2042</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>https://user-images.githubusercontent.com/16563496/112071088-8973bd00-8b45-11eb-9e56-6217931cd5f1.png</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/pull/6646</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="n">
-        <v>6646</v>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L51" s="3" t="inlineStr">
-        <is>
-          <t>Code/GraphMol/FMCS/Test/testFMCS.cpp
-Code/GraphMol/FMCS/Wrap/testFMCS.py
-Code/GraphMol/FMCS/testFMCS_Unit.cpp
-Code/GraphMol/Wrap/rough_test.py
-Code/GraphMol/molopstest.cpp</t>
-        </is>
-      </c>
-      <c r="M51" s="3" t="inlineStr">
-        <is>
-          <t>queryMol from FindMCS doesn't match mols used to generate MCS: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>Cheminformatics</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>Molecular representation or stereochemistry; Scientific algorithms</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>queryMol from FindMCS doesn't match mols used to generate MCS: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>rdkit/rdkit</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="n">
-        <v>2042</v>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ability to generate a list of possible smiles representation for a given molecule </t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/issues/2042</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>1,2</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G52" s="3" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/assets/26168777/bd81aa11-6b2f-46e0-91c0-047c3e921abe</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr">
         <is>
           <t>enhancement
 Hackathon idea</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/pull/2059</t>
         </is>
       </c>
-      <c r="J52" s="2" t="n">
+      <c r="J47" s="2" t="n">
         <v>2059</v>
       </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L52" s="3" t="inlineStr">
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
         <is>
           <t>Code/GraphMol/SmilesParse/test.cpp</t>
         </is>
       </c>
-      <c r="M52" s="3" t="inlineStr">
+      <c r="M47" s="3" t="inlineStr">
         <is>
           <t>Ability to generate a list of possible smiles representation for a given molecule : the oracle requires knowing how the scientific file format represents molecular or simulation meaning; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>Cheminformatics</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>Scientific format semantics; Scientific algorithms</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>Ability to generate a list of possible smiles representation for a given molecule : the oracle requires knowing how the scientific file format represents molecular or simulation meaning; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>rdkit/rdkit</t>
         </is>
       </c>
-      <c r="B53" s="2" t="n">
+      <c r="B48" s="2" t="n">
         <v>5222</v>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>Core with query atoms and no user definded attachment points may create poor decompostions</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/issues/5222</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
         <is>
           <t>https://user-images.githubusercontent.com/24233741/164304524-3cd11e32-80bf-468e-bd27-8031bc545af3.png
 https://user-images.githubusercontent.com/24233741/164304641-a7591015-764c-4a03-a280-3244d1b236e9.png
 https://user-images.githubusercontent.com/24233741/164304930-1f6785f7-5d83-4f3b-bb40-236d9f744dc2.png</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
+      <c r="H48" s="3" t="inlineStr">
         <is>
           <t>bug</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/pull/5232</t>
         </is>
       </c>
-      <c r="J53" s="2" t="n">
+      <c r="J48" s="2" t="n">
         <v>5232</v>
       </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L53" s="3" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
         <is>
           <t>Code/GraphMol/RGroupDecomposition/testRGroupDecomp.cpp
 Code/GraphMol/RGroupDecomposition/test_data/rgd_testing.ipynb
@@ -4760,336 +4340,336 @@
 Code/GraphMol/RGroupDecomposition/test_data/simple2.out1.json</t>
         </is>
       </c>
-      <c r="M53" s="3" t="inlineStr">
+      <c r="M48" s="3" t="inlineStr">
         <is>
           <t>Core with query atoms and no user definded attachment points may create poor decompostions: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>Cheminformatics</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>Molecular representation or stereochemistry; Scientific algorithms</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>Core with query atoms and no user definded attachment points may create poor decompostions: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>rdkit/rdkit</t>
         </is>
       </c>
-      <c r="B54" s="2" t="n">
+      <c r="B49" s="2" t="n">
         <v>4302</v>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>computeCanonicalTransform may generate non-canonical coords</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/issues/4302</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>https://user-images.githubusercontent.com/5244385/124397950-70b59e80-dd13-11eb-9c35-8a4a52c8f3fe.png</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr">
         <is>
           <t>bug</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/pull/4303</t>
         </is>
       </c>
-      <c r="J54" s="2" t="n">
+      <c r="J49" s="2" t="n">
         <v>4303</v>
       </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L54" s="3" t="inlineStr">
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
         <is>
           <t>Code/GraphMol/MolTransforms/Wrap/testMolTransforms.py
 Code/GraphMol/MolTransforms/test1.cpp
 Code/GraphMol/MolTransforms/test_data/github4302.sdf</t>
         </is>
       </c>
-      <c r="M54" s="3" t="inlineStr">
+      <c r="M49" s="3" t="inlineStr">
         <is>
           <t>computeCanonicalTransform may generate non-canonical coords: the oracle requires deriving the expected scientific value, invariant, units, or tolerance; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>Computational Chemistry</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>Numerical scientific invariants; Scientific algorithms</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>computeCanonicalTransform may generate non-canonical coords: the oracle requires deriving the expected scientific value, invariant, units, or tolerance; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>rdkit/rdkit</t>
         </is>
       </c>
-      <c r="B55" s="2" t="n">
+      <c r="B50" s="2" t="n">
         <v>5569</v>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>RGD may yield poor depictions</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/issues/5569</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
         <is>
           <t>https://user-images.githubusercontent.com/24233741/190455728-8da04c3f-a5cc-44c6-a5a7-9f2150401564.png</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr">
+      <c r="H50" s="3" t="inlineStr">
         <is>
           <t>bug</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/pull/5570</t>
         </is>
       </c>
-      <c r="J55" s="2" t="n">
+      <c r="J50" s="2" t="n">
         <v>5570</v>
       </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L55" s="3" t="inlineStr">
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
         <is>
           <t>Code/GraphMol/RGroupDecomposition/testRGroupDecomp.cpp</t>
         </is>
       </c>
-      <c r="M55" s="3" t="inlineStr">
+      <c r="M50" s="3" t="inlineStr">
         <is>
           <t>RGD may yield poor depictions: the oracle requires distinguishing chemically meaningful depiction from ordinary canvas layout; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>Cheminformatics</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>Molecular drawing/visualization meaning; Scientific algorithms</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>RGD may yield poor depictions: the oracle requires distinguishing chemically meaningful depiction from ordinary canvas layout; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>rdkit/rdkit</t>
         </is>
       </c>
-      <c r="B56" s="2" t="n">
+      <c r="B51" s="2" t="n">
         <v>8720</v>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>rdMolTransforms.CanonicalizeConformer inverts structure</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/issues/8720</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G56" s="3" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>https://github.com/user-attachments/assets/e2279ada-e8fb-47d1-bf51-dee9bfe030c9</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr">
         <is>
           <t>bug</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/pull/8734</t>
         </is>
       </c>
-      <c r="J56" s="2" t="n">
+      <c r="J51" s="2" t="n">
         <v>8734</v>
       </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L56" s="3" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
         <is>
           <t>Code/GraphMol/MolTransforms/catch_tests.cpp</t>
         </is>
       </c>
-      <c r="M56" s="3" t="inlineStr">
+      <c r="M51" s="3" t="inlineStr">
         <is>
           <t>rdMolTransforms.CanonicalizeConformer inverts structure: the oracle requires deriving the expected scientific value, invariant, units, or tolerance; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>Computational Chemistry</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>Numerical scientific invariants; Scientific algorithms</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>rdMolTransforms.CanonicalizeConformer inverts structure: the oracle requires deriving the expected scientific value, invariant, units, or tolerance; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>rdkit/rdkit</t>
         </is>
       </c>
-      <c r="B57" s="2" t="n">
+      <c r="B52" s="2" t="n">
         <v>9122</v>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>Kekulization depends on atom/bond ordering, affects tautomer enumeration and canonicalization</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/issues/9122</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
         <is>
           <t>https://github.com/user-attachments/assets/1968c5dd-c139-4622-ba59-51799fd43405</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
+      <c r="H52" s="3" t="inlineStr">
         <is>
           <t>bug</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/pull/9125</t>
         </is>
       </c>
-      <c r="J57" s="2" t="n">
+      <c r="J52" s="2" t="n">
         <v>9125</v>
       </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L57" s="3" t="inlineStr">
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
         <is>
           <t>Code/GraphMol/Depictor/Wrap/testDepictor.py
 Code/GraphMol/Depictor/catch_tests.cpp
@@ -5335,173 +4915,85 @@
 Code/MinimalLib/tests/tests.js</t>
         </is>
       </c>
-      <c r="M57" s="3" t="inlineStr">
+      <c r="M52" s="3" t="inlineStr">
         <is>
           <t>Kekulization depends on atom/bond ordering, affects tautomer enumeration and canonicalization: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>Cheminformatics</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>Scientific format semantics; Scientific algorithms</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>Kekulization depends on atom/bond ordering, affects tautomer enumeration and canonicalization: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>rdkit/rdkit</t>
         </is>
       </c>
-      <c r="B58" t="n">
-        <v>3965</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>rdFMCS.FindMCS uses huge amounts of memory for this pair of molecules when CompleteRingsOnly is True</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/issues/3965</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
+      <c r="B53" s="2" t="n">
+        <v>8973</v>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Atropisomer bond is found in N-S(=O)C system</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/issues/8973</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://user-images.githubusercontent.com/16563496/112071088-8973bd00-8b45-11eb-9e56-6217931cd5f1.png
-https://user-images.githubusercontent.com/7498185/122264971-2eccd180-cea6-11eb-99c5-4e1fcdd9cec2.png</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/user-attachments/assets/d8987b0b-5a06-4eba-a99b-f3781db71166</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
         <is>
           <t>bug</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/pull/6646</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
-        <v>6646</v>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>Code/GraphMol/FMCS/Test/testFMCS.cpp
-Code/GraphMol/FMCS/Wrap/testFMCS.py
-Code/GraphMol/FMCS/testFMCS_Unit.cpp
-Code/GraphMol/Wrap/rough_test.py
-Code/GraphMol/molopstest.cpp</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>rdFMCS.FindMCS uses huge amounts of memory for this pair of molecules when CompleteRingsOnly is True: the oracle requires understanding the domain algorithm and the scientific properties its output must preserve.</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>Cheminformatics</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>Scientific algorithms</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>rdFMCS.FindMCS uses huge amounts of memory for this pair of molecules when CompleteRingsOnly is True: the oracle requires understanding the domain algorithm and the scientific properties its output must preserve.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>rdkit/rdkit</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="n">
-        <v>8973</v>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>Atropisomer bond is found in N-S(=O)C system</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/issues/8973</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>1,2</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/user-attachments/assets/d8987b0b-5a06-4eba-a99b-f3781db71166</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/pull/8974</t>
         </is>
       </c>
-      <c r="J59" s="2" t="n">
+      <c r="J53" s="2" t="n">
         <v>8974</v>
       </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L59" s="3" t="inlineStr">
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
         <is>
           <t>Code/GraphMol/FileParsers/testAtropisomers.cpp
 Code/GraphMol/FileParsers/test_data/atropisomers/sulfinamide-double-bond-O-R.mol
@@ -5509,259 +5001,749 @@
 Code/GraphMol/FileParsers/test_data/atropisomers/sulfinamide-single-bond-O-S.mol</t>
         </is>
       </c>
-      <c r="M59" s="3" t="inlineStr">
+      <c r="M53" s="3" t="inlineStr">
         <is>
           <t>Atropisomer bond is found in N-S(=O)C system: the oracle requires interpreting the physical or chemical rule encoded by the expected result; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>Cheminformatics</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>Chemistry or physics semantics; Molecular representation or stereochemistry</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>Atropisomer bond is found in N-S(=O)C system: the oracle requires interpreting the physical or chemical rule encoded by the expected result; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>rdkit/rdkit</t>
         </is>
       </c>
-      <c r="B60" s="2" t="n">
+      <c r="B54" s="2" t="n">
         <v>8726</v>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>Hydrides in organometallics removed when parsing</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/issues/8726</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
         <is>
           <t>https://github.com/user-attachments/assets/a88a52b0-73cb-43c8-ac1a-2764f4cbac6c
 https://github.com/user-attachments/assets/e2165a68-5961-4212-9325-8b08a4e96634</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
+      <c r="H54" s="3" t="inlineStr">
         <is>
           <t>bug
 changes results</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/pull/8874</t>
         </is>
       </c>
-      <c r="J60" s="2" t="n">
+      <c r="J54" s="2" t="n">
         <v>8874</v>
       </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L60" s="3" t="inlineStr">
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
         <is>
           <t>Code/GraphMol/Wrap/rough_test.py</t>
         </is>
       </c>
-      <c r="M60" s="3" t="inlineStr">
+      <c r="M54" s="3" t="inlineStr">
         <is>
           <t>Hydrides in organometallics removed when parsing: the oracle requires interpreting the physical or chemical rule encoded by the expected result; knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>Cheminformatics</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>Chemistry or physics semantics; Scientific format semantics; Molecular representation or stereochemistry</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>Hydrides in organometallics removed when parsing: the oracle requires interpreting the physical or chemical rule encoded by the expected result; knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>rdkit/rdkit</t>
         </is>
       </c>
-      <c r="B61" s="2" t="n">
+      <c r="B55" s="2" t="n">
         <v>9114</v>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>DetermineBonds fails for thiolate</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/issues/9114</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G61" s="3" t="n"/>
-      <c r="H61" s="3" t="inlineStr">
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="inlineStr">
         <is>
           <t>bug</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/pull/9120</t>
         </is>
       </c>
-      <c r="J61" s="2" t="n">
+      <c r="J55" s="2" t="n">
         <v>9120</v>
       </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L61" s="3" t="inlineStr">
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
         <is>
           <t>Code/GraphMol/DetermineBonds/catch_tests.cpp</t>
         </is>
       </c>
-      <c r="M61" s="3" t="inlineStr">
+      <c r="M55" s="3" t="inlineStr">
         <is>
           <t>DetermineBonds fails for thiolate: the oracle requires interpreting the physical or chemical rule encoded by the expected result; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>Cheminformatics</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>Chemistry or physics semantics; Scientific algorithms</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>DetermineBonds fails for thiolate: the oracle requires interpreting the physical or chemical rule encoded by the expected result; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>rdkit/rdkit</t>
         </is>
       </c>
-      <c r="B62" s="2" t="n">
+      <c r="B56" s="2" t="n">
         <v>9009</v>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>SynthonSpace Substructure search misses a hit - Mk2</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/issues/9009</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
         <is>
           <t>https://github.com/user-attachments/assets/75dd9c04-f71c-4d40-871f-34b29e5600bd
 https://github.com/user-attachments/assets/5e579e99-c7e8-47a3-b556-d99530475ea7
 https://github.com/user-attachments/assets/52dc622f-444c-413e-a0d2-9606d9a6ee44</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
+      <c r="H56" s="3" t="inlineStr">
         <is>
           <t>bug</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/pull/9012</t>
         </is>
       </c>
-      <c r="J62" s="2" t="n">
+      <c r="J56" s="2" t="n">
         <v>9012</v>
       </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L62" s="3" t="inlineStr">
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
         <is>
           <t>Code/GraphMol/ChemTransforms/catch_tests.cpp
 Code/GraphMol/SynthonSpaceSearch/substructure_search_catch_tests.cpp</t>
         </is>
       </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>SynthonSpace Substructure search misses a hit - Mk2: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Cheminformatics</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Molecular representation or stereochemistry; Scientific algorithms</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>SynthonSpace Substructure search misses a hit - Mk2: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>rdkit/rdkit</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>8481</v>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>RDKit minilib get_molblock() returns molV3000 without throwing error</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/issues/8481</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/pull/8808</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>8808</v>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>Code/MinimalLib/cffi_test.c
+Code/MinimalLib/tests/tests.js</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>RDKit minilib get_molblock() returns molV3000 without throwing error: the oracle requires interpreting the physical or chemical rule encoded by the expected result; knowing how the scientific file format represents molecular or simulation meaning.</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Cheminformatics</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Chemistry or physics semantics; Scientific format semantics</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>RDKit minilib get_molblock() returns molV3000 without throwing error: the oracle requires interpreting the physical or chemical rule encoded by the expected result; knowing how the scientific file format represents molecular or simulation meaning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>rdkit/rdkit</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>8201</v>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Possible Off-by-One Bug in the ERG Implementation</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/issues/8201</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/pull/8385</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>8385</v>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>Code/GraphMol/ReducedGraphs/test1.cpp</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>Possible Off-by-One Bug in the ERG Implementation: the oracle requires deriving the expected scientific value, invariant, units, or tolerance; understanding the domain algorithm and the scientific properties its output must preserve.</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Cheminformatics</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Numerical scientific invariants; Scientific algorithms</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Possible Off-by-One Bug in the ERG Implementation: the oracle requires deriving the expected scientific value, invariant, units, or tolerance; understanding the domain algorithm and the scientific properties its output must preserve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>rdkit/rdkit</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>7901</v>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>UFF optimization leads to overlapping atoms</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/issues/7901</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/pull/8264</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>8264</v>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>Code/GraphMol/ForceFieldHelpers/catch_tests.cpp</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>UFF optimization leads to overlapping atoms: the oracle requires interpreting the physical or chemical rule encoded by the expected result; deriving the expected scientific value, invariant, units, or tolerance; understanding the domain algorithm and the scientific properties its output must preserve.</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Computational Chemistry</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Chemistry or physics semantics; Numerical scientific invariants; Scientific algorithms</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>UFF optimization leads to overlapping atoms: the oracle requires interpreting the physical or chemical rule encoded by the expected result; deriving the expected scientific value, invariant, units, or tolerance; understanding the domain algorithm and the scientific properties its output must preserve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>rdkit/rdkit</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>9347</v>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>CDXML reading doesn't respect AbnormalValence flag</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/issues/9347</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/user-attachments/assets/69ceffbc-5133-41b9-b68e-8f0d6515715f
+https://github.com/user-attachments/assets/942ba843-8cd6-4f5e-94c7-760cff021e00</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/pull/9348</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>9348</v>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>External/ChemDraw/test.cpp
+External/ChemDraw/test_data/abnormal-valence-cyclopentane.cdxml</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>CDXML reading doesn't respect AbnormalValence flag: the oracle requires interpreting the physical or chemical rule encoded by the expected result; knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Cheminformatics</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Chemistry or physics semantics; Scientific format semantics; Molecular representation or stereochemistry</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>CDXML reading doesn't respect AbnormalValence flag: the oracle requires interpreting the physical or chemical rule encoded by the expected result; knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>rdkit/rdkit</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>5466</v>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>CXSmiles isn't properly escaping floating point properties</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/issues/5466</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>https://user-images.githubusercontent.com/9888416/181307012-7313ee62-81a7-4099-95cd-5d0ba6a77b4c.png</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/pull/5468</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>5468</v>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>Code/GraphMol/SmilesParse/catch_tests.cpp</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>CXSmiles isn't properly escaping floating point properties: the oracle requires knowing how the scientific file format represents molecular or simulation meaning.</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Cheminformatics</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Scientific format semantics</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>CXSmiles isn't properly escaping floating point properties: the oracle requires knowing how the scientific file format represents molecular or simulation meaning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>rdkit/rdkit</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>9102</v>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Double bond stereo appearing in InChI after tautomer canonicalization</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/issues/9102</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/user-attachments/assets/675e5283-6c09-41ea-b748-47ad5361a48a</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/pull/9119</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>9119</v>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>Code/GraphMol/MolStandardize/Wrap/testMolStandardize.py
+Code/GraphMol/MolStandardize/testTautomer.cpp</t>
+        </is>
+      </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>SynthonSpace Substructure search misses a hit - Mk2: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
+          <t>Double bond stereo appearing in InChI after tautomer canonicalization: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -5771,17 +5753,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Molecular representation or stereochemistry; Scientific algorithms</t>
+          <t>Scientific format semantics; Molecular representation or stereochemistry; Scientific algorithms</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>SynthonSpace Substructure search misses a hit - Mk2: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
+          <t>Double bond stereo appearing in InChI after tautomer canonicalization: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
     </row>
@@ -5792,16 +5774,16 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>8481</v>
+        <v>8906</v>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>RDKit minilib get_molblock() returns molV3000 without throwing error</t>
+          <t>CXSmiles strips away isotopes</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rdkit/rdkit/issues/8481</t>
+          <t>https://github.com/rdkit/rdkit/issues/8906</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -5817,16 +5799,16 @@
       <c r="G63" s="3" t="n"/>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>enhancement</t>
+          <t>bug</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rdkit/rdkit/pull/8808</t>
+          <t>https://github.com/rdkit/rdkit/pull/8907</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>8808</v>
+        <v>8907</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
@@ -5835,13 +5817,12 @@
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>Code/MinimalLib/cffi_test.c
-Code/MinimalLib/tests/tests.js</t>
+          <t>Code/GraphMol/SmilesParse/catch_tests.cpp</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>RDKit minilib get_molblock() returns molV3000 without throwing error: the oracle requires interpreting the physical or chemical rule encoded by the expected result; knowing how the scientific file format represents molecular or simulation meaning.</t>
+          <t>CXSmiles strips away isotopes: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -5851,17 +5832,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Chemistry or physics semantics; Scientific format semantics</t>
+          <t>Scientific format semantics; Molecular representation or stereochemistry</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>RDKit minilib get_molblock() returns molV3000 without throwing error: the oracle requires interpreting the physical or chemical rule encoded by the expected result; knowing how the scientific file format represents molecular or simulation meaning.</t>
+          <t>CXSmiles strips away isotopes: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
         </is>
       </c>
     </row>
@@ -5872,16 +5853,16 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>8201</v>
+        <v>8527</v>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Possible Off-by-One Bug in the ERG Implementation</t>
+          <t>Chem.GetMolFrags Destroys Stereogroups containing only bonds</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rdkit/rdkit/issues/8201</t>
+          <t>https://github.com/rdkit/rdkit/issues/8527</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -5902,11 +5883,11 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rdkit/rdkit/pull/8385</t>
+          <t>https://github.com/rdkit/rdkit/pull/8542</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>8385</v>
+        <v>8542</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
@@ -5915,12 +5896,12 @@
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>Code/GraphMol/ReducedGraphs/test1.cpp</t>
+          <t>Code/GraphMol/molopstest.cpp</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>Possible Off-by-One Bug in the ERG Implementation: the oracle requires deriving the expected scientific value, invariant, units, or tolerance; understanding the domain algorithm and the scientific properties its output must preserve.</t>
+          <t>Chem.GetMolFrags Destroys Stereogroups containing only bonds: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -5930,7 +5911,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Numerical scientific invariants; Scientific algorithms</t>
+          <t>Molecular representation or stereochemistry</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -5940,7 +5921,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>Possible Off-by-One Bug in the ERG Implementation: the oracle requires deriving the expected scientific value, invariant, units, or tolerance; understanding the domain algorithm and the scientific properties its output must preserve.</t>
+          <t>Chem.GetMolFrags Destroys Stereogroups containing only bonds: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
         </is>
       </c>
     </row>
@@ -5951,41 +5932,45 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>7901</v>
+        <v>8467</v>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>UFF optimization leads to overlapping atoms</t>
+          <t>Method to remove enhanced stereo from an atom</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rdkit/rdkit/issues/7901</t>
+          <t>https://github.com/rdkit/rdkit/issues/8467</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G65" s="3" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/user-attachments/assets/7ec15265-f00b-4649-b097-1fc9565c64a0</t>
+        </is>
+      </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>bug</t>
+          <t>enhancement</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rdkit/rdkit/pull/8264</t>
+          <t>https://github.com/rdkit/rdkit/pull/8515</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>8264</v>
+        <v>8515</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
@@ -5994,32 +5979,32 @@
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>Code/GraphMol/ForceFieldHelpers/catch_tests.cpp</t>
+          <t>Code/GraphMol/Wrap/rough_test.py</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>UFF optimization leads to overlapping atoms: the oracle requires interpreting the physical or chemical rule encoded by the expected result; deriving the expected scientific value, invariant, units, or tolerance; understanding the domain algorithm and the scientific properties its output must preserve.</t>
+          <t>Method to remove enhanced stereo from an atom: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Computational Chemistry</t>
+          <t>Cheminformatics</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Chemistry or physics semantics; Numerical scientific invariants; Scientific algorithms</t>
+          <t>Molecular representation or stereochemistry</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>UFF optimization leads to overlapping atoms: the oracle requires interpreting the physical or chemical rule encoded by the expected result; deriving the expected scientific value, invariant, units, or tolerance; understanding the domain algorithm and the scientific properties its output must preserve.</t>
+          <t>Method to remove enhanced stereo from an atom: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
         </is>
       </c>
     </row>
@@ -6030,34 +6015,29 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>9347</v>
+        <v>8288</v>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>CDXML reading doesn't respect AbnormalValence flag</t>
+          <t>molzip doesn't handle linker style zipping</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rdkit/rdkit/issues/9347</t>
+          <t>https://github.com/rdkit/rdkit/issues/8288</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/user-attachments/assets/69ceffbc-5133-41b9-b68e-8f0d6515715f
-https://github.com/user-attachments/assets/942ba843-8cd6-4f5e-94c7-760cff021e00</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="n"/>
       <c r="H66" s="3" t="inlineStr">
         <is>
           <t>bug</t>
@@ -6065,11 +6045,11 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rdkit/rdkit/pull/9348</t>
+          <t>https://github.com/rdkit/rdkit/pull/8289</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>9348</v>
+        <v>8289</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
@@ -6078,13 +6058,12 @@
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>External/ChemDraw/test.cpp
-External/ChemDraw/test_data/abnormal-valence-cyclopentane.cdxml</t>
+          <t>Code/GraphMol/ChemTransforms/catch_tests.cpp</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>CDXML reading doesn't respect AbnormalValence flag: the oracle requires interpreting the physical or chemical rule encoded by the expected result; knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
+          <t>molzip doesn't handle linker style zipping: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -6094,7 +6073,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Chemistry or physics semantics; Scientific format semantics; Molecular representation or stereochemistry</t>
+          <t>Molecular representation or stereochemistry; Scientific algorithms</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -6104,7 +6083,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>CDXML reading doesn't respect AbnormalValence flag: the oracle requires interpreting the physical or chemical rule encoded by the expected result; knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
+          <t>molzip doesn't handle linker style zipping: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
     </row>
@@ -6115,33 +6094,29 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>9354</v>
+        <v>8492</v>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>CDXML reading has no support for cleaning NeedsClean atoms</t>
+          <t>TautomerQuery drops queries for some atoms</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rdkit/rdkit/issues/9354</t>
+          <t>https://github.com/rdkit/rdkit/issues/8492</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/user-attachments/assets/0a290993-6728-48e9-8cf4-1cfdda9fe10f</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="n"/>
       <c r="H67" s="3" t="inlineStr">
         <is>
           <t>bug</t>
@@ -6149,11 +6124,11 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rdkit/rdkit/pull/9355</t>
+          <t>https://github.com/rdkit/rdkit/pull/8493</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>9355</v>
+        <v>8493</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
@@ -6162,13 +6137,12 @@
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>External/ChemDraw/test.cpp
-External/ChemDraw/test_data/needsclean-carbamate-n.cdxml</t>
+          <t>Code/GraphMol/TautomerQuery/catch_tests.cpp</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>CDXML reading has no support for cleaning NeedsClean atoms: the oracle requires interpreting the physical or chemical rule encoded by the expected result; knowing how the scientific file format represents molecular or simulation meaning.</t>
+          <t>TautomerQuery drops queries for some atoms: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -6178,7 +6152,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Chemistry or physics semantics; Scientific format semantics</t>
+          <t>Molecular representation or stereochemistry; Scientific algorithms</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -6188,7 +6162,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>CDXML reading has no support for cleaning NeedsClean atoms: the oracle requires interpreting the physical or chemical rule encoded by the expected result; knowing how the scientific file format represents molecular or simulation meaning.</t>
+          <t>TautomerQuery drops queries for some atoms: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
     </row>
@@ -6199,33 +6173,29 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>5466</v>
+        <v>8238</v>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>CXSmiles isn't properly escaping floating point properties</t>
+          <t>Generating inchi for chiral phosphates raises a warning</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rdkit/rdkit/issues/5466</t>
+          <t>https://github.com/rdkit/rdkit/issues/8238</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G68" s="3" t="inlineStr">
-        <is>
-          <t>https://user-images.githubusercontent.com/9888416/181307012-7313ee62-81a7-4099-95cd-5d0ba6a77b4c.png</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="n"/>
       <c r="H68" s="3" t="inlineStr">
         <is>
           <t>bug</t>
@@ -6233,11 +6203,11 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rdkit/rdkit/pull/5468</t>
+          <t>https://github.com/rdkit/rdkit/pull/8266</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>5468</v>
+        <v>8266</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
@@ -6246,12 +6216,12 @@
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>Code/GraphMol/SmilesParse/catch_tests.cpp</t>
+          <t>External/INCHI-API/test.cpp</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>CXSmiles isn't properly escaping floating point properties: the oracle requires knowing how the scientific file format represents molecular or simulation meaning.</t>
+          <t>Generating inchi for chiral phosphates raises a warning: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -6261,17 +6231,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Scientific format semantics</t>
+          <t>Scientific format semantics; Molecular representation or stereochemistry</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>CXSmiles isn't properly escaping floating point properties: the oracle requires knowing how the scientific file format represents molecular or simulation meaning.</t>
+          <t>Generating inchi for chiral phosphates raises a warning: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
         </is>
       </c>
     </row>
@@ -6282,16 +6252,16 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>8664</v>
+        <v>8348</v>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>RDKit CXSMiles includes "map number" as an atom property</t>
+          <t>Unable to write wiggly bond information by default</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rdkit/rdkit/issues/8664</t>
+          <t>https://github.com/rdkit/rdkit/issues/8348</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -6307,18 +6277,16 @@
       <c r="G69" s="3" t="n"/>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>bug
-Hackathon idea
-changes results</t>
+          <t>bug</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rdkit/rdkit/pull/9002</t>
+          <t>https://github.com/rdkit/rdkit/pull/8367</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>9002</v>
+        <v>8367</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
@@ -6327,23 +6295,13 @@
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>Code/GraphMol/FileParsers/test_data/atropisomers/BMS-986142_3d_chiral.sdf.expected.cxsmi
-Code/GraphMol/FileParsers/test_data/atropisomers/BMS-986142_3d_chiral.sdf.expectedArom.cxsmi
-Code/GraphMol/RGroupDecomposition/Wrap/test_rgroups.py
-Code/GraphMol/SmilesParse/cxsmiles_test.cpp
-Code/GraphMol/SmilesParse/test_data/BMS-986142_3d_chiral.cxsmi
-Code/GraphMol/SmilesParse/test_data/BMS-986142_3d_chiral.cxsmi.expected.cxsmi
-Code/GraphMol/SmilesParse/test_data/BMS-986142_3d_chiral.cxsmi.expected2.cxsmi
-Code/GraphMol/SmilesParse/test_data/BMS-986142_3d_chiral.cxsmi.expected3.cxsmi
-Code/GraphMol/SmilesParse/test_data/BMS-986142_3d_chiral.cxsmi.expected3D.cxsmi
-Code/GraphMol/SmilesParse/test_data/BMS-986142_3d_chiral.cxsmi.expected3D2.cxsmi
-Code/MinimalLib/cffi_test.c
-Code/MinimalLib/tests/tests.js</t>
+          <t>Code/GraphMol/SmilesParse/catch_tests.cpp
+Code/GraphMol/SmilesParse/cxsmiles_test.cpp</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>RDKit CXSMiles includes "map number" as an atom property: the oracle requires knowing how the scientific file format represents molecular or simulation meaning.</t>
+          <t>Unable to write wiggly bond information by default: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -6353,17 +6311,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Scientific format semantics</t>
+          <t>Scientific format semantics; Molecular representation or stereochemistry</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>RDKit CXSMiles includes "map number" as an atom property: the oracle requires knowing how the scientific file format represents molecular or simulation meaning.</t>
+          <t>Unable to write wiggly bond information by default: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
         </is>
       </c>
     </row>
@@ -6374,33 +6332,29 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>9102</v>
+        <v>7944</v>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Double bond stereo appearing in InChI after tautomer canonicalization</t>
+          <t>rxn.RunReactants mismatch directional bonds in a heterocycle ring</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rdkit/rdkit/issues/9102</t>
+          <t>https://github.com/rdkit/rdkit/issues/7944</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G70" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/user-attachments/assets/675e5283-6c09-41ea-b748-47ad5361a48a</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="n"/>
       <c r="H70" s="3" t="inlineStr">
         <is>
           <t>bug</t>
@@ -6408,11 +6362,11 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rdkit/rdkit/pull/9119</t>
+          <t>https://github.com/rdkit/rdkit/pull/8192</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>9119</v>
+        <v>8192</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
@@ -6421,13 +6375,13 @@
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>Code/GraphMol/MolStandardize/Wrap/testMolStandardize.py
-Code/GraphMol/MolStandardize/testTautomer.cpp</t>
+          <t>Code/GraphMol/SmilesParse/smatest.cpp
+Code/GraphMol/Substruct/catch_tests.cpp</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>Double bond stereo appearing in InChI after tautomer canonicalization: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
+          <t>rxn.RunReactants mismatch directional bonds in a heterocycle ring: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -6437,17 +6391,17 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Scientific format semantics; Molecular representation or stereochemistry; Scientific algorithms</t>
+          <t>Molecular representation or stereochemistry; Scientific algorithms</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>Double bond stereo appearing in InChI after tautomer canonicalization: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
+          <t>rxn.RunReactants mismatch directional bonds in a heterocycle ring: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
     </row>
@@ -6458,29 +6412,33 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>8906</v>
+        <v>7044</v>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>CXSmiles strips away isotopes</t>
+          <t>Tautomer canonicalizer invariant violation</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rdkit/rdkit/issues/8906</t>
+          <t>https://github.com/rdkit/rdkit/issues/7044</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/assets/5342086/59265bbd-0b39-4af4-83f1-303a4584c2be</t>
+        </is>
+      </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
           <t>bug</t>
@@ -6488,11 +6446,11 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rdkit/rdkit/pull/8907</t>
+          <t>https://github.com/rdkit/rdkit/pull/7137</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>8907</v>
+        <v>7137</v>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
@@ -6501,12 +6459,12 @@
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>Code/GraphMol/SmilesParse/catch_tests.cpp</t>
+          <t>Code/GraphMol/MolStandardize/testTautomer.cpp</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>CXSmiles strips away isotopes: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
+          <t>Tautomer canonicalizer invariant violation: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -6516,17 +6474,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Scientific format semantics; Molecular representation or stereochemistry</t>
+          <t>Molecular representation or stereochemistry; Scientific algorithms</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>CXSmiles strips away isotopes: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
+          <t>Tautomer canonicalizer invariant violation: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
     </row>
@@ -6537,16 +6495,16 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>8527</v>
+        <v>8265</v>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Chem.GetMolFrags Destroys Stereogroups containing only bonds</t>
+          <t>MolBlocks should fail to write when given coordinates that are too large</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rdkit/rdkit/issues/8527</t>
+          <t>https://github.com/rdkit/rdkit/issues/8265</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -6567,11 +6525,11 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rdkit/rdkit/pull/8542</t>
+          <t>https://github.com/rdkit/rdkit/pull/8269</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>8542</v>
+        <v>8269</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
@@ -6580,12 +6538,12 @@
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>Code/GraphMol/molopstest.cpp</t>
+          <t>Code/GraphMol/FileParsers/testMolWriter.cpp</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>Chem.GetMolFrags Destroys Stereogroups containing only bonds: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
+          <t>MolBlocks should fail to write when given coordinates that are too large: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; deriving the expected scientific value, invariant, units, or tolerance.</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -6595,17 +6553,17 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Molecular representation or stereochemistry</t>
+          <t>Scientific format semantics; Numerical scientific invariants</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>Chem.GetMolFrags Destroys Stereogroups containing only bonds: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
+          <t>MolBlocks should fail to write when given coordinates that are too large: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; deriving the expected scientific value, invariant, units, or tolerance.</t>
         </is>
       </c>
     </row>
@@ -6616,45 +6574,41 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>8467</v>
+        <v>9229</v>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Method to remove enhanced stereo from an atom</t>
+          <t>Incorrect UFF Inversion term gradient for P/As/Sb/Bi centers</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rdkit/rdkit/issues/8467</t>
+          <t>https://github.com/rdkit/rdkit/issues/9229</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G73" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/user-attachments/assets/7ec15265-f00b-4649-b097-1fc9565c64a0</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="n"/>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>enhancement</t>
+          <t>bug</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rdkit/rdkit/pull/8515</t>
+          <t>https://github.com/rdkit/rdkit/pull/9228</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>8515</v>
+        <v>9228</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
@@ -6663,32 +6617,32 @@
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>Code/GraphMol/Wrap/rough_test.py</t>
+          <t>Code/ForceField/UFF/testUFFForceField.cpp</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>Method to remove enhanced stereo from an atom: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
+          <t>Incorrect UFF Inversion term gradient for P/As/Sb/Bi centers: the oracle requires deriving the expected scientific value, invariant, units, or tolerance; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Cheminformatics</t>
+          <t>Computational Chemistry</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Molecular representation or stereochemistry</t>
+          <t>Numerical scientific invariants; Scientific algorithms</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>Method to remove enhanced stereo from an atom: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
+          <t>Incorrect UFF Inversion term gradient for P/As/Sb/Bi centers: the oracle requires deriving the expected scientific value, invariant, units, or tolerance; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
     </row>
@@ -6699,16 +6653,16 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>8288</v>
+        <v>508</v>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>molzip doesn't handle linker style zipping</t>
+          <t>Adding MCS support for atom match distance threshold?</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rdkit/rdkit/issues/8288</t>
+          <t>https://github.com/rdkit/rdkit/issues/508</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -6724,16 +6678,16 @@
       <c r="G74" s="3" t="n"/>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>bug</t>
+          <t>question</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rdkit/rdkit/pull/8289</t>
+          <t>https://github.com/rdkit/rdkit/pull/3749</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>8289</v>
+        <v>3749</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
@@ -6741,1130 +6695,492 @@
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
-        <is>
-          <t>Code/GraphMol/ChemTransforms/catch_tests.cpp</t>
-        </is>
-      </c>
-      <c r="M74" s="3" t="inlineStr">
-        <is>
-          <t>molzip doesn't handle linker style zipping: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>Cheminformatics</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>Molecular representation or stereochemistry; Scientific algorithms</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>molzip doesn't handle linker style zipping: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>rdkit/rdkit</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="n">
-        <v>8492</v>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>TautomerQuery drops queries for some atoms</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/issues/8492</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G75" s="3" t="n"/>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/pull/8493</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="n">
-        <v>8493</v>
-      </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L75" s="3" t="inlineStr">
-        <is>
-          <t>Code/GraphMol/TautomerQuery/catch_tests.cpp</t>
-        </is>
-      </c>
-      <c r="M75" s="3" t="inlineStr">
-        <is>
-          <t>TautomerQuery drops queries for some atoms: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>Cheminformatics</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>Molecular representation or stereochemistry; Scientific algorithms</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>TautomerQuery drops queries for some atoms: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>rdkit/rdkit</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="n">
-        <v>8238</v>
-      </c>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t>Generating inchi for chiral phosphates raises a warning</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/issues/8238</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G76" s="3" t="n"/>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/pull/8266</t>
-        </is>
-      </c>
-      <c r="J76" s="2" t="n">
-        <v>8266</v>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L76" s="3" t="inlineStr">
-        <is>
-          <t>External/INCHI-API/test.cpp</t>
-        </is>
-      </c>
-      <c r="M76" s="3" t="inlineStr">
-        <is>
-          <t>Generating inchi for chiral phosphates raises a warning: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>Cheminformatics</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>Scientific format semantics; Molecular representation or stereochemistry</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>Generating inchi for chiral phosphates raises a warning: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>rdkit/rdkit</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="n">
-        <v>8348</v>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>Unable to write wiggly bond information by default</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/issues/8348</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G77" s="3" t="n"/>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/pull/8367</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="n">
-        <v>8367</v>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L77" s="3" t="inlineStr">
-        <is>
-          <t>Code/GraphMol/SmilesParse/catch_tests.cpp
-Code/GraphMol/SmilesParse/cxsmiles_test.cpp</t>
-        </is>
-      </c>
-      <c r="M77" s="3" t="inlineStr">
-        <is>
-          <t>Unable to write wiggly bond information by default: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>Cheminformatics</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>Scientific format semantics; Molecular representation or stereochemistry</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>Unable to write wiggly bond information by default: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>rdkit/rdkit</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="n">
-        <v>7944</v>
-      </c>
-      <c r="C78" s="3" t="inlineStr">
-        <is>
-          <t>rxn.RunReactants mismatch directional bonds in a heterocycle ring</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/issues/7944</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G78" s="3" t="n"/>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/pull/8192</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="n">
-        <v>8192</v>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L78" s="3" t="inlineStr">
-        <is>
-          <t>Code/GraphMol/SmilesParse/smatest.cpp
-Code/GraphMol/Substruct/catch_tests.cpp</t>
-        </is>
-      </c>
-      <c r="M78" s="3" t="inlineStr">
-        <is>
-          <t>rxn.RunReactants mismatch directional bonds in a heterocycle ring: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>Cheminformatics</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>Molecular representation or stereochemistry; Scientific algorithms</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>rxn.RunReactants mismatch directional bonds in a heterocycle ring: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>rdkit/rdkit</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="n">
-        <v>7044</v>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t>Tautomer canonicalizer invariant violation</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/issues/7044</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>1,2</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G79" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/assets/5342086/59265bbd-0b39-4af4-83f1-303a4584c2be</t>
-        </is>
-      </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/pull/7137</t>
-        </is>
-      </c>
-      <c r="J79" s="2" t="n">
-        <v>7137</v>
-      </c>
-      <c r="K79" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L79" s="3" t="inlineStr">
-        <is>
-          <t>Code/GraphMol/MolStandardize/testTautomer.cpp</t>
-        </is>
-      </c>
-      <c r="M79" s="3" t="inlineStr">
-        <is>
-          <t>Tautomer canonicalizer invariant violation: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>Cheminformatics</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>Molecular representation or stereochemistry; Scientific algorithms</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>Tautomer canonicalizer invariant violation: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>rdkit/rdkit</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="n">
-        <v>8265</v>
-      </c>
-      <c r="C80" s="3" t="inlineStr">
-        <is>
-          <t>MolBlocks should fail to write when given coordinates that are too large</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/issues/8265</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G80" s="3" t="n"/>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/pull/8269</t>
-        </is>
-      </c>
-      <c r="J80" s="2" t="n">
-        <v>8269</v>
-      </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L80" s="3" t="inlineStr">
-        <is>
-          <t>Code/GraphMol/FileParsers/testMolWriter.cpp</t>
-        </is>
-      </c>
-      <c r="M80" s="3" t="inlineStr">
-        <is>
-          <t>MolBlocks should fail to write when given coordinates that are too large: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; deriving the expected scientific value, invariant, units, or tolerance.</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>Cheminformatics</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>Scientific format semantics; Numerical scientific invariants</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>MolBlocks should fail to write when given coordinates that are too large: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; deriving the expected scientific value, invariant, units, or tolerance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>rdkit/rdkit</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="n">
-        <v>9229</v>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t>Incorrect UFF Inversion term gradient for P/As/Sb/Bi centers</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/issues/9229</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G81" s="3" t="n"/>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/pull/9228</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="n">
-        <v>9228</v>
-      </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L81" s="3" t="inlineStr">
-        <is>
-          <t>Code/ForceField/UFF/testUFFForceField.cpp</t>
-        </is>
-      </c>
-      <c r="M81" s="3" t="inlineStr">
-        <is>
-          <t>Incorrect UFF Inversion term gradient for P/As/Sb/Bi centers: the oracle requires deriving the expected scientific value, invariant, units, or tolerance; understanding the domain algorithm and the scientific properties its output must preserve.</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>Computational Chemistry</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>Numerical scientific invariants; Scientific algorithms</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>Incorrect UFF Inversion term gradient for P/As/Sb/Bi centers: the oracle requires deriving the expected scientific value, invariant, units, or tolerance; understanding the domain algorithm and the scientific properties its output must preserve.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>rdkit/rdkit</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="n">
-        <v>508</v>
-      </c>
-      <c r="C82" s="3" t="inlineStr">
-        <is>
-          <t>Adding MCS support for atom match distance threshold?</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/issues/508</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G82" s="3" t="n"/>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>question</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/pull/3749</t>
-        </is>
-      </c>
-      <c r="J82" s="2" t="n">
-        <v>3749</v>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L82" s="3" t="inlineStr">
         <is>
           <t>Code/GraphMol/FMCS/Wrap/testFMCS.py
 Code/GraphMol/FMCS/testData/Jnk1_ligands.sdf
 Code/GraphMol/FMCS/testFMCS_Unit.cpp</t>
         </is>
       </c>
-      <c r="M82" s="3" t="inlineStr">
+      <c r="M74" s="3" t="inlineStr">
         <is>
           <t>Adding MCS support for atom match distance threshold?: the oracle requires deriving the expected scientific value, invariant, units, or tolerance; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>Cheminformatics</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>Numerical scientific invariants; Scientific algorithms</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>Adding MCS support for atom match distance threshold?: the oracle requires deriving the expected scientific value, invariant, units, or tolerance; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>rdkit/rdkit</t>
         </is>
       </c>
-      <c r="B83" s="2" t="n">
+      <c r="B75" s="2" t="n">
         <v>2082</v>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>CTABs behave differently than before regarding stereo</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/issues/2082</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G83" s="3" t="n"/>
-      <c r="H83" s="3" t="inlineStr">
+      <c r="G75" s="3" t="n"/>
+      <c r="H75" s="3" t="inlineStr">
         <is>
           <t>bug</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/pull/2083</t>
         </is>
       </c>
-      <c r="J83" s="2" t="n">
+      <c r="J75" s="2" t="n">
         <v>2083</v>
       </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L83" s="3" t="inlineStr">
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
         <is>
           <t>Code/GraphMol/Wrap/rough_test.py
 Code/GraphMol/Wrap/test_data/issue2082.mol</t>
         </is>
       </c>
-      <c r="M83" s="3" t="inlineStr">
+      <c r="M75" s="3" t="inlineStr">
         <is>
           <t>CTABs behave differently than before regarding stereo: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>Cheminformatics</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>Scientific format semantics; Molecular representation or stereochemistry</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>CTABs behave differently than before regarding stereo: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>rdkit/rdkit</t>
         </is>
       </c>
-      <c r="B84" s="2" t="n">
+      <c r="B76" s="2" t="n">
         <v>9007</v>
       </c>
-      <c r="C84" s="3" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>SynthonSpace Substructure search misses some hits</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/issues/9007</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G84" s="3" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
         <is>
           <t>https://github.com/user-attachments/assets/cef73269-3769-4a91-b560-08d6afa7b328</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr">
+      <c r="H76" s="3" t="inlineStr">
         <is>
           <t>bug</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/pull/9022</t>
         </is>
       </c>
-      <c r="J84" s="2" t="n">
+      <c r="J76" s="2" t="n">
         <v>9022</v>
       </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L84" s="3" t="inlineStr">
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
         <is>
           <t>Code/GraphMol/SynthonSpaceSearch/LONG_TEST_catch_tests.cpp
 Code/GraphMol/SynthonSpaceSearch/substructure_search_catch_tests.cpp</t>
         </is>
       </c>
-      <c r="M84" s="3" t="inlineStr">
+      <c r="M76" s="3" t="inlineStr">
         <is>
           <t>SynthonSpace Substructure search misses some hits: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>Cheminformatics</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t>Molecular representation or stereochemistry; Scientific algorithms</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>SynthonSpace Substructure search misses some hits: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>rdkit/rdkit</t>
         </is>
       </c>
-      <c r="B85" s="2" t="n">
+      <c r="B77" s="2" t="n">
         <v>8584</v>
       </c>
-      <c r="C85" s="3" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>Allow creation of bond-only stereogroups from Python</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/issues/8584</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G85" s="3" t="n"/>
-      <c r="H85" s="3" t="inlineStr">
+      <c r="G77" s="3" t="n"/>
+      <c r="H77" s="3" t="inlineStr">
         <is>
           <t>enhancement</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/pull/8587</t>
         </is>
       </c>
-      <c r="J85" s="2" t="n">
+      <c r="J77" s="2" t="n">
         <v>8587</v>
       </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L85" s="3" t="inlineStr">
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
         <is>
           <t>Code/GraphMol/Wrap/rough_test.py</t>
         </is>
       </c>
-      <c r="M85" s="3" t="inlineStr">
+      <c r="M77" s="3" t="inlineStr">
         <is>
           <t>Allow creation of bond-only stereogroups from Python: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>Cheminformatics</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t>Molecular representation or stereochemistry</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr">
+      <c r="P77" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>Allow creation of bond-only stereogroups from Python: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>rdkit/rdkit</t>
         </is>
       </c>
-      <c r="B86" s="2" t="n">
+      <c r="B78" s="2" t="n">
         <v>8650</v>
       </c>
-      <c r="C86" s="3" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>Enhanced stereo synthons break SynthonSpace.ReadTextFile</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/issues/8650</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G86" s="3" t="n"/>
-      <c r="H86" s="3" t="inlineStr">
+      <c r="G78" s="3" t="n"/>
+      <c r="H78" s="3" t="inlineStr">
         <is>
           <t>bug</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/pull/8652</t>
         </is>
       </c>
-      <c r="J86" s="2" t="n">
+      <c r="J78" s="2" t="n">
         <v>8652</v>
       </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L86" s="3" t="inlineStr">
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
         <is>
           <t>Code/GraphMol/SynthonSpaceSearch/substructure_search_catch_tests.cpp</t>
         </is>
       </c>
-      <c r="M86" s="3" t="inlineStr">
+      <c r="M78" s="3" t="inlineStr">
         <is>
           <t>Enhanced stereo synthons break SynthonSpace.ReadTextFile: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>Cheminformatics</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>Scientific format semantics; Molecular representation or stereochemistry</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
+      <c r="P78" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="Q86" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t>Enhanced stereo synthons break SynthonSpace.ReadTextFile: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>rdkit/rdkit</t>
         </is>
       </c>
-      <c r="B87" s="2" t="n">
+      <c r="B79" s="2" t="n">
         <v>7570</v>
       </c>
-      <c r="C87" s="3" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t>Complex query atoms in reactions don't show their map number.</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/issues/7570</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G87" s="3" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/assets/9198870/54e5629d-4b81-4bfa-b1bd-932dc3f875d5</t>
         </is>
       </c>
-      <c r="H87" s="3" t="inlineStr">
+      <c r="H79" s="3" t="inlineStr">
         <is>
           <t>bug</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/pull/7571</t>
         </is>
       </c>
-      <c r="J87" s="2" t="n">
+      <c r="J79" s="2" t="n">
         <v>7571</v>
       </c>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L87" s="3" t="inlineStr">
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
         <is>
           <t>Code/GraphMol/MolDraw2D/catch_tests.cpp</t>
         </is>
       </c>
-      <c r="M87" s="3" t="inlineStr">
+      <c r="M79" s="3" t="inlineStr">
         <is>
           <t>Complex query atoms in reactions don't show their map number: the oracle requires distinguishing chemically meaningful depiction from ordinary canvas layout.</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>Cheminformatics</t>
         </is>
       </c>
-      <c r="O87" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t>Molecular drawing/visualization meaning</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr">
+      <c r="P79" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t>Complex query atoms in reactions don't show their map number: the oracle requires distinguishing chemically meaningful depiction from ordinary canvas layout.</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>rdkit/rdkit</t>
         </is>
       </c>
-      <c r="B88" s="2" t="n">
+      <c r="B80" s="2" t="n">
         <v>7372</v>
       </c>
-      <c r="C88" s="3" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>SMILES output option to disable the RDKit dative bond syntax</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/issues/7372</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G88" s="3" t="n"/>
-      <c r="H88" s="3" t="inlineStr">
+      <c r="G80" s="3" t="n"/>
+      <c r="H80" s="3" t="inlineStr">
         <is>
           <t>enhancement</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/pull/7384</t>
         </is>
       </c>
-      <c r="J88" s="2" t="n">
+      <c r="J80" s="2" t="n">
         <v>7384</v>
       </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L88" s="3" t="inlineStr">
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
         <is>
           <t>Code/GraphMol/ChemReactions/Wrap/testReactionWrapper.py
 Code/GraphMol/ChemReactions/catch_tests.cpp
@@ -7873,796 +7189,716 @@
 Code/GraphMol/Wrap/rough_test.py</t>
         </is>
       </c>
-      <c r="M88" s="3" t="inlineStr">
+      <c r="M80" s="3" t="inlineStr">
         <is>
           <t>SMILES output option to disable the RDKit dative bond syntax: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>Cheminformatics</t>
         </is>
       </c>
-      <c r="O88" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>Scientific format semantics; Molecular representation or stereochemistry</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr">
+      <c r="P80" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr">
+      <c r="Q80" t="inlineStr">
         <is>
           <t>SMILES output option to disable the RDKit dative bond syntax: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>rdkit/rdkit</t>
         </is>
       </c>
-      <c r="B89" s="2" t="n">
+      <c r="B81" s="2" t="n">
         <v>5890</v>
       </c>
-      <c r="C89" s="3" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>Chemical reactions with radicals cannot be pickled and unpickled.</t>
         </is>
       </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/issues/5890</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G89" s="3" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
         <is>
           <t>https://user-images.githubusercontent.com/840684/209118954-731f2047-5e61-4d63-93d7-8d20f303f6cb.png
 https://user-images.githubusercontent.com/840684/209120177-96c3b310-f22b-477c-b074-a0eb33036b1e.png</t>
         </is>
       </c>
-      <c r="H89" s="3" t="inlineStr">
+      <c r="H81" s="3" t="inlineStr">
         <is>
           <t>bug</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/pull/7152</t>
         </is>
       </c>
-      <c r="J89" s="2" t="n">
+      <c r="J81" s="2" t="n">
         <v>7152</v>
       </c>
-      <c r="K89" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L89" s="3" t="inlineStr">
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
         <is>
           <t>Code/GraphMol/ChemReactions/testData/v3k.radicals.rxn
 Code/GraphMol/ChemReactions/testReaction.cpp</t>
         </is>
       </c>
-      <c r="M89" s="3" t="inlineStr">
+      <c r="M81" s="3" t="inlineStr">
         <is>
           <t>Chemical reactions with radicals cannot be pickled and unpickled: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>Cheminformatics</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t>Scientific format semantics; Molecular representation or stereochemistry</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr">
+      <c r="P81" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr">
+      <c r="Q81" t="inlineStr">
         <is>
           <t>Chemical reactions with radicals cannot be pickled and unpickled: the oracle requires knowing how the scientific file format represents molecular or simulation meaning; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>rdkit/rdkit</t>
         </is>
       </c>
-      <c r="B90" s="2" t="n">
+      <c r="B82" s="2" t="n">
         <v>7108</v>
       </c>
-      <c r="C90" s="3" t="inlineStr">
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t>Add option to sanitize reaction components like molecules</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/issues/7108</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G90" s="3" t="n"/>
-      <c r="H90" s="3" t="inlineStr">
+      <c r="G82" s="3" t="n"/>
+      <c r="H82" s="3" t="inlineStr">
         <is>
           <t>enhancement</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/pull/7116</t>
         </is>
       </c>
-      <c r="J90" s="2" t="n">
+      <c r="J82" s="2" t="n">
         <v>7116</v>
       </c>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L90" s="3" t="inlineStr">
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
         <is>
           <t>Code/GraphMol/ChemReactions/Wrap/testReactionWrapper.py
 Code/GraphMol/ChemReactions/catch_tests.cpp</t>
         </is>
       </c>
-      <c r="M90" s="3" t="inlineStr">
+      <c r="M82" s="3" t="inlineStr">
         <is>
           <t>Add option to sanitize reaction components like molecules: the oracle requires interpreting the physical or chemical rule encoded by the expected result; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>Cheminformatics</t>
         </is>
       </c>
-      <c r="O90" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t>Chemistry or physics semantics; Scientific algorithms</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr">
+      <c r="P82" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="Q90" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>Add option to sanitize reaction components like molecules: the oracle requires interpreting the physical or chemical rule encoded by the expected result; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>rdkit/rdkit</t>
         </is>
       </c>
-      <c r="B91" s="2" t="n">
+      <c r="B83" s="2" t="n">
         <v>6195</v>
       </c>
-      <c r="C91" s="3" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr">
         <is>
           <t>ReactionFromRxnBlock fails on bond with reacting center status set</t>
         </is>
       </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/issues/6195</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G91" s="3" t="n"/>
-      <c r="H91" s="3" t="inlineStr">
+      <c r="G83" s="3" t="n"/>
+      <c r="H83" s="3" t="inlineStr">
         <is>
           <t>bug</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/pull/6199</t>
         </is>
       </c>
-      <c r="J91" s="2" t="n">
+      <c r="J83" s="2" t="n">
         <v>6199</v>
       </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L91" s="3" t="inlineStr">
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
         <is>
           <t>Code/GraphMol/ChemReactions/catch_tests.cpp</t>
         </is>
       </c>
-      <c r="M91" s="3" t="inlineStr">
+      <c r="M83" s="3" t="inlineStr">
         <is>
           <t>ReactionFromRxnBlock fails on bond with reacting center status set: the oracle requires interpreting the physical or chemical rule encoded by the expected result; knowing how the scientific file format represents molecular or simulation meaning.</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t>Cheminformatics</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr">
+      <c r="O83" t="inlineStr">
         <is>
           <t>Chemistry or physics semantics; Scientific format semantics</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr">
+      <c r="P83" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="Q91" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t>ReactionFromRxnBlock fails on bond with reacting center status set: the oracle requires interpreting the physical or chemical rule encoded by the expected result; knowing how the scientific file format represents molecular or simulation meaning.</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>rdkit/rdkit</t>
         </is>
       </c>
-      <c r="B92" s="2" t="n">
+      <c r="B84" s="2" t="n">
         <v>6211</v>
       </c>
-      <c r="C92" s="3" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t>Support chirality when determining if a molecule is a reaction reactant</t>
         </is>
       </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/issues/6211</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G92" s="3" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
         <is>
           <t>https://user-images.githubusercontent.com/24233741/225975812-b4de7297-156f-42c4-8374-bc40c934c60b.png
 https://user-images.githubusercontent.com/24233741/225975959-f6ec0b8e-a273-4cb7-bc83-228d4aacd8bc.png
 https://user-images.githubusercontent.com/24233741/225976050-9ec1ee2b-3178-414a-bf1c-152dd23d3c85.png</t>
         </is>
       </c>
-      <c r="H92" s="3" t="inlineStr">
+      <c r="H84" s="3" t="inlineStr">
         <is>
           <t>enhancement</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/pull/6250</t>
         </is>
       </c>
-      <c r="J92" s="2" t="n">
+      <c r="J84" s="2" t="n">
         <v>6250</v>
       </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L92" s="3" t="inlineStr">
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
         <is>
           <t>Code/GraphMol/ChemReactions/Wrap/testReactionWrapper.py
 Code/GraphMol/ChemReactions/catch_tests.cpp</t>
         </is>
       </c>
-      <c r="M92" s="3" t="inlineStr">
+      <c r="M84" s="3" t="inlineStr">
         <is>
           <t>Support chirality when determining if a molecule is a reaction reactant: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t>Cheminformatics</t>
         </is>
       </c>
-      <c r="O92" t="inlineStr">
+      <c r="O84" t="inlineStr">
         <is>
           <t>Molecular representation or stereochemistry; Scientific algorithms</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr">
+      <c r="P84" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="Q92" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t>Support chirality when determining if a molecule is a reaction reactant: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>rdkit/rdkit</t>
         </is>
       </c>
-      <c r="B93" s="2" t="n">
+      <c r="B85" s="2" t="n">
         <v>6015</v>
       </c>
-      <c r="C93" s="3" t="inlineStr">
+      <c r="C85" s="3" t="inlineStr">
         <is>
           <t>Reactions do not propagate query information to products</t>
         </is>
       </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/issues/6015</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G93" s="3" t="n"/>
-      <c r="H93" s="3" t="inlineStr">
+      <c r="G85" s="3" t="n"/>
+      <c r="H85" s="3" t="inlineStr">
         <is>
           <t>bug</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/pull/6021</t>
         </is>
       </c>
-      <c r="J93" s="2" t="n">
+      <c r="J85" s="2" t="n">
         <v>6021</v>
       </c>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L93" s="3" t="inlineStr">
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
         <is>
           <t>Code/GraphMol/ChemReactions/catch_tests.cpp</t>
         </is>
       </c>
-      <c r="M93" s="3" t="inlineStr">
+      <c r="M85" s="3" t="inlineStr">
         <is>
           <t>Reactions do not propagate query information to products: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr">
+      <c r="N85" t="inlineStr">
         <is>
           <t>Cheminformatics</t>
         </is>
       </c>
-      <c r="O93" t="inlineStr">
+      <c r="O85" t="inlineStr">
         <is>
           <t>Molecular representation or stereochemistry; Scientific algorithms</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr">
+      <c r="P85" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="Q93" t="inlineStr">
+      <c r="Q85" t="inlineStr">
         <is>
           <t>Reactions do not propagate query information to products: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>rdkit/rdkit</t>
         </is>
       </c>
-      <c r="B94" s="2" t="n">
+      <c r="B86" s="2" t="n">
         <v>4410</v>
       </c>
-      <c r="C94" s="3" t="inlineStr">
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t>RDKit reaction produces wrong double bond stereochemistry</t>
         </is>
       </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/issues/4410</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G94" s="3" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
         <is>
           <t>https://user-images.githubusercontent.com/2325645/129032086-a062fb07-2b5a-407d-87ee-4c3afced813a.png
 https://user-images.githubusercontent.com/2325645/129036437-e8720572-7077-4349-92f5-cc42f8fcc51c.png
 https://user-images.githubusercontent.com/2325645/129036475-4877b1ef-bab6-4959-9a28-bda3771d53fd.png</t>
         </is>
       </c>
-      <c r="H94" s="3" t="inlineStr">
+      <c r="H86" s="3" t="inlineStr">
         <is>
           <t>bug</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/pull/4414</t>
         </is>
       </c>
-      <c r="J94" s="2" t="n">
+      <c r="J86" s="2" t="n">
         <v>4414</v>
       </c>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L94" s="3" t="inlineStr">
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
         <is>
           <t>Code/GraphMol/ChemReactions/testReaction.cpp</t>
         </is>
       </c>
-      <c r="M94" s="3" t="inlineStr">
+      <c r="M86" s="3" t="inlineStr">
         <is>
           <t>RDKit reaction produces wrong double bond stereochemistry: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t>Cheminformatics</t>
         </is>
       </c>
-      <c r="O94" t="inlineStr">
+      <c r="O86" t="inlineStr">
         <is>
           <t>Molecular representation or stereochemistry</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr">
+      <c r="P86" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="Q94" t="inlineStr">
+      <c r="Q86" t="inlineStr">
         <is>
           <t>RDKit reaction produces wrong double bond stereochemistry: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>rdkit/rdkit</t>
         </is>
       </c>
-      <c r="B95" s="2" t="n">
+      <c r="B87" s="2" t="n">
         <v>2547</v>
       </c>
-      <c r="C95" s="3" t="inlineStr">
+      <c r="C87" s="3" t="inlineStr">
         <is>
           <t>Default sanitizerxn doesn't aromatize if possible</t>
         </is>
       </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/issues/2547</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G95" s="3" t="n"/>
-      <c r="H95" s="3" t="inlineStr">
+      <c r="G87" s="3" t="n"/>
+      <c r="H87" s="3" t="inlineStr">
         <is>
           <t>bug</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr">
+      <c r="I87" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/pull/2548</t>
         </is>
       </c>
-      <c r="J95" s="2" t="n">
+      <c r="J87" s="2" t="n">
         <v>2548</v>
       </c>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L95" s="3" t="inlineStr">
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
         <is>
           <t>Code/GraphMol/ChemReactions/Wrap/testSanitize.py
 Code/GraphMol/ChemReactions/testData/kekule_reaction.rxn
 Code/GraphMol/ChemReactions/testReaction.cpp</t>
         </is>
       </c>
-      <c r="M95" s="3" t="inlineStr">
+      <c r="M87" s="3" t="inlineStr">
         <is>
           <t>Default sanitizerxn doesn't aromatize if possible: the oracle requires interpreting the physical or chemical rule encoded by the expected result; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr">
+      <c r="N87" t="inlineStr">
         <is>
           <t>Cheminformatics</t>
         </is>
       </c>
-      <c r="O95" t="inlineStr">
+      <c r="O87" t="inlineStr">
         <is>
           <t>Chemistry or physics semantics; Scientific algorithms</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr">
+      <c r="P87" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="Q95" t="inlineStr">
+      <c r="Q87" t="inlineStr">
         <is>
           <t>Default sanitizerxn doesn't aromatize if possible: the oracle requires interpreting the physical or chemical rule encoded by the expected result; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>rdkit/rdkit</t>
         </is>
       </c>
-      <c r="B96" s="2" t="n">
-        <v>3078</v>
-      </c>
-      <c r="C96" s="3" t="inlineStr">
-        <is>
-          <t>Reactions setting unspecified double-bond stereo to STEREOANY</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/issues/3078</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="B88" s="2" t="n">
+        <v>3097</v>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>Reactions should not use strict implicit valence calculations</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/issues/3097</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G96" s="3" t="n"/>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>bug
-changes results</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/pull/3729</t>
-        </is>
-      </c>
-      <c r="J96" s="2" t="n">
-        <v>3729</v>
-      </c>
-      <c r="K96" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L96" s="3" t="inlineStr">
+      <c r="G88" s="3" t="n"/>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/pull/3098</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>3098</v>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
         <is>
           <t>Code/GraphMol/ChemReactions/testReaction.cpp</t>
         </is>
       </c>
-      <c r="M96" s="3" t="inlineStr">
-        <is>
-          <t>Reactions setting unspecified double-bond stereo to STEREOANY: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>Reactions should not use strict implicit valence calculations: the oracle requires interpreting the physical or chemical rule encoded by the expected result; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
         <is>
           <t>Cheminformatics</t>
         </is>
       </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>Molecular representation or stereochemistry</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr">
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Chemistry or physics semantics; Molecular representation or stereochemistry</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>Reactions setting unspecified double-bond stereo to STEREOANY: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>Reactions should not use strict implicit valence calculations: the oracle requires interpreting the physical or chemical rule encoded by the expected result; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>rdkit/rdkit</t>
         </is>
       </c>
-      <c r="B97" s="2" t="n">
-        <v>3097</v>
-      </c>
-      <c r="C97" s="3" t="inlineStr">
-        <is>
-          <t>Reactions should not use strict implicit valence calculations</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/issues/3097</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G97" s="3" t="n"/>
-      <c r="H97" s="3" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/pull/3098</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="n">
-        <v>3098</v>
-      </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L97" s="3" t="inlineStr">
-        <is>
-          <t>Code/GraphMol/ChemReactions/testReaction.cpp</t>
-        </is>
-      </c>
-      <c r="M97" s="3" t="inlineStr">
-        <is>
-          <t>Reactions should not use strict implicit valence calculations: the oracle requires interpreting the physical or chemical rule encoded by the expected result; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>Cheminformatics</t>
-        </is>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>Chemistry or physics semantics; Molecular representation or stereochemistry</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>Reactions should not use strict implicit valence calculations: the oracle requires interpreting the physical or chemical rule encoded by the expected result; reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>rdkit/rdkit</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="n">
+      <c r="B89" s="2" t="n">
         <v>2891</v>
       </c>
-      <c r="C98" s="3" t="inlineStr">
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t>Issue with inversion/retention of stereochemistry</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/issues/2891</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G98" s="3" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
         <is>
           <t>https://user-images.githubusercontent.com/10458975/72764165-c0de8680-3b9b-11ea-95bf-1a17ce5df62b.png
 https://user-images.githubusercontent.com/10458975/72764304-5d088d80-3b9c-11ea-8310-3f57aab080d0.png
@@ -8673,137 +7909,137 @@
 https://user-images.githubusercontent.com/10458975/72764967-12d4db80-3b9f-11ea-9a9f-1cf961e257a4.png</t>
         </is>
       </c>
-      <c r="H98" s="3" t="inlineStr">
+      <c r="H89" s="3" t="inlineStr">
         <is>
           <t>bug</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr">
+      <c r="I89" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/pull/3412</t>
         </is>
       </c>
-      <c r="J98" s="2" t="n">
+      <c r="J89" s="2" t="n">
         <v>3412</v>
       </c>
-      <c r="K98" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L98" s="3" t="inlineStr">
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
         <is>
           <t>Code/GraphMol/ChemReactions/catch_tests.cpp</t>
         </is>
       </c>
-      <c r="M98" s="3" t="inlineStr">
+      <c r="M89" s="3" t="inlineStr">
         <is>
           <t>Issue with inversion/retention of stereochemistry: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr">
+      <c r="N89" t="inlineStr">
         <is>
           <t>Cheminformatics</t>
         </is>
       </c>
-      <c r="O98" t="inlineStr">
+      <c r="O89" t="inlineStr">
         <is>
           <t>Molecular representation or stereochemistry; Scientific algorithms</t>
         </is>
       </c>
-      <c r="P98" t="inlineStr">
+      <c r="P89" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="Q98" t="inlineStr">
+      <c r="Q89" t="inlineStr">
         <is>
           <t>Issue with inversion/retention of stereochemistry: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>rdkit/rdkit</t>
         </is>
       </c>
-      <c r="B99" s="2" t="n">
+      <c r="B90" s="2" t="n">
         <v>2366</v>
       </c>
-      <c r="C99" s="3" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>Preserve Enhanced Stereochemistry information through reactions</t>
         </is>
       </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/issues/2366</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G99" s="3" t="n"/>
-      <c r="H99" s="3" t="inlineStr">
+      <c r="G90" s="3" t="n"/>
+      <c r="H90" s="3" t="inlineStr">
         <is>
           <t>enhancement</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr">
         <is>
           <t>https://github.com/rdkit/rdkit/pull/2377</t>
         </is>
       </c>
-      <c r="J99" s="2" t="n">
+      <c r="J90" s="2" t="n">
         <v>2377</v>
       </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L99" s="3" t="inlineStr">
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
         <is>
           <t>Code/GraphMol/ChemReactions/Wrap/testReactionWrapper.py
 Code/GraphMol/ChemReactions/catch_tests.cpp</t>
         </is>
       </c>
-      <c r="M99" s="3" t="inlineStr">
+      <c r="M90" s="3" t="inlineStr">
         <is>
           <t>Preserve Enhanced Stereochemistry information through reactions: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr">
+      <c r="N90" t="inlineStr">
         <is>
           <t>Cheminformatics</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr">
+      <c r="O90" t="inlineStr">
         <is>
           <t>Molecular representation or stereochemistry; Scientific algorithms</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr">
+      <c r="P90" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="Q99" t="inlineStr">
+      <c r="Q90" t="inlineStr">
         <is>
           <t>Preserve Enhanced Stereochemistry information through reactions: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q99"/>
+  <autoFilter ref="A1:Q90"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
@@ -8818,189 +8054,200 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId207"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9012,7 +8259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -9044,7 +8291,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9065,257 +8312,267 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Evaluation Confound</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Original Total</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B5" t="n">
         <v>138</v>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Problem Domain</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>% of Retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Cheminformatics</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>51</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>52.0%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Computational Chemistry</t>
+          <t>Cheminformatics</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>50.6%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Computational Chemistry</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Molecular Simulation</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>42</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="B10" t="n">
+        <v>40</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>44.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Problem Type (multi-label)</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>% of Retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Chemistry or physics semantics</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>40</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>40.8%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Molecular drawing/visualization meaning</t>
+          <t>Chemistry or physics semantics</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>42.7%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Molecular representation or stereochemistry</t>
+          <t>Molecular drawing/visualization meaning</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>3.4%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Numerical scientific invariants</t>
+          <t>Molecular representation or stereochemistry</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>44.9%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Scientific algorithms</t>
+          <t>Numerical scientific invariants</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.7%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Scientific algorithms</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>44</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>49.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Scientific format semantics</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>37</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>37.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="B18" t="n">
+        <v>35</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>39.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Scientific Difficulty</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>% of Retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>11</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>11.2%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>51.7%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>33</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>37.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>98</v>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="B24" t="n">
+        <v>89</v>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -9327,6 +8584,1020 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="70" customWidth="1" min="17" max="17"/>
+    <col width="34" customWidth="1" min="18" max="18"/>
+    <col width="95" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Repo</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Issue Number</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Has Images</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Image URLs</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Labels</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Closing PR</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Closing PR #</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Has Tests</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Test Files</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Problem Domain</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Problem Type</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Scientific Difficulty</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Scientific Challenge</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Confound Reason</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Confound Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>2689</v>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Langevin dynamics with multiple time steps</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/2689</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/2695</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>2695</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>wrappers/python/tests/TestIntegrators.py</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>Langevin dynamics with multiple time steps: the oracle requires interpreting the physical or chemical rule encoded by the expected result; deriving the expected scientific value, invariant, units, or tolerance; understanding the domain algorithm and the scientific properties its output must preserve.</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Molecular Simulation</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Chemistry or physics semantics; Numerical scientific invariants; Scientific algorithms</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Langevin dynamics with multiple time steps: the oracle requires interpreting the physical or chemical rule encoded by the expected result; deriving the expected scientific value, invariant, units, or tolerance; understanding the domain algorithm and the scientific properties its output must preserve.</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>Baseline selector/harness confound</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>Broad pytest selection stopped at pre-existing testBadGroups in both base and gold runs; the generated MTS test was not isolated or scored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>openmm/openmm</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>2427</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Update values for physical constants</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/issues/2427</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>https://user-images.githubusercontent.com/3656088/67059150-d4ee9400-f125-11e9-9067-58e81d51f559.png</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/openmm/openmm/pull/2802</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>2802</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>plugins/amoeba/platforms/cuda/tests/TestCudaAmoebaAngleForce.cpp
+plugins/amoeba/platforms/cuda/tests/TestCudaAmoebaInPlaneAngleForce.cpp
+plugins/amoeba/platforms/cuda/tests/TestCudaAmoebaOutOfPlaneBendForce.cpp
+plugins/amoeba/platforms/cuda/tests/TestCudaAmoebaPiTorsionForce.cpp
+plugins/amoeba/platforms/cuda/tests/TestCudaAmoebaStretchBendForce.cpp
+plugins/amoeba/platforms/reference/tests/TestReferenceAmoebaAngleForce.cpp
+plugins/amoeba/platforms/reference/tests/TestReferenceAmoebaInPlaneAngleForce.cpp
+plugins/amoeba/platforms/reference/tests/TestReferenceAmoebaOutOfPlaneBendForce.cpp
+plugins/amoeba/platforms/reference/tests/TestReferenceAmoebaPiTorsionForce.cpp
+plugins/amoeba/platforms/reference/tests/TestReferenceAmoebaStretchBendForce.cpp
+plugins/amoeba/serialization/tests/TestSerializeAmoebaMultipoleForce.cpp
+plugins/drude/tests/TestDrudeNoseHoover.h
+plugins/drude/tests/TestDrudeSCFIntegrator.h
+tests/TestEwald.h
+wrappers/python/tests/TestAPIUnits.py</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Update values for physical constants: the oracle requires deriving the expected scientific value, invariant, units, or tolerance.</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Molecular Simulation</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Numerical scientific invariants</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Update values for physical constants: the oracle requires deriving the expected scientific value, invariant, units, or tolerance.</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>Baseline selector/harness confound</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>Broad pytest selection stopped at pre-existing testAmoebaAngleForce in both base and gold runs; the generated constants test was not isolated or scored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>rdkit/rdkit</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>8513</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>rdShapeAlign is sensitive to starting conformation</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/issues/8513</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/pull/8999</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>8999</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>External/pubchem_shape/Wrap/test_rdshapealign.py
+External/pubchem_shape/test.cpp</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>rdShapeAlign is sensitive to starting conformation: the oracle requires deriving the expected scientific value, invariant, units, or tolerance; understanding the domain algorithm and the scientific properties its output must preserve.</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Computational Chemistry</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Numerical scientific invariants; Scientific algorithms</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>rdShapeAlign is sensitive to starting conformation: the oracle requires deriving the expected scientific value, invariant, units, or tolerance; understanding the domain algorithm and the scientific properties its output must preserve.</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>Gold patch breaks pre-existing tests</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>The full test_rdshapealign.py gold run failed/errored pre-existing tests test3, test5, test7, and test8; generated tests test10 and test11 were not the failures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>rdkit/rdkit</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>8360</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Missing bonds in MCES when singleLargestFrag = True</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/issues/8360</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/user-attachments/assets/15042039-734a-444d-813d-f3a96034bea9</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/pull/8376</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>8376</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Code/GraphMol/RascalMCES/Wrap/testRascalMCES.py</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Missing bonds in MCES when singleLargestFrag = True: the oracle requires understanding the domain algorithm and the scientific properties its output must preserve.</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Cheminformatics</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Scientific algorithms</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Missing bonds in MCES when singleLargestFrag = True: the oracle requires understanding the domain algorithm and the scientific properties its output must preserve.</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>Gold patch breaks pre-existing test</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>The full testRascalMCES.py gold run failed pre-existing test5; generated testGithubIssue8376 was not the failing test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>rdkit/rdkit</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>6082</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>queryMol from FindMCS doesn't match mols used to generate MCS</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/issues/6082</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>https://user-images.githubusercontent.com/16563496/112071088-8973bd00-8b45-11eb-9e56-6217931cd5f1.png</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/pull/6646</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>6646</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Code/GraphMol/FMCS/Test/testFMCS.cpp
+Code/GraphMol/FMCS/Wrap/testFMCS.py
+Code/GraphMol/FMCS/testFMCS_Unit.cpp
+Code/GraphMol/Wrap/rough_test.py
+Code/GraphMol/molopstest.cpp</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>queryMol from FindMCS doesn't match mols used to generate MCS: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Cheminformatics</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Molecular representation or stereochemistry; Scientific algorithms</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>queryMol from FindMCS doesn't match mols used to generate MCS: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state; understanding the domain algorithm and the scientific properties its output must preserve.</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>Gold patch breaks pre-existing tests</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>The full testFMCS.py gold run produced 32 errors in pre-existing Python-implementation tests after the MCS API refactor; the generated regression was not the failing test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>rdkit/rdkit</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3965</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>rdFMCS.FindMCS uses huge amounts of memory for this pair of molecules when CompleteRingsOnly is True</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/issues/3965</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://user-images.githubusercontent.com/16563496/112071088-8973bd00-8b45-11eb-9e56-6217931cd5f1.png
+https://user-images.githubusercontent.com/7498185/122264971-2eccd180-cea6-11eb-99c5-4e1fcdd9cec2.png</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/pull/6646</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>6646</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Code/GraphMol/FMCS/Test/testFMCS.cpp
+Code/GraphMol/FMCS/Wrap/testFMCS.py
+Code/GraphMol/FMCS/testFMCS_Unit.cpp
+Code/GraphMol/Wrap/rough_test.py
+Code/GraphMol/molopstest.cpp</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>rdFMCS.FindMCS uses huge amounts of memory for this pair of molecules when CompleteRingsOnly is True: the oracle requires understanding the domain algorithm and the scientific properties its output must preserve.</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Cheminformatics</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Scientific algorithms</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>rdFMCS.FindMCS uses huge amounts of memory for this pair of molecules when CompleteRingsOnly is True: the oracle requires understanding the domain algorithm and the scientific properties its output must preserve.</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Gold patch breaks pre-existing tests</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>The full testFMCS.py gold run produced 32 errors in pre-existing Python-implementation tests after the MCS API refactor; the generated regression was not the failing test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>rdkit/rdkit</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>9354</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>CDXML reading has no support for cleaning NeedsClean atoms</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/issues/9354</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/user-attachments/assets/0a290993-6728-48e9-8cf4-1cfdda9fe10f</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/pull/9355</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>9355</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>External/ChemDraw/test.cpp
+External/ChemDraw/test_data/needsclean-carbamate-n.cdxml</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>CDXML reading has no support for cleaning NeedsClean atoms: the oracle requires interpreting the physical or chemical rule encoded by the expected result; knowing how the scientific file format represents molecular or simulation meaning.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Cheminformatics</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Chemistry or physics semantics; Scientific format semantics</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>CDXML reading has no support for cleaning NeedsClean atoms: the oracle requires interpreting the physical or chemical rule encoded by the expected result; knowing how the scientific file format represents molecular or simulation meaning.</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>Gold patch breaks pre-existing test</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>The gold run failed and segfaulted in pre-existing ChemDraw checks at lines 495/498 before the generated NeedsClean test could be scored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>rdkit/rdkit</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>8664</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>RDKit CXSMiles includes "map number" as an atom property</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/issues/8664</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>bug
+Hackathon idea
+changes results</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/pull/9002</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>9002</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Code/GraphMol/FileParsers/test_data/atropisomers/BMS-986142_3d_chiral.sdf.expected.cxsmi
+Code/GraphMol/FileParsers/test_data/atropisomers/BMS-986142_3d_chiral.sdf.expectedArom.cxsmi
+Code/GraphMol/RGroupDecomposition/Wrap/test_rgroups.py
+Code/GraphMol/SmilesParse/cxsmiles_test.cpp
+Code/GraphMol/SmilesParse/test_data/BMS-986142_3d_chiral.cxsmi
+Code/GraphMol/SmilesParse/test_data/BMS-986142_3d_chiral.cxsmi.expected.cxsmi
+Code/GraphMol/SmilesParse/test_data/BMS-986142_3d_chiral.cxsmi.expected2.cxsmi
+Code/GraphMol/SmilesParse/test_data/BMS-986142_3d_chiral.cxsmi.expected3.cxsmi
+Code/GraphMol/SmilesParse/test_data/BMS-986142_3d_chiral.cxsmi.expected3D.cxsmi
+Code/GraphMol/SmilesParse/test_data/BMS-986142_3d_chiral.cxsmi.expected3D2.cxsmi
+Code/MinimalLib/cffi_test.c
+Code/MinimalLib/tests/tests.js</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>RDKit CXSMiles includes "map number" as an atom property: the oracle requires knowing how the scientific file format represents molecular or simulation meaning.</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Cheminformatics</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Scientific format semantics</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>RDKit CXSMiles includes "map number" as an atom property: the oracle requires knowing how the scientific file format represents molecular or simulation meaning.</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>Gold patch breaks pre-existing tests</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <t>The gold run failed pre-existing CXSMILES expectations at lines 745, 771, 798, 988, and 1016; the generated map-number test passed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>rdkit/rdkit</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>3078</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Reactions setting unspecified double-bond stereo to STEREOANY</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/issues/3078</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>bug
+changes results</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/pull/3729</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>3729</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Code/GraphMol/ChemReactions/testReaction.cpp</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Reactions setting unspecified double-bond stereo to STEREOANY: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Cheminformatics</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Molecular representation or stereochemistry</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Reactions setting unspecified double-bond stereo to STEREOANY: the oracle requires reasoning about atoms, bonds, valence, molecular graphs, or stereochemical state.</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>Gold patch breaks pre-existing test</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t>The gold run aborted on a pre-existing reaction assertion expecting STEREOANY; the base run had instead failed the generated regression, so the generated test could not be scored after the fix.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:S10"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId23"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
